--- a/Excel/一方通行/logos.xlsx
+++ b/Excel/一方通行/logos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965F097D-F080-43B2-AC55-F15CE33FD584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2784F7-17B8-4CE3-8D84-FFCD682F4908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="566">
   <si>
     <t>Id</t>
   </si>
@@ -1504,9 +1504,6 @@
     <t>0,0#0,1#0,-1#1,0#2,0#1,1#1,-1#2,1#2,-1#3,0#3,1#3,-1</t>
   </si>
   <si>
-    <t>逻各斯1攻击,逻1斩杀</t>
-  </si>
-  <si>
     <t>逻各斯1启动</t>
   </si>
   <si>
@@ -1523,9 +1520,6 @@
   </si>
   <si>
     <t>Skill_1_Attack</t>
-  </si>
-  <si>
-    <t>逻1斩杀</t>
   </si>
   <si>
     <t>Target.Hp&lt;Unit.Attack*1.5</t>
@@ -1995,6 +1989,22 @@
   </si>
   <si>
     <t>string</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>#逻1斩杀</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻各斯1攻击,逻1斩杀</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>#逻各斯1</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻各斯1攻击</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -6018,7 +6028,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DJ653"/>
+  <dimension ref="A1:DJ654"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6230,10 +6240,10 @@
         <v>182</v>
       </c>
       <c r="AR1" s="13" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AS1" s="13" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AT1" t="s">
         <v>183</v>
@@ -6565,10 +6575,10 @@
         <v>284</v>
       </c>
       <c r="AR2" s="13" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AS2" s="13" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AT2" t="s">
         <v>285</v>
@@ -6903,10 +6913,10 @@
         <v>2</v>
       </c>
       <c r="AR3" s="13" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AS3" s="13" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AT3" t="s">
         <v>357</v>
@@ -7421,8 +7431,8 @@
       </c>
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>393</v>
+      <c r="A11" s="13" t="s">
+        <v>564</v>
       </c>
       <c r="C11" t="s">
         <v>370</v>
@@ -7463,11 +7473,11 @@
       <c r="BD11">
         <v>1</v>
       </c>
-      <c r="BO11" t="s">
+      <c r="BO11" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="BP11" t="s">
         <v>401</v>
-      </c>
-      <c r="BP11" t="s">
-        <v>402</v>
       </c>
       <c r="BT11">
         <v>99999</v>
@@ -7494,7 +7504,7 @@
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
       <c r="CN11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="CO11">
         <v>1</v>
@@ -7503,96 +7513,107 @@
         <v>99999</v>
       </c>
       <c r="CU11" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C12" t="s">
         <v>370</v>
       </c>
-      <c r="J12" s="3"/>
+      <c r="D12" t="s">
+        <v>394</v>
+      </c>
+      <c r="E12" t="s">
+        <v>395</v>
+      </c>
+      <c r="F12" t="s">
+        <v>396</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="J12" t="s">
+        <v>397</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>398</v>
+      </c>
       <c r="M12"/>
       <c r="N12"/>
-      <c r="O12" t="s">
-        <v>406</v>
-      </c>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12">
-        <v>2</v>
-      </c>
-      <c r="AD12">
-        <v>1</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>371</v>
+        <v>1</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>399</v>
       </c>
       <c r="AT12" t="s">
         <v>400</v>
       </c>
-      <c r="AX12" t="s">
-        <v>373</v>
-      </c>
-      <c r="AZ12">
-        <v>1</v>
-      </c>
       <c r="BD12">
         <v>1</v>
       </c>
+      <c r="BO12" s="13" t="s">
+        <v>565</v>
+      </c>
       <c r="BP12" t="s">
-        <v>374</v>
-      </c>
-      <c r="BV12"/>
-      <c r="CB12" t="s">
-        <v>407</v>
-      </c>
-      <c r="CG12" t="s">
-        <v>376</v>
-      </c>
-      <c r="CH12" t="s">
-        <v>377</v>
-      </c>
-      <c r="CI12" t="s">
-        <v>378</v>
-      </c>
-      <c r="CL12" t="s">
-        <v>379</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="BT12">
+        <v>99999</v>
+      </c>
+      <c r="BV12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW12" s="4">
+        <v>60</v>
+      </c>
+      <c r="BX12" s="4">
+        <v>1</v>
+      </c>
+      <c r="BY12" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="BZ12"/>
+      <c r="CA12"/>
+      <c r="CB12" s="3"/>
+      <c r="CC12" s="3"/>
+      <c r="CD12" s="3"/>
+      <c r="CE12" s="3"/>
+      <c r="CF12" s="3"/>
+      <c r="CK12" s="3"/>
+      <c r="CL12" s="3"/>
       <c r="CN12" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="CO12">
-        <v>-10</v>
-      </c>
-      <c r="CP12">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="CR12">
-        <v>5</v>
-      </c>
-      <c r="CY12" t="s">
-        <v>381</v>
+        <v>99999</v>
+      </c>
+      <c r="CU12" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C13" t="s">
         <v>370</v>
       </c>
-      <c r="H13" t="s">
-        <v>409</v>
-      </c>
+      <c r="J13" s="3"/>
       <c r="M13"/>
       <c r="N13"/>
       <c r="O13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
@@ -7605,10 +7626,10 @@
         <v>1</v>
       </c>
       <c r="AO13" t="s">
-        <v>383</v>
-      </c>
-      <c r="AW13">
-        <v>1</v>
+        <v>371</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>400</v>
       </c>
       <c r="AX13" t="s">
         <v>373</v>
@@ -7622,292 +7643,328 @@
       <c r="BP13" t="s">
         <v>374</v>
       </c>
-      <c r="CB13" s="3"/>
-      <c r="CC13" s="3"/>
-      <c r="CD13" s="3"/>
-      <c r="CE13" s="3"/>
-      <c r="CF13" s="3"/>
-      <c r="CJ13" s="3"/>
-      <c r="CK13" s="3"/>
+      <c r="BV13"/>
+      <c r="CB13" t="s">
+        <v>406</v>
+      </c>
+      <c r="CG13" t="s">
+        <v>376</v>
+      </c>
+      <c r="CH13" t="s">
+        <v>377</v>
+      </c>
+      <c r="CI13" t="s">
+        <v>378</v>
+      </c>
       <c r="CL13" t="s">
         <v>379</v>
       </c>
       <c r="CN13" t="s">
-        <v>410</v>
+        <v>380</v>
+      </c>
+      <c r="CO13">
+        <v>-10</v>
+      </c>
+      <c r="CP13">
+        <v>0.1</v>
       </c>
       <c r="CR13">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="CY13" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>402</v>
+      <c r="A14" s="13" t="s">
+        <v>562</v>
       </c>
       <c r="C14" t="s">
         <v>370</v>
       </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>382</v>
+      <c r="H14" t="s">
+        <v>407</v>
       </c>
       <c r="M14"/>
       <c r="N14"/>
+      <c r="O14" t="s">
+        <v>405</v>
+      </c>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14">
-        <v>1</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>399</v>
+        <v>2</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>383</v>
+      </c>
+      <c r="AW14">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AZ14">
+        <v>1</v>
       </c>
       <c r="BD14">
         <v>1</v>
       </c>
-      <c r="BS14">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="CB14" s="3" t="s">
-        <v>411</v>
-      </c>
+      <c r="BP14" t="s">
+        <v>374</v>
+      </c>
+      <c r="CB14" s="3"/>
       <c r="CC14" s="3"/>
       <c r="CD14" s="3"/>
       <c r="CE14" s="3"/>
       <c r="CF14" s="3"/>
-      <c r="CG14" t="s">
-        <v>376</v>
-      </c>
-      <c r="CH14" s="3"/>
-      <c r="CI14" s="3"/>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
-      <c r="CL14" s="3"/>
-      <c r="DD14">
-        <v>1</v>
-      </c>
-      <c r="DF14">
-        <v>1</v>
-      </c>
-      <c r="DG14">
-        <v>1</v>
-      </c>
-      <c r="DH14">
+      <c r="CL14" t="s">
+        <v>379</v>
+      </c>
+      <c r="CN14" t="s">
+        <v>408</v>
+      </c>
+      <c r="CR14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="BO15" s="4"/>
-      <c r="BP15" s="4"/>
-      <c r="BQ15" s="4"/>
-      <c r="BR15" s="4"/>
-      <c r="BS15" s="4"/>
-      <c r="BV15"/>
-      <c r="BW15"/>
-      <c r="BX15"/>
-      <c r="BY15"/>
-      <c r="BZ15"/>
-      <c r="CA15"/>
+      <c r="A15" t="s">
+        <v>401</v>
+      </c>
+      <c r="C15" t="s">
+        <v>370</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>399</v>
+      </c>
+      <c r="BD15">
+        <v>1</v>
+      </c>
+      <c r="BS15">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="CB15" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="CC15" s="3"/>
+      <c r="CD15" s="3"/>
+      <c r="CE15" s="3"/>
+      <c r="CF15" s="3"/>
+      <c r="CG15" t="s">
+        <v>376</v>
+      </c>
+      <c r="CH15" s="3"/>
+      <c r="CI15" s="3"/>
+      <c r="CJ15" s="3"/>
+      <c r="CK15" s="3"/>
+      <c r="CL15" s="3"/>
+      <c r="DD15">
+        <v>1</v>
+      </c>
+      <c r="DF15">
+        <v>1</v>
+      </c>
+      <c r="DG15">
+        <v>1</v>
+      </c>
+      <c r="DH15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>412</v>
-      </c>
-      <c r="C16" t="s">
-        <v>370</v>
-      </c>
-      <c r="D16" t="s">
-        <v>413</v>
-      </c>
-      <c r="E16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F16" t="s">
-        <v>415</v>
-      </c>
-      <c r="G16">
-        <v>3</v>
-      </c>
-      <c r="J16" t="s">
-        <v>397</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16">
-        <v>1</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>399</v>
-      </c>
-      <c r="AZ16" s="3"/>
-      <c r="BD16">
-        <v>1</v>
-      </c>
-      <c r="BO16" t="s">
-        <v>417</v>
-      </c>
-      <c r="BP16" t="s">
-        <v>418</v>
-      </c>
-      <c r="BT16">
-        <v>20</v>
-      </c>
-      <c r="BV16" s="4">
-        <v>20</v>
-      </c>
-      <c r="BW16" s="4">
-        <v>30</v>
-      </c>
-      <c r="BX16" s="4">
-        <v>1</v>
-      </c>
-      <c r="BY16" s="4" t="s">
-        <v>398</v>
-      </c>
+      <c r="BO16" s="4"/>
+      <c r="BP16" s="4"/>
+      <c r="BQ16" s="4"/>
+      <c r="BR16" s="4"/>
+      <c r="BS16" s="4"/>
+      <c r="BV16"/>
+      <c r="BW16"/>
+      <c r="BX16"/>
+      <c r="BY16"/>
       <c r="BZ16"/>
       <c r="CA16"/>
-      <c r="CB16" s="3"/>
-      <c r="CC16" s="3"/>
-      <c r="CD16" s="3"/>
-      <c r="CE16" s="3"/>
-      <c r="CF16" s="3"/>
-      <c r="CK16" s="3"/>
-      <c r="CL16" s="3"/>
-      <c r="CN16" t="s">
-        <v>419</v>
-      </c>
-      <c r="CO16">
-        <v>70</v>
-      </c>
-      <c r="CR16">
-        <v>20</v>
-      </c>
-      <c r="DC16" t="s">
-        <v>420</v>
-      </c>
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="C17" t="s">
         <v>370</v>
       </c>
+      <c r="D17" t="s">
+        <v>411</v>
+      </c>
+      <c r="E17" t="s">
+        <v>412</v>
+      </c>
+      <c r="F17" t="s">
+        <v>413</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="J17" t="s">
+        <v>397</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>414</v>
+      </c>
       <c r="M17"/>
       <c r="N17"/>
-      <c r="O17" t="s">
-        <v>422</v>
-      </c>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17">
-        <v>2</v>
-      </c>
-      <c r="AD17">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="s">
-        <v>371</v>
-      </c>
-      <c r="AT17" t="s">
-        <v>372</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>373</v>
-      </c>
-      <c r="AZ17">
-        <v>0.75</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>399</v>
+      </c>
+      <c r="AZ17" s="3"/>
       <c r="BD17">
         <v>1</v>
       </c>
+      <c r="BO17" t="s">
+        <v>415</v>
+      </c>
       <c r="BP17" t="s">
-        <v>423</v>
-      </c>
-      <c r="BS17">
-        <v>0.5</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>424</v>
-      </c>
-      <c r="CE17" t="s">
-        <v>424</v>
-      </c>
-      <c r="CH17" t="s">
-        <v>377</v>
-      </c>
-      <c r="CI17" t="s">
-        <v>378</v>
-      </c>
-      <c r="CL17" t="s">
-        <v>379</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="BT17">
+        <v>20</v>
+      </c>
+      <c r="BV17" s="4">
+        <v>20</v>
+      </c>
+      <c r="BW17" s="4">
+        <v>30</v>
+      </c>
+      <c r="BX17" s="4">
+        <v>1</v>
+      </c>
+      <c r="BY17" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="BZ17"/>
+      <c r="CA17"/>
+      <c r="CB17" s="3"/>
+      <c r="CC17" s="3"/>
+      <c r="CD17" s="3"/>
+      <c r="CE17" s="3"/>
+      <c r="CF17" s="3"/>
+      <c r="CK17" s="3"/>
+      <c r="CL17" s="3"/>
       <c r="CN17" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="CO17">
-        <v>-0.04</v>
+        <v>70</v>
       </c>
       <c r="CR17">
-        <v>0.6</v>
-      </c>
-      <c r="CY17" t="s">
-        <v>381</v>
+        <v>20</v>
+      </c>
+      <c r="DC17" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C18" t="s">
         <v>370</v>
       </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>382</v>
-      </c>
       <c r="M18"/>
       <c r="N18"/>
+      <c r="O18" t="s">
+        <v>420</v>
+      </c>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18">
-        <v>1</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>399</v>
+        <v>2</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>371</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>372</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>373</v>
+      </c>
+      <c r="AZ18">
+        <v>0.75</v>
       </c>
       <c r="BD18">
         <v>1</v>
       </c>
-      <c r="BV18"/>
+      <c r="BP18" t="s">
+        <v>421</v>
+      </c>
+      <c r="BS18">
+        <v>0.5</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>422</v>
+      </c>
+      <c r="CE18" t="s">
+        <v>422</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>377</v>
+      </c>
+      <c r="CI18" t="s">
+        <v>378</v>
+      </c>
+      <c r="CL18" t="s">
+        <v>379</v>
+      </c>
       <c r="CN18" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="CO18">
-        <v>0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="CR18">
         <v>0.6</v>
       </c>
+      <c r="CY18" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C19" t="s">
         <v>370</v>
@@ -7920,42 +7977,33 @@
       </c>
       <c r="M19"/>
       <c r="N19"/>
-      <c r="Q19" s="3" t="s">
-        <v>428</v>
-      </c>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19">
-        <v>2</v>
-      </c>
-      <c r="AD19">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="s">
-        <v>371</v>
-      </c>
-      <c r="AW19">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>399</v>
       </c>
       <c r="BD19">
         <v>1</v>
       </c>
       <c r="BV19"/>
       <c r="CN19" t="s">
-        <v>374</v>
+        <v>424</v>
+      </c>
+      <c r="CO19">
+        <v>0.2</v>
       </c>
       <c r="CR19">
-        <v>9999</v>
-      </c>
-      <c r="CS19">
         <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C20" t="s">
         <v>370</v>
@@ -7968,60 +8016,42 @@
       </c>
       <c r="M20"/>
       <c r="N20"/>
+      <c r="Q20" s="3" t="s">
+        <v>426</v>
+      </c>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20">
-        <v>1</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>399</v>
-      </c>
-      <c r="AZ20" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="AD20">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>371</v>
+      </c>
+      <c r="AW20">
+        <v>1</v>
+      </c>
       <c r="BD20">
         <v>1</v>
       </c>
-      <c r="BS20">
-        <v>0.16700000000000001</v>
-      </c>
-      <c r="CB20" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="CC20" s="3"/>
-      <c r="CD20" s="3"/>
-      <c r="CE20" s="3"/>
-      <c r="CF20" s="3"/>
-      <c r="CG20" t="s">
-        <v>376</v>
-      </c>
-      <c r="CH20" s="3"/>
-      <c r="CI20" s="3"/>
-      <c r="CJ20" s="3"/>
-      <c r="CK20" s="3"/>
-      <c r="CL20" s="3"/>
+      <c r="BV20"/>
       <c r="CN20" t="s">
-        <v>430</v>
+        <v>374</v>
       </c>
       <c r="CR20">
-        <v>19.7</v>
-      </c>
-      <c r="DD20">
-        <v>1</v>
-      </c>
-      <c r="DF20">
-        <v>1</v>
-      </c>
-      <c r="DG20">
-        <v>1</v>
-      </c>
-      <c r="DH20">
-        <v>1</v>
+        <v>9999</v>
+      </c>
+      <c r="CS20">
+        <v>0.6</v>
       </c>
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="C21" t="s">
         <v>370</v>
@@ -8029,14 +8059,11 @@
       <c r="I21">
         <v>1</v>
       </c>
+      <c r="K21" s="3" t="s">
+        <v>382</v>
+      </c>
       <c r="M21"/>
       <c r="N21"/>
-      <c r="O21" t="s">
-        <v>422</v>
-      </c>
-      <c r="P21" t="s">
-        <v>430</v>
-      </c>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
@@ -8052,10 +8079,10 @@
         <v>1</v>
       </c>
       <c r="BS21">
-        <v>0.26700000000000002</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="CB21" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="CC21" s="3"/>
       <c r="CD21" s="3"/>
@@ -8069,6 +8096,12 @@
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
+      <c r="CN21" t="s">
+        <v>428</v>
+      </c>
+      <c r="CR21">
+        <v>19.7</v>
+      </c>
       <c r="DD21">
         <v>1</v>
       </c>
@@ -8083,194 +8116,183 @@
       </c>
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="V22"/>
-      <c r="W22"/>
-      <c r="X22"/>
-      <c r="BS22" s="4"/>
-      <c r="BT22" s="4"/>
-      <c r="BU22" s="4"/>
-      <c r="BY22"/>
-      <c r="BZ22"/>
-      <c r="CA22"/>
+      <c r="A22" t="s">
+        <v>429</v>
+      </c>
+      <c r="C22" t="s">
+        <v>370</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22" t="s">
+        <v>420</v>
+      </c>
+      <c r="P22" t="s">
+        <v>428</v>
+      </c>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>399</v>
+      </c>
+      <c r="AZ22" s="3"/>
+      <c r="BD22">
+        <v>1</v>
+      </c>
+      <c r="BS22">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="CB22" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="CC22" s="3"/>
+      <c r="CD22" s="3"/>
+      <c r="CE22" s="3"/>
+      <c r="CF22" s="3"/>
+      <c r="CG22" t="s">
+        <v>376</v>
+      </c>
+      <c r="CH22" s="3"/>
+      <c r="CI22" s="3"/>
+      <c r="CJ22" s="3"/>
+      <c r="CK22" s="3"/>
+      <c r="CL22" s="3"/>
+      <c r="DD22">
+        <v>1</v>
+      </c>
+      <c r="DF22">
+        <v>1</v>
+      </c>
+      <c r="DG22">
+        <v>1</v>
+      </c>
+      <c r="DH22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>433</v>
-      </c>
-      <c r="C23" t="s">
-        <v>370</v>
-      </c>
-      <c r="D23" t="s">
-        <v>434</v>
-      </c>
-      <c r="E23" t="s">
-        <v>435</v>
-      </c>
-      <c r="F23" t="s">
-        <v>436</v>
-      </c>
-      <c r="G23">
-        <v>3</v>
-      </c>
-      <c r="J23" t="s">
-        <v>397</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="M23"/>
-      <c r="N23"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="3"/>
-      <c r="AB23" s="3"/>
-      <c r="AC23">
-        <v>1</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>399</v>
-      </c>
-      <c r="AT23" t="s">
-        <v>437</v>
-      </c>
-      <c r="BD23">
-        <v>1</v>
-      </c>
-      <c r="BO23" t="s">
-        <v>438</v>
-      </c>
-      <c r="BP23" t="s">
-        <v>439</v>
-      </c>
-      <c r="BT23">
-        <v>30</v>
-      </c>
-      <c r="BV23" s="4">
-        <v>30</v>
-      </c>
-      <c r="BW23" s="4">
-        <v>45</v>
-      </c>
-      <c r="BX23" s="4">
-        <v>1</v>
-      </c>
-      <c r="BY23" s="4" t="s">
-        <v>398</v>
-      </c>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="BS23" s="4"/>
+      <c r="BT23" s="4"/>
+      <c r="BU23" s="4"/>
+      <c r="BY23"/>
       <c r="BZ23"/>
       <c r="CA23"/>
-      <c r="CB23" s="3"/>
-      <c r="CC23" s="3"/>
-      <c r="CD23" s="3"/>
-      <c r="CE23" s="3"/>
-      <c r="CF23" s="3"/>
-      <c r="CK23" s="3"/>
-      <c r="CL23" s="3"/>
-      <c r="CN23" t="s">
-        <v>440</v>
-      </c>
-      <c r="CO23">
-        <v>3</v>
-      </c>
-      <c r="CR23">
-        <v>30</v>
-      </c>
-      <c r="CU23" t="s">
-        <v>404</v>
-      </c>
-      <c r="DB23" t="s">
-        <v>441</v>
-      </c>
-      <c r="DC23" t="s">
-        <v>442</v>
-      </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C24" t="s">
         <v>370</v>
       </c>
+      <c r="D24" t="s">
+        <v>432</v>
+      </c>
+      <c r="E24" t="s">
+        <v>433</v>
+      </c>
+      <c r="F24" t="s">
+        <v>434</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="J24" t="s">
+        <v>397</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>414</v>
+      </c>
       <c r="M24"/>
       <c r="N24"/>
-      <c r="O24" t="s">
-        <v>444</v>
-      </c>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24">
-        <v>2</v>
-      </c>
-      <c r="AD24">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="s">
-        <v>371</v>
+        <v>1</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>399</v>
       </c>
       <c r="AT24" t="s">
+        <v>435</v>
+      </c>
+      <c r="BD24">
+        <v>1</v>
+      </c>
+      <c r="BO24" t="s">
+        <v>436</v>
+      </c>
+      <c r="BP24" t="s">
         <v>437</v>
       </c>
-      <c r="AX24" t="s">
-        <v>373</v>
-      </c>
-      <c r="AZ24">
-        <v>1</v>
-      </c>
-      <c r="BD24">
-        <v>4</v>
-      </c>
-      <c r="BP24" t="s">
-        <v>445</v>
-      </c>
-      <c r="CB24" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="CG24" t="s">
-        <v>376</v>
-      </c>
-      <c r="CH24" t="s">
-        <v>377</v>
-      </c>
-      <c r="CI24" t="s">
-        <v>378</v>
-      </c>
-      <c r="CL24" t="s">
-        <v>379</v>
-      </c>
+      <c r="BT24">
+        <v>30</v>
+      </c>
+      <c r="BV24" s="4">
+        <v>30</v>
+      </c>
+      <c r="BW24" s="4">
+        <v>45</v>
+      </c>
+      <c r="BX24" s="4">
+        <v>1</v>
+      </c>
+      <c r="BY24" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="BZ24"/>
+      <c r="CA24"/>
+      <c r="CB24" s="3"/>
+      <c r="CC24" s="3"/>
+      <c r="CD24" s="3"/>
+      <c r="CE24" s="3"/>
+      <c r="CF24" s="3"/>
+      <c r="CK24" s="3"/>
+      <c r="CL24" s="3"/>
       <c r="CN24" t="s">
-        <v>380</v>
+        <v>438</v>
       </c>
       <c r="CO24">
-        <v>-10</v>
-      </c>
-      <c r="CP24">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="CR24">
-        <v>5</v>
-      </c>
-      <c r="CY24" t="s">
-        <v>447</v>
+        <v>30</v>
+      </c>
+      <c r="CU24" t="s">
+        <v>403</v>
+      </c>
+      <c r="DB24" t="s">
+        <v>439</v>
+      </c>
+      <c r="DC24" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C25" t="s">
         <v>370</v>
       </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>382</v>
-      </c>
       <c r="M25"/>
       <c r="N25"/>
+      <c r="O25" t="s">
+        <v>442</v>
+      </c>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
@@ -8282,28 +8304,57 @@
         <v>1</v>
       </c>
       <c r="AO25" t="s">
-        <v>383</v>
-      </c>
-      <c r="AW25">
+        <v>371</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>435</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>373</v>
+      </c>
+      <c r="AZ25">
         <v>1</v>
       </c>
       <c r="BD25">
         <v>4</v>
       </c>
-      <c r="BV25"/>
+      <c r="BP25" t="s">
+        <v>443</v>
+      </c>
+      <c r="CB25" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="CG25" t="s">
+        <v>376</v>
+      </c>
+      <c r="CH25" t="s">
+        <v>377</v>
+      </c>
+      <c r="CI25" t="s">
+        <v>378</v>
+      </c>
+      <c r="CL25" t="s">
+        <v>379</v>
+      </c>
       <c r="CN25" t="s">
-        <v>374</v>
+        <v>380</v>
+      </c>
+      <c r="CO25">
+        <v>-10</v>
+      </c>
+      <c r="CP25">
+        <v>0.1</v>
       </c>
       <c r="CR25">
-        <v>9999</v>
-      </c>
-      <c r="CS25">
-        <v>0.6</v>
+        <v>5</v>
+      </c>
+      <c r="CY25" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C26" t="s">
         <v>370</v>
@@ -8321,48 +8372,34 @@
       <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26">
-        <v>1</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>399</v>
+        <v>2</v>
+      </c>
+      <c r="AD26">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>383</v>
+      </c>
+      <c r="AW26">
+        <v>1</v>
       </c>
       <c r="BD26">
-        <v>1</v>
-      </c>
-      <c r="BS26">
-        <v>0.16700000000000001</v>
-      </c>
-      <c r="CB26" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="CC26" s="3"/>
-      <c r="CD26" s="3"/>
-      <c r="CE26" s="3"/>
-      <c r="CF26" s="3"/>
-      <c r="CG26" t="s">
-        <v>376</v>
-      </c>
-      <c r="CH26" s="3"/>
-      <c r="CI26" s="3"/>
-      <c r="CJ26" s="3"/>
-      <c r="CK26" s="3"/>
-      <c r="CL26" s="3"/>
-      <c r="DD26">
-        <v>1</v>
-      </c>
-      <c r="DF26">
-        <v>1</v>
-      </c>
-      <c r="DG26">
-        <v>1</v>
-      </c>
-      <c r="DH26">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="BV26"/>
+      <c r="CN26" t="s">
+        <v>374</v>
+      </c>
+      <c r="CR26">
+        <v>9999</v>
+      </c>
+      <c r="CS26">
+        <v>0.6</v>
       </c>
     </row>
     <row r="27" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C27" t="s">
         <v>370</v>
@@ -8373,13 +8410,8 @@
       <c r="K27" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>450</v>
-      </c>
       <c r="M27"/>
       <c r="N27"/>
-      <c r="O27"/>
-      <c r="P27"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
@@ -8394,10 +8426,10 @@
         <v>1</v>
       </c>
       <c r="BS27">
-        <v>0.5</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="CB27" s="3" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="CC27" s="3"/>
       <c r="CD27" s="3"/>
@@ -8425,133 +8457,193 @@
       </c>
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>447</v>
+      </c>
+      <c r="C28" t="s">
+        <v>370</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>399</v>
+      </c>
+      <c r="BD28">
+        <v>1</v>
+      </c>
+      <c r="BS28">
+        <v>0.5</v>
+      </c>
+      <c r="CB28" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="CC28" s="3"/>
+      <c r="CD28" s="3"/>
+      <c r="CE28" s="3"/>
+      <c r="CF28" s="3"/>
+      <c r="CG28" t="s">
+        <v>376</v>
+      </c>
+      <c r="CH28" s="3"/>
+      <c r="CI28" s="3"/>
+      <c r="CJ28" s="3"/>
+      <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
+      <c r="DD28">
+        <v>1</v>
+      </c>
+      <c r="DF28">
+        <v>1</v>
+      </c>
+      <c r="DG28">
+        <v>1</v>
+      </c>
+      <c r="DH28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="BV29"/>
+      <c r="CL29" s="3"/>
     </row>
     <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="BV30"/>
-      <c r="CL30" s="3"/>
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="BV31"/>
       <c r="CL31" s="3"/>
     </row>
-    <row r="33" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV33"/>
+    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="CL32" s="3"/>
     </row>
     <row r="34" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV34"/>
-      <c r="CL34" s="3"/>
     </row>
     <row r="35" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV35"/>
       <c r="CL35" s="3"/>
     </row>
-    <row r="37" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV37"/>
+    <row r="36" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL36" s="3"/>
     </row>
     <row r="38" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL38" s="3"/>
-    </row>
-    <row r="41" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL41" s="3"/>
-    </row>
-    <row r="45" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL45" s="3"/>
-    </row>
-    <row r="47" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV47"/>
+      <c r="BV38"/>
+    </row>
+    <row r="39" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL39" s="3"/>
+    </row>
+    <row r="42" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL42" s="3"/>
+    </row>
+    <row r="46" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL46" s="3"/>
     </row>
     <row r="48" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL48" s="3"/>
-    </row>
-    <row r="55" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV55"/>
+      <c r="BV48"/>
+    </row>
+    <row r="49" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL49" s="3"/>
     </row>
     <row r="56" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL56" s="3"/>
+      <c r="BV56"/>
     </row>
     <row r="57" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL57" s="3"/>
     </row>
-    <row r="59" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV59"/>
+    <row r="58" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL58" s="3"/>
     </row>
     <row r="60" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV60"/>
-      <c r="CL60" s="3"/>
     </row>
     <row r="61" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV61"/>
       <c r="CL61" s="3"/>
     </row>
-    <row r="67" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV67"/>
+    <row r="62" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL62" s="3"/>
     </row>
     <row r="68" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV68"/>
-      <c r="CL68" s="3"/>
     </row>
     <row r="69" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV69"/>
       <c r="CL69" s="3"/>
     </row>
     <row r="70" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV70"/>
       <c r="CL70" s="3"/>
     </row>
-    <row r="75" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV75"/>
+    <row r="71" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL71" s="3"/>
     </row>
     <row r="76" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV76"/>
     </row>
-    <row r="80" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV80"/>
+    <row r="77" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV77"/>
     </row>
     <row r="81" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL81" s="3"/>
+      <c r="BV81"/>
     </row>
     <row r="82" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV82"/>
+      <c r="CL82" s="3"/>
     </row>
     <row r="83" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL83" s="3"/>
-    </row>
-    <row r="93" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV93"/>
+      <c r="BV83"/>
+    </row>
+    <row r="84" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL84" s="3"/>
     </row>
     <row r="94" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL94" s="3"/>
-    </row>
-    <row r="96" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV96"/>
+      <c r="BV94"/>
+    </row>
+    <row r="95" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL95" s="3"/>
     </row>
     <row r="97" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL97" s="3"/>
-    </row>
-    <row r="105" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV105"/>
+      <c r="BV97"/>
+    </row>
+    <row r="98" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL98" s="3"/>
     </row>
     <row r="106" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL106" s="3"/>
-    </row>
-    <row r="110" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV110"/>
+      <c r="BV106"/>
+    </row>
+    <row r="107" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL107" s="3"/>
     </row>
     <row r="111" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL111" s="3"/>
-    </row>
-    <row r="113" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV113"/>
+      <c r="BV111"/>
+    </row>
+    <row r="112" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL112" s="3"/>
     </row>
     <row r="114" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL114" s="3"/>
-    </row>
-    <row r="130" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV130"/>
+      <c r="BV114"/>
+    </row>
+    <row r="115" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL115" s="3"/>
     </row>
     <row r="131" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV131"/>
-      <c r="CL131" s="3"/>
     </row>
     <row r="132" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV132"/>
@@ -8563,49 +8655,50 @@
     </row>
     <row r="134" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV134"/>
-    </row>
-    <row r="136" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV136"/>
+      <c r="CL134" s="3"/>
+    </row>
+    <row r="135" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV135"/>
     </row>
     <row r="137" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV137"/>
-      <c r="CL137" s="3"/>
     </row>
     <row r="138" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV138"/>
       <c r="CL138" s="3"/>
     </row>
     <row r="139" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV139"/>
       <c r="CL139" s="3"/>
     </row>
-    <row r="143" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV143"/>
+    <row r="140" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL140" s="3"/>
     </row>
     <row r="144" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL144" s="3"/>
-    </row>
-    <row r="146" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV146"/>
+      <c r="BV144"/>
+    </row>
+    <row r="145" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL145" s="3"/>
     </row>
     <row r="147" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV147"/>
-      <c r="CL147" s="3"/>
     </row>
     <row r="148" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV148"/>
       <c r="CL148" s="3"/>
     </row>
     <row r="149" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV149"/>
       <c r="CL149" s="3"/>
     </row>
-    <row r="165" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV165"/>
+    <row r="150" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL150" s="3"/>
     </row>
     <row r="166" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL166" s="3"/>
-    </row>
-    <row r="174" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL174" s="3"/>
+      <c r="BV166"/>
+    </row>
+    <row r="167" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL167" s="3"/>
     </row>
     <row r="175" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL175" s="3"/>
@@ -8619,47 +8712,47 @@
     <row r="178" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL178" s="3"/>
     </row>
-    <row r="180" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV180"/>
+    <row r="179" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL179" s="3"/>
     </row>
     <row r="181" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL181" s="3"/>
+      <c r="BV181"/>
     </row>
     <row r="182" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV182"/>
+      <c r="CL182" s="3"/>
     </row>
     <row r="183" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV183"/>
-      <c r="CL183" s="3"/>
     </row>
     <row r="184" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV184"/>
       <c r="CL184" s="3"/>
     </row>
-    <row r="186" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV186"/>
+    <row r="185" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL185" s="3"/>
     </row>
     <row r="187" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV187"/>
-      <c r="CL187" s="3"/>
     </row>
     <row r="188" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV188"/>
       <c r="CL188" s="3"/>
     </row>
     <row r="189" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV189"/>
       <c r="CL189" s="3"/>
     </row>
-    <row r="191" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL191" s="3"/>
-    </row>
-    <row r="193" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL193" s="3"/>
-    </row>
-    <row r="195" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL195" s="3"/>
-    </row>
-    <row r="198" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL198" s="3"/>
+    <row r="190" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL190" s="3"/>
+    </row>
+    <row r="192" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL192" s="3"/>
+    </row>
+    <row r="194" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL194" s="3"/>
+    </row>
+    <row r="196" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL196" s="3"/>
     </row>
     <row r="199" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL199" s="3"/>
@@ -8677,17 +8770,17 @@
       <c r="CL203" s="3"/>
     </row>
     <row r="204" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV204"/>
+      <c r="CL204" s="3"/>
     </row>
     <row r="205" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV205"/>
-      <c r="CL205" s="3"/>
     </row>
     <row r="206" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV206"/>
       <c r="CL206" s="3"/>
     </row>
     <row r="207" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV207"/>
       <c r="CL207" s="3"/>
     </row>
     <row r="208" spans="74:90" x14ac:dyDescent="0.25">
@@ -8699,37 +8792,36 @@
     <row r="210" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL210" s="3"/>
     </row>
-    <row r="212" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL212" s="3"/>
+    <row r="211" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL211" s="3"/>
     </row>
     <row r="213" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL213" s="3"/>
     </row>
     <row r="214" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV214"/>
+      <c r="CL214" s="3"/>
     </row>
     <row r="215" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV215"/>
-      <c r="CL215" s="3"/>
     </row>
     <row r="216" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV216"/>
       <c r="CL216" s="3"/>
     </row>
     <row r="217" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV217"/>
       <c r="CL217" s="3"/>
     </row>
     <row r="218" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL218" s="3"/>
     </row>
-    <row r="220" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL220" s="3"/>
+    <row r="219" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL219" s="3"/>
     </row>
     <row r="221" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL221" s="3"/>
     </row>
     <row r="222" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV222"/>
       <c r="CL222" s="3"/>
     </row>
     <row r="223" spans="74:90" x14ac:dyDescent="0.25">
@@ -8737,6 +8829,7 @@
       <c r="CL223" s="3"/>
     </row>
     <row r="224" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV224"/>
       <c r="CL224" s="3"/>
     </row>
     <row r="225" spans="74:90" x14ac:dyDescent="0.25">
@@ -8745,70 +8838,70 @@
     <row r="226" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL226" s="3"/>
     </row>
-    <row r="228" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV228"/>
-      <c r="CL228" s="3"/>
+    <row r="227" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL227" s="3"/>
     </row>
     <row r="229" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV229"/>
       <c r="CL229" s="3"/>
     </row>
     <row r="230" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL230" s="3"/>
     </row>
-    <row r="232" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV232"/>
-      <c r="CL232" s="3"/>
+    <row r="231" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL231" s="3"/>
     </row>
     <row r="233" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV233"/>
       <c r="CL233" s="3"/>
     </row>
     <row r="234" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV234"/>
       <c r="CL234" s="3"/>
     </row>
-    <row r="236" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL236" s="3"/>
-    </row>
-    <row r="238" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL238" s="3"/>
-    </row>
-    <row r="241" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL241" s="3"/>
+    <row r="235" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL235" s="3"/>
+    </row>
+    <row r="237" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL237" s="3"/>
+    </row>
+    <row r="239" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL239" s="3"/>
     </row>
     <row r="242" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL242" s="3"/>
     </row>
-    <row r="246" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV246"/>
+    <row r="243" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL243" s="3"/>
     </row>
     <row r="247" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV247"/>
-      <c r="CL247" s="3"/>
     </row>
     <row r="248" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV248"/>
       <c r="CL248" s="3"/>
     </row>
     <row r="249" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV249"/>
       <c r="CL249" s="3"/>
     </row>
     <row r="250" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL250" s="3"/>
     </row>
     <row r="251" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV251"/>
+      <c r="CL251" s="3"/>
     </row>
     <row r="252" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL252" s="3"/>
-    </row>
-    <row r="254" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL254" s="3"/>
+      <c r="BV252"/>
+    </row>
+    <row r="253" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL253" s="3"/>
     </row>
     <row r="255" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL255" s="3"/>
     </row>
-    <row r="257" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL257" s="3"/>
+    <row r="256" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL256" s="3"/>
     </row>
     <row r="258" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL258" s="3"/>
@@ -8828,75 +8921,74 @@
     <row r="263" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL263" s="3"/>
     </row>
-    <row r="265" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV265"/>
+    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL264" s="3"/>
     </row>
     <row r="266" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL266" s="3"/>
+      <c r="BV266"/>
     </row>
     <row r="267" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL267" s="3"/>
     </row>
-    <row r="300" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU300" s="7"/>
-      <c r="BV300" s="8"/>
+    <row r="268" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL268" s="3"/>
     </row>
     <row r="301" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H301" s="7"/>
-      <c r="CL301" s="7"/>
-    </row>
-    <row r="307" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV307"/>
+      <c r="BU301" s="7"/>
+      <c r="BV301" s="8"/>
+    </row>
+    <row r="302" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H302" s="7"/>
+      <c r="CL302" s="7"/>
     </row>
     <row r="308" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV308"/>
-      <c r="CL308" s="3"/>
     </row>
     <row r="309" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV309"/>
       <c r="CL309" s="3"/>
     </row>
     <row r="310" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV310"/>
       <c r="CL310" s="3"/>
     </row>
-    <row r="327" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV327"/>
+    <row r="311" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL311" s="3"/>
     </row>
     <row r="328" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL328" s="3"/>
-    </row>
-    <row r="360" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV360"/>
+      <c r="BV328"/>
+    </row>
+    <row r="329" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL329" s="3"/>
     </row>
     <row r="361" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV361"/>
-      <c r="CL361" s="3"/>
     </row>
     <row r="362" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV362"/>
       <c r="CL362" s="3"/>
     </row>
-    <row r="378" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV378"/>
+    <row r="363" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL363" s="3"/>
     </row>
     <row r="379" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL379" s="3"/>
-    </row>
-    <row r="385" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV385"/>
+      <c r="BV379"/>
+    </row>
+    <row r="380" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL380" s="3"/>
     </row>
     <row r="386" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV386"/>
-      <c r="CL386" s="3"/>
     </row>
     <row r="387" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV387"/>
       <c r="CL387" s="3"/>
     </row>
-    <row r="392" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV392"/>
+    <row r="388" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL388" s="3"/>
     </row>
     <row r="393" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV393"/>
-      <c r="CL393" s="3"/>
     </row>
     <row r="394" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV394"/>
@@ -8955,40 +9047,40 @@
       <c r="CL407" s="3"/>
     </row>
     <row r="408" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV408"/>
       <c r="CL408" s="3"/>
     </row>
-    <row r="412" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV412"/>
+    <row r="409" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL409" s="3"/>
     </row>
     <row r="413" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV413"/>
-      <c r="CL413" s="3"/>
     </row>
     <row r="414" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV414"/>
       <c r="CL414" s="3"/>
     </row>
     <row r="415" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV415"/>
+      <c r="CL415" s="3"/>
     </row>
     <row r="416" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL416" s="3"/>
-    </row>
-    <row r="419" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV419"/>
+      <c r="BV416"/>
+    </row>
+    <row r="417" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL417" s="3"/>
     </row>
     <row r="420" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV420"/>
-      <c r="CL420" s="3"/>
     </row>
     <row r="421" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV421"/>
       <c r="CL421" s="3"/>
     </row>
-    <row r="452" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV452"/>
+    <row r="422" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL422" s="3"/>
     </row>
     <row r="453" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV453"/>
-      <c r="CL453" s="3"/>
     </row>
     <row r="454" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV454"/>
@@ -9015,26 +9107,26 @@
       <c r="CL459" s="3"/>
     </row>
     <row r="460" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV460"/>
       <c r="CL460" s="3"/>
     </row>
-    <row r="462" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV462"/>
+    <row r="461" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL461" s="3"/>
     </row>
     <row r="463" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL463" s="3"/>
-    </row>
-    <row r="467" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV467"/>
+      <c r="BV463"/>
+    </row>
+    <row r="464" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL464" s="3"/>
     </row>
     <row r="468" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL468" s="3"/>
-    </row>
-    <row r="471" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV471"/>
+      <c r="BV468"/>
+    </row>
+    <row r="469" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL469" s="3"/>
     </row>
     <row r="472" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV472"/>
-      <c r="CL472" s="3"/>
     </row>
     <row r="473" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV473"/>
@@ -9045,20 +9137,20 @@
       <c r="CL474" s="3"/>
     </row>
     <row r="475" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV475"/>
       <c r="CL475" s="3"/>
     </row>
-    <row r="482" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV482"/>
+    <row r="476" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL476" s="3"/>
     </row>
     <row r="483" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL483" s="3"/>
-    </row>
-    <row r="486" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV486"/>
+      <c r="BV483"/>
+    </row>
+    <row r="484" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL484" s="3"/>
     </row>
     <row r="487" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV487"/>
-      <c r="CL487" s="3"/>
     </row>
     <row r="488" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV488"/>
@@ -9069,74 +9161,74 @@
       <c r="CL489" s="3"/>
     </row>
     <row r="490" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV490"/>
       <c r="CL490" s="3"/>
     </row>
-    <row r="492" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV492"/>
+    <row r="491" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL491" s="3"/>
     </row>
     <row r="493" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV493"/>
-      <c r="CL493" s="3"/>
     </row>
     <row r="494" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV494"/>
       <c r="CL494" s="3"/>
     </row>
     <row r="495" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL495">
+      <c r="CL495" s="3"/>
+    </row>
+    <row r="496" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL496">
         <v>0.15</v>
-      </c>
-    </row>
-    <row r="497" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL497">
-        <v>0.2</v>
       </c>
     </row>
     <row r="498" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL498">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="499" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL499">
         <v>0.1</v>
       </c>
     </row>
-    <row r="500" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL500">
+    <row r="501" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL501">
         <v>0.2</v>
       </c>
     </row>
-    <row r="507" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL507">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="509" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL509">
-        <v>0.4</v>
+    <row r="508" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL508">
+        <v>1</v>
       </c>
     </row>
     <row r="510" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL510">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="511" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL511">
         <v>0.6</v>
-      </c>
-    </row>
-    <row r="513" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL513">
-        <v>0.5</v>
       </c>
     </row>
     <row r="514" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL514">
-        <v>0.66700000000000004</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="515" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL515">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="516" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL516">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="518" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV518"/>
     </row>
     <row r="519" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV519"/>
-      <c r="CL519" s="3"/>
     </row>
     <row r="520" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV520"/>
@@ -9167,20 +9259,20 @@
       <c r="CL526" s="3"/>
     </row>
     <row r="527" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV527"/>
       <c r="CL527" s="3"/>
     </row>
     <row r="528" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV528"/>
+      <c r="CL528" s="3"/>
     </row>
     <row r="529" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL529" s="3"/>
-    </row>
-    <row r="538" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV538"/>
+      <c r="BV529"/>
+    </row>
+    <row r="530" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL530" s="3"/>
     </row>
     <row r="539" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV539"/>
-      <c r="CL539" s="3"/>
     </row>
     <row r="540" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV540"/>
@@ -9207,40 +9299,40 @@
       <c r="CL545" s="3"/>
     </row>
     <row r="546" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV546"/>
       <c r="CL546" s="3"/>
     </row>
     <row r="547" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV547"/>
+      <c r="CL547" s="3"/>
     </row>
     <row r="548" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL548" s="3"/>
-    </row>
-    <row r="553" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV553"/>
+      <c r="BV548"/>
+    </row>
+    <row r="549" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL549" s="3"/>
     </row>
     <row r="554" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV554"/>
-      <c r="CL554" s="3"/>
     </row>
     <row r="555" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV555"/>
       <c r="CL555" s="3"/>
     </row>
     <row r="556" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV556"/>
+      <c r="CL556" s="3"/>
     </row>
     <row r="557" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV557"/>
-      <c r="CL557" s="3"/>
     </row>
     <row r="558" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV558"/>
       <c r="CL558" s="3"/>
     </row>
     <row r="559" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV559"/>
+      <c r="CL559" s="3"/>
     </row>
     <row r="560" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV560"/>
-      <c r="CL560" s="3"/>
     </row>
     <row r="561" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV561"/>
@@ -9251,42 +9343,42 @@
       <c r="CL562" s="3"/>
     </row>
     <row r="563" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV563"/>
       <c r="CL563" s="3"/>
     </row>
-    <row r="567" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV567"/>
+    <row r="564" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL564" s="3"/>
     </row>
     <row r="568" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV568"/>
-      <c r="CL568" s="3"/>
     </row>
     <row r="569" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV569"/>
       <c r="CL569" s="3"/>
     </row>
     <row r="570" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV570"/>
       <c r="CL570" s="3"/>
     </row>
     <row r="571" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV571"/>
+      <c r="CL571" s="3"/>
     </row>
     <row r="572" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="CL572" s="3"/>
+      <c r="BV572"/>
     </row>
     <row r="573" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU573" s="7"/>
-      <c r="BV573" s="8"/>
+      <c r="CL573" s="3"/>
     </row>
     <row r="574" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H574" s="7"/>
-      <c r="CL574" s="7"/>
-    </row>
-    <row r="591" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV591"/>
-    </row>
-    <row r="592" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BU574" s="7"/>
+      <c r="BV574" s="8"/>
+    </row>
+    <row r="575" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H575" s="7"/>
+      <c r="CL575" s="7"/>
+    </row>
+    <row r="592" spans="74:74" x14ac:dyDescent="0.25">
       <c r="BV592"/>
-      <c r="CL592" s="3"/>
     </row>
     <row r="593" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV593"/>
@@ -9297,30 +9389,30 @@
       <c r="CL594" s="3"/>
     </row>
     <row r="595" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV595"/>
       <c r="CL595" s="3"/>
     </row>
     <row r="596" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV596"/>
+      <c r="CL596" s="3"/>
     </row>
     <row r="597" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV597"/>
-      <c r="CL597" s="3"/>
     </row>
     <row r="598" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU598" s="7"/>
-      <c r="BV598" s="8"/>
+      <c r="BV598"/>
       <c r="CL598" s="3"/>
     </row>
     <row r="599" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H599" s="7"/>
-      <c r="CL599" s="7"/>
-    </row>
-    <row r="602" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV602"/>
+      <c r="BU599" s="7"/>
+      <c r="BV599" s="8"/>
+      <c r="CL599" s="3"/>
+    </row>
+    <row r="600" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H600" s="7"/>
+      <c r="CL600" s="7"/>
     </row>
     <row r="603" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV603"/>
-      <c r="CL603" s="3"/>
     </row>
     <row r="604" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV604"/>
@@ -9347,14 +9439,14 @@
       <c r="CL609" s="3"/>
     </row>
     <row r="610" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV610"/>
       <c r="CL610" s="3"/>
     </row>
-    <row r="612" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV612"/>
+    <row r="611" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL611" s="3"/>
     </row>
     <row r="613" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV613"/>
-      <c r="CL613" s="3"/>
     </row>
     <row r="614" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV614"/>
@@ -9373,14 +9465,14 @@
       <c r="CL617" s="3"/>
     </row>
     <row r="618" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV618"/>
       <c r="CL618" s="3"/>
     </row>
     <row r="619" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV619"/>
+      <c r="CL619" s="3"/>
     </row>
     <row r="620" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV620"/>
-      <c r="CL620" s="3"/>
     </row>
     <row r="621" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV621"/>
@@ -9495,21 +9587,25 @@
       <c r="CL648" s="3"/>
     </row>
     <row r="649" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV649"/>
       <c r="CL649" s="3"/>
     </row>
     <row r="650" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV650"/>
+      <c r="CL650" s="3"/>
     </row>
     <row r="651" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV651"/>
-      <c r="CL651" s="3"/>
     </row>
     <row r="652" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV652"/>
       <c r="CL652" s="3"/>
     </row>
     <row r="653" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV653"/>
       <c r="CL653" s="3"/>
+    </row>
+    <row r="654" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL654" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -9543,37 +9639,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>450</v>
+      </c>
+      <c r="F1" t="s">
+        <v>451</v>
+      </c>
+      <c r="G1" t="s">
         <v>452</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>453</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>454</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>455</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>456</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>457</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>458</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>459</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>460</v>
-      </c>
-      <c r="O1" t="s">
-        <v>461</v>
-      </c>
-      <c r="P1" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -9587,40 +9683,40 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
+        <v>461</v>
+      </c>
+      <c r="F2" t="s">
+        <v>462</v>
+      </c>
+      <c r="G2" t="s">
         <v>463</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>464</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>465</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>466</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>467</v>
-      </c>
-      <c r="J2" t="s">
-        <v>468</v>
-      </c>
-      <c r="K2" t="s">
-        <v>469</v>
       </c>
       <c r="L2" t="s">
         <v>53</v>
       </c>
       <c r="M2" t="s">
+        <v>468</v>
+      </c>
+      <c r="N2" t="s">
+        <v>469</v>
+      </c>
+      <c r="O2" t="s">
         <v>470</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>471</v>
-      </c>
-      <c r="O2" t="s">
-        <v>472</v>
-      </c>
-      <c r="P2" t="s">
-        <v>473</v>
       </c>
       <c r="Q2" t="s">
         <v>336</v>
@@ -9681,7 +9777,7 @@
         <v>374</v>
       </c>
       <c r="C4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -9689,38 +9785,38 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C5" t="s">
+        <v>474</v>
+      </c>
+      <c r="J5" t="s">
         <v>475</v>
       </c>
-      <c r="C5" t="s">
+      <c r="Q5" t="s">
         <v>476</v>
-      </c>
-      <c r="J5" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C8" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Q8" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C9" t="s">
         <v>218</v>
@@ -9729,29 +9825,29 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C10" t="s">
+        <v>474</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q10" t="s">
         <v>476</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
         <v>218</v>
@@ -9760,18 +9856,18 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Q11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C12" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -9779,38 +9875,38 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C13" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K13">
         <v>0.3</v>
       </c>
       <c r="Q13" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C14" t="s">
+        <v>486</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="s">
         <v>488</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C15" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -9818,24 +9914,24 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C16" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="Q16" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C17" t="s">
         <v>218</v>
@@ -9844,12 +9940,12 @@
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="Q19" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="276" spans="16:16" x14ac:dyDescent="0.25">
@@ -9884,7 +9980,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9895,7 +9991,7 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D2" t="s">
         <v>336</v>
@@ -9917,16 +10013,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C4" t="s">
+        <v>426</v>
+      </c>
+      <c r="D4" t="s">
         <v>497</v>
-      </c>
-      <c r="B4" t="s">
-        <v>498</v>
-      </c>
-      <c r="C4" t="s">
-        <v>428</v>
-      </c>
-      <c r="D4" t="s">
-        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -9958,19 +10054,19 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
+        <v>499</v>
+      </c>
+      <c r="G2" t="s">
+        <v>500</v>
+      </c>
+      <c r="H2" t="s">
         <v>501</v>
-      </c>
-      <c r="G2" t="s">
-        <v>502</v>
-      </c>
-      <c r="H2" t="s">
-        <v>503</v>
       </c>
       <c r="I2" t="s">
         <v>336</v>
@@ -10013,7 +10109,7 @@
         <v>221</v>
       </c>
       <c r="C4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E4">
         <v>50</v>
@@ -10046,34 +10142,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D1" t="s">
         <v>505</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>506</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>507</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>508</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>509</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>510</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>511</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>512</v>
-      </c>
-      <c r="K1" t="s">
-        <v>513</v>
-      </c>
-      <c r="L1" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10081,34 +10177,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D2" t="s">
         <v>515</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>516</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>517</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>518</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>519</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>520</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>521</v>
       </c>
-      <c r="I2" t="s">
-        <v>522</v>
-      </c>
-      <c r="J2" t="s">
-        <v>523</v>
-      </c>
       <c r="K2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="L2" t="s">
         <v>97</v>
@@ -10125,7 +10221,7 @@
         <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -10154,13 +10250,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -10202,22 +10298,22 @@
         <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F2" t="s">
         <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H2" t="s">
         <v>276</v>
       </c>
       <c r="I2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="J2" t="s">
         <v>54</v>
@@ -10246,7 +10342,7 @@
         <v>118</v>
       </c>
       <c r="H3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="I3" t="s">
         <v>118</v>
@@ -10281,28 +10377,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10310,28 +10406,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10365,48 +10461,48 @@
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/logos.xlsx
+++ b/Excel/一方通行/logos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2784F7-17B8-4CE3-8D84-FFCD682F4908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33BB96F-D523-417A-AEC4-A30B33B6F8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="566">
   <si>
     <t>Id</t>
   </si>
@@ -10034,16 +10034,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10069,10 +10074,13 @@
         <v>501</v>
       </c>
       <c r="I2" t="s">
+        <v>325</v>
+      </c>
+      <c r="J2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10098,10 +10106,13 @@
         <v>118</v>
       </c>
       <c r="I3" t="s">
+        <v>365</v>
+      </c>
+      <c r="J3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>387</v>
       </c>

--- a/Excel/一方通行/logos.xlsx
+++ b/Excel/一方通行/logos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33BB96F-D523-417A-AEC4-A30B33B6F8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B50A4B4-BDEC-40CD-B510-A49BCF6E7810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="566">
   <si>
     <t>Id</t>
   </si>
@@ -388,12 +388,6 @@
     <t>高度</t>
   </si>
   <si>
-    <t>高台单位？</t>
-  </si>
-  <si>
-    <t>地面</t>
-  </si>
-  <si>
     <t>阻挡个数</t>
   </si>
   <si>
@@ -548,12 +542,6 @@
   </si>
   <si>
     <t>Height</t>
-  </si>
-  <si>
-    <t>CanSetHigh</t>
-  </si>
-  <si>
-    <t>CanSetGround</t>
   </si>
   <si>
     <t>StopCount</t>
@@ -2005,6 +1993,22 @@
   </si>
   <si>
     <t>逻各斯1攻击</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>可部署位</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanSetPos</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>高台位</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2534,7 +2538,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BW572"/>
+  <dimension ref="A1:BV572"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2564,22 +2568,22 @@
     <col min="34" max="34" width="13.83203125" customWidth="1"/>
     <col min="35" max="35" width="34.5" customWidth="1"/>
     <col min="36" max="37" width="9.83203125" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.5" customWidth="1"/>
+    <col min="49" max="49" width="24.33203125" customWidth="1"/>
+    <col min="51" max="51" width="17.75" customWidth="1"/>
+    <col min="52" max="52" width="7.83203125" customWidth="1"/>
+    <col min="55" max="55" width="24.25" customWidth="1"/>
+    <col min="56" max="56" width="13.25" customWidth="1"/>
+    <col min="57" max="57" width="16.08203125" customWidth="1"/>
+    <col min="58" max="58" width="8" customWidth="1"/>
+    <col min="63" max="63" width="39.58203125" customWidth="1"/>
+    <col min="64" max="64" width="14" customWidth="1"/>
+    <col min="65" max="65" width="14.83203125" customWidth="1"/>
+    <col min="66" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>5</v>
       </c>
@@ -2655,274 +2659,268 @@
       <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="13" t="s">
+        <v>562</v>
+      </c>
+      <c r="AN1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BC1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>42</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" t="s">
-        <v>46</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>49</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>50</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>53</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>58</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>59</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>62</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="AN2" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AO2" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AP2" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
         <v>84</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AR2" t="s">
         <v>85</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AS2" t="s">
         <v>86</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AT2" t="s">
         <v>87</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>88</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>89</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>90</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>91</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" t="s">
         <v>92</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AZ2" t="s">
         <v>93</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BA2" t="s">
         <v>94</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>95</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BC2" t="s">
         <v>96</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>97</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>98</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>99</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BG2" t="s">
         <v>100</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BH2" t="s">
         <v>101</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BK2" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BL2" t="s">
         <v>105</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BM2" t="s">
         <v>106</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BN2" t="s">
         <v>107</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BO2" t="s">
         <v>108</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BP2" t="s">
         <v>109</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BQ2" t="s">
         <v>110</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BR2" t="s">
         <v>111</v>
       </c>
-      <c r="BP2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2930,88 +2928,88 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Q3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="R3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="S3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="T3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="V3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="W3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Y3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Z3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AA3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AB3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AC3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AE3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AF3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
         <v>2</v>
@@ -3020,61 +3018,61 @@
         <v>2</v>
       </c>
       <c r="AI3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AJ3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM3" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU3" t="s">
         <v>116</v>
       </c>
-      <c r="AN3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>118</v>
-      </c>
       <c r="AV3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AW3" t="s">
         <v>117</v>
       </c>
       <c r="AX3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AZ3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BB3" t="s">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="BC3" t="s">
         <v>2</v>
@@ -3086,60 +3084,57 @@
         <v>2</v>
       </c>
       <c r="BF3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BH3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>118</v>
-      </c>
       <c r="BI3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>2</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>124</v>
-      </c>
       <c r="BK3" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="BL3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BN3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BO3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BP3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BQ3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BR3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:75" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F4" t="str">
         <f>"char_"&amp;E4&amp;"_"&amp;D4</f>
@@ -3197,2406 +3192,2409 @@
         <v>4</v>
       </c>
       <c r="AH4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM4" s="13" t="s">
+        <v>565</v>
+      </c>
+      <c r="AN4">
+        <v>1</v>
+      </c>
+      <c r="AO4">
+        <v>0.5</v>
+      </c>
+      <c r="AV4">
+        <v>0.25</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BB4" t="s">
         <v>129</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="BC4" t="s">
         <v>130</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="BD4" t="s">
         <v>131</v>
       </c>
-      <c r="AM4">
-        <v>1</v>
-      </c>
-      <c r="AO4">
-        <v>1</v>
-      </c>
-      <c r="AP4">
-        <v>0.5</v>
-      </c>
-      <c r="AW4">
-        <v>0.25</v>
-      </c>
-      <c r="BB4" t="s">
+      <c r="BE4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BF4" t="s">
         <v>132</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BG4">
+        <v>6</v>
+      </c>
+      <c r="BH4" t="s">
         <v>133</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BI4" t="s">
         <v>134</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BJ4" t="s">
         <v>135</v>
       </c>
-      <c r="BF4" t="s">
-        <v>127</v>
-      </c>
-      <c r="BG4" t="s">
+      <c r="BL4" t="s">
         <v>136</v>
       </c>
-      <c r="BH4">
-        <v>6</v>
-      </c>
-      <c r="BI4" t="s">
+      <c r="BM4" t="s">
         <v>137</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BO4" t="s">
         <v>138</v>
       </c>
-      <c r="BK4" t="s">
-        <v>139</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>140</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>141</v>
-      </c>
       <c r="BP4" t="s">
-        <v>142</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>142</v>
-      </c>
-      <c r="BS4">
-        <v>1</v>
-      </c>
-      <c r="BW4" s="3"/>
-    </row>
-    <row r="9" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="BR9" s="12"/>
-    </row>
-    <row r="10" spans="1:75" ht="14.5" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="BR4">
+        <v>1</v>
+      </c>
+      <c r="BV4" s="3"/>
+    </row>
+    <row r="5" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="AM5" s="13"/>
+    </row>
+    <row r="9" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BQ9" s="12"/>
+    </row>
+    <row r="10" spans="1:74" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D10" s="10"/>
       <c r="E10" s="11"/>
-      <c r="BO10" s="12"/>
-      <c r="BR10" s="12"/>
-    </row>
-    <row r="11" spans="1:75" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN10" s="12"/>
+      <c r="BQ10" s="12"/>
+    </row>
+    <row r="11" spans="1:74" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D11" s="10"/>
       <c r="E11" s="11"/>
-      <c r="BO11" s="12"/>
-      <c r="BR11" s="12"/>
-    </row>
-    <row r="12" spans="1:75" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN11" s="12"/>
+      <c r="BQ11" s="12"/>
+    </row>
+    <row r="12" spans="1:74" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D12" s="10"/>
       <c r="E12" s="11"/>
-      <c r="BO12" s="12"/>
-      <c r="BR12" s="12"/>
-    </row>
-    <row r="13" spans="1:75" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN12" s="12"/>
+      <c r="BQ12" s="12"/>
+    </row>
+    <row r="13" spans="1:74" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D13" s="10"/>
       <c r="E13" s="11"/>
-      <c r="BO13" s="12"/>
-      <c r="BR13" s="12"/>
-    </row>
-    <row r="14" spans="1:75" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN13" s="12"/>
+      <c r="BQ13" s="12"/>
+    </row>
+    <row r="14" spans="1:74" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D14" s="10"/>
       <c r="E14" s="11"/>
-      <c r="BO14" s="12"/>
-      <c r="BR14" s="12"/>
-    </row>
-    <row r="15" spans="1:75" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN14" s="12"/>
+      <c r="BQ14" s="12"/>
+    </row>
+    <row r="15" spans="1:74" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D15" s="10"/>
       <c r="E15" s="11"/>
-      <c r="BO15" s="12"/>
-      <c r="BR15" s="12"/>
-    </row>
-    <row r="16" spans="1:75" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN15" s="12"/>
+      <c r="BQ15" s="12"/>
+    </row>
+    <row r="16" spans="1:74" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D16" s="10"/>
       <c r="E16" s="11"/>
-      <c r="BO16" s="12"/>
-      <c r="BR16" s="12"/>
-    </row>
-    <row r="17" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN16" s="12"/>
+      <c r="BQ16" s="12"/>
+    </row>
+    <row r="17" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
-      <c r="BR17" s="12"/>
-    </row>
-    <row r="18" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ17" s="12"/>
+    </row>
+    <row r="18" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D18" s="10"/>
       <c r="E18" s="11"/>
-      <c r="BR18" s="12"/>
-    </row>
-    <row r="19" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ18" s="12"/>
+    </row>
+    <row r="19" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D19" s="10"/>
       <c r="E19" s="11"/>
-      <c r="BR19" s="12"/>
-    </row>
-    <row r="20" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ19" s="12"/>
+    </row>
+    <row r="20" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
-      <c r="BO20" s="12"/>
-      <c r="BR20" s="12"/>
-    </row>
-    <row r="21" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN20" s="12"/>
+      <c r="BQ20" s="12"/>
+    </row>
+    <row r="21" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
-      <c r="BO21" s="12"/>
-      <c r="BR21" s="12"/>
-    </row>
-    <row r="22" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN21" s="12"/>
+      <c r="BQ21" s="12"/>
+    </row>
+    <row r="22" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D22" s="10"/>
       <c r="E22" s="11"/>
-      <c r="BO22" s="12"/>
-      <c r="BR22" s="12"/>
-    </row>
-    <row r="23" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN22" s="12"/>
+      <c r="BQ22" s="12"/>
+    </row>
+    <row r="23" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
-      <c r="BO23" s="12"/>
-      <c r="BR23" s="12"/>
-    </row>
-    <row r="24" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN23" s="12"/>
+      <c r="BQ23" s="12"/>
+    </row>
+    <row r="24" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
-      <c r="BO24" s="12"/>
-      <c r="BR24" s="12"/>
-    </row>
-    <row r="25" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN24" s="12"/>
+      <c r="BQ24" s="12"/>
+    </row>
+    <row r="25" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D25" s="10"/>
       <c r="E25" s="11"/>
-      <c r="BO25" s="12"/>
-      <c r="BR25" s="12"/>
-    </row>
-    <row r="26" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN25" s="12"/>
+      <c r="BQ25" s="12"/>
+    </row>
+    <row r="26" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D26" s="10"/>
       <c r="E26" s="11"/>
-      <c r="BO26" s="12"/>
-      <c r="BR26" s="12"/>
-    </row>
-    <row r="27" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN26" s="12"/>
+      <c r="BQ26" s="12"/>
+    </row>
+    <row r="27" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
-      <c r="BO27" s="12"/>
-      <c r="BR27" s="12"/>
-    </row>
-    <row r="28" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN27" s="12"/>
+      <c r="BQ27" s="12"/>
+    </row>
+    <row r="28" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
-      <c r="BO28" s="12"/>
-      <c r="BR28" s="12"/>
-    </row>
-    <row r="29" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN28" s="12"/>
+      <c r="BQ28" s="12"/>
+    </row>
+    <row r="29" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D29" s="10"/>
       <c r="E29" s="11"/>
-      <c r="BO29" s="12"/>
-      <c r="BR29" s="12"/>
-    </row>
-    <row r="30" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN29" s="12"/>
+      <c r="BQ29" s="12"/>
+    </row>
+    <row r="30" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
-      <c r="BO30" s="12"/>
-      <c r="BR30" s="12"/>
-    </row>
-    <row r="31" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN30" s="12"/>
+      <c r="BQ30" s="12"/>
+    </row>
+    <row r="31" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D31" s="10"/>
       <c r="E31" s="11"/>
-      <c r="BO31" s="12"/>
-      <c r="BR31" s="12"/>
-    </row>
-    <row r="32" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN31" s="12"/>
+      <c r="BQ31" s="12"/>
+    </row>
+    <row r="32" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D32" s="10"/>
       <c r="E32" s="11"/>
-      <c r="BO32" s="12"/>
-      <c r="BR32" s="12"/>
-    </row>
-    <row r="33" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN32" s="12"/>
+      <c r="BQ32" s="12"/>
+    </row>
+    <row r="33" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D33" s="10"/>
       <c r="E33" s="11"/>
-      <c r="BO33" s="12"/>
-      <c r="BR33" s="12"/>
-    </row>
-    <row r="34" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN33" s="12"/>
+      <c r="BQ33" s="12"/>
+    </row>
+    <row r="34" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D34" s="10"/>
       <c r="E34" s="11"/>
-      <c r="BO34" s="12"/>
-      <c r="BR34" s="12"/>
-    </row>
-    <row r="35" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN34" s="12"/>
+      <c r="BQ34" s="12"/>
+    </row>
+    <row r="35" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D35" s="10"/>
       <c r="E35" s="11"/>
-      <c r="BO35" s="12"/>
-      <c r="BR35" s="12"/>
-    </row>
-    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN35" s="12"/>
+      <c r="BQ35" s="12"/>
+    </row>
+    <row r="36" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="10"/>
       <c r="E36" s="11"/>
-      <c r="BO36" s="12"/>
-      <c r="BR36" s="12"/>
-    </row>
-    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN36" s="12"/>
+      <c r="BQ36" s="12"/>
+    </row>
+    <row r="37" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
-      <c r="BO37" s="12"/>
-      <c r="BR37" s="12"/>
-    </row>
-    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN37" s="12"/>
+      <c r="BQ37" s="12"/>
+    </row>
+    <row r="38" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D38" s="10"/>
       <c r="E38" s="11"/>
-      <c r="BO38" s="12"/>
-      <c r="BR38" s="12"/>
-    </row>
-    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN38" s="12"/>
+      <c r="BQ38" s="12"/>
+    </row>
+    <row r="39" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
-      <c r="BO39" s="12"/>
-      <c r="BR39" s="12"/>
-    </row>
-    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN39" s="12"/>
+      <c r="BQ39" s="12"/>
+    </row>
+    <row r="40" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
-      <c r="BO40" s="12"/>
-      <c r="BR40" s="12"/>
-    </row>
-    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN40" s="12"/>
+      <c r="BQ40" s="12"/>
+    </row>
+    <row r="41" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
-      <c r="BO41" s="12"/>
-      <c r="BR41" s="12"/>
-    </row>
-    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN41" s="12"/>
+      <c r="BQ41" s="12"/>
+    </row>
+    <row r="42" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="10"/>
       <c r="E42" s="11"/>
-      <c r="BO42" s="12"/>
-      <c r="BR42" s="12"/>
-    </row>
-    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN42" s="12"/>
+      <c r="BQ42" s="12"/>
+    </row>
+    <row r="43" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D43" s="10"/>
       <c r="E43" s="11"/>
-      <c r="BO43" s="12"/>
-      <c r="BR43" s="12"/>
-    </row>
-    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN43" s="12"/>
+      <c r="BQ43" s="12"/>
+    </row>
+    <row r="44" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="10"/>
       <c r="E44" s="11"/>
-      <c r="BO44" s="12"/>
-      <c r="BR44" s="12"/>
-    </row>
-    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN44" s="12"/>
+      <c r="BQ44" s="12"/>
+    </row>
+    <row r="45" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="10"/>
       <c r="E45" s="11"/>
-      <c r="BO45" s="12"/>
-      <c r="BR45" s="12"/>
-    </row>
-    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN45" s="12"/>
+      <c r="BQ45" s="12"/>
+    </row>
+    <row r="46" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D46" s="10"/>
       <c r="E46" s="11"/>
-      <c r="BO46" s="12"/>
-      <c r="BR46" s="12"/>
-    </row>
-    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN46" s="12"/>
+      <c r="BQ46" s="12"/>
+    </row>
+    <row r="47" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D47" s="10"/>
       <c r="E47" s="11"/>
-      <c r="BO47" s="12"/>
-      <c r="BR47" s="12"/>
-    </row>
-    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN47" s="12"/>
+      <c r="BQ47" s="12"/>
+    </row>
+    <row r="48" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
-      <c r="BO48" s="12"/>
-      <c r="BR48" s="12"/>
-    </row>
-    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN48" s="12"/>
+      <c r="BQ48" s="12"/>
+    </row>
+    <row r="49" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D49" s="10"/>
       <c r="E49" s="11"/>
-      <c r="BO49" s="12"/>
-      <c r="BR49" s="12"/>
-    </row>
-    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN49" s="12"/>
+      <c r="BQ49" s="12"/>
+    </row>
+    <row r="50" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
-      <c r="BO50" s="12"/>
-      <c r="BR50" s="12"/>
-    </row>
-    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN50" s="12"/>
+      <c r="BQ50" s="12"/>
+    </row>
+    <row r="51" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="10"/>
       <c r="E51" s="11"/>
-      <c r="BO51" s="12"/>
-      <c r="BR51" s="12"/>
-    </row>
-    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN51" s="12"/>
+      <c r="BQ51" s="12"/>
+    </row>
+    <row r="52" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
-      <c r="BO52" s="12"/>
-      <c r="BR52" s="12"/>
-    </row>
-    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN52" s="12"/>
+      <c r="BQ52" s="12"/>
+    </row>
+    <row r="53" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="10"/>
       <c r="E53" s="11"/>
-      <c r="BO53" s="12"/>
-      <c r="BR53" s="12"/>
-    </row>
-    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN53" s="12"/>
+      <c r="BQ53" s="12"/>
+    </row>
+    <row r="54" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="10"/>
       <c r="E54" s="11"/>
-      <c r="BO54" s="12"/>
-      <c r="BR54" s="12"/>
-    </row>
-    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN54" s="12"/>
+      <c r="BQ54" s="12"/>
+    </row>
+    <row r="55" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="10"/>
       <c r="E55" s="11"/>
-      <c r="BO55" s="12"/>
-      <c r="BR55" s="12"/>
-    </row>
-    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN55" s="12"/>
+      <c r="BQ55" s="12"/>
+    </row>
+    <row r="56" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="10"/>
       <c r="E56" s="11"/>
-      <c r="BO56" s="12"/>
-      <c r="BR56" s="12"/>
-    </row>
-    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN56" s="12"/>
+      <c r="BQ56" s="12"/>
+    </row>
+    <row r="57" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="10"/>
       <c r="E57" s="11"/>
-      <c r="BO57" s="12"/>
-      <c r="BR57" s="12"/>
-    </row>
-    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN57" s="12"/>
+      <c r="BQ57" s="12"/>
+    </row>
+    <row r="58" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="10"/>
       <c r="E58" s="11"/>
-      <c r="BO58" s="12"/>
-      <c r="BR58" s="12"/>
-    </row>
-    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN58" s="12"/>
+      <c r="BQ58" s="12"/>
+    </row>
+    <row r="59" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="10"/>
       <c r="E59" s="11"/>
-      <c r="BO59" s="12"/>
-      <c r="BR59" s="12"/>
-    </row>
-    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN59" s="12"/>
+      <c r="BQ59" s="12"/>
+    </row>
+    <row r="60" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="10"/>
       <c r="E60" s="11"/>
-      <c r="BO60" s="12"/>
-      <c r="BR60" s="12"/>
-    </row>
-    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN60" s="12"/>
+      <c r="BQ60" s="12"/>
+    </row>
+    <row r="61" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="10"/>
       <c r="E61" s="11"/>
-      <c r="BO61" s="12"/>
-      <c r="BR61" s="12"/>
-    </row>
-    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN61" s="12"/>
+      <c r="BQ61" s="12"/>
+    </row>
+    <row r="62" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="10"/>
       <c r="E62" s="11"/>
-      <c r="BO62" s="12"/>
-      <c r="BR62" s="12"/>
-    </row>
-    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN62" s="12"/>
+      <c r="BQ62" s="12"/>
+    </row>
+    <row r="63" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="10"/>
       <c r="E63" s="11"/>
-      <c r="BO63" s="12"/>
-      <c r="BR63" s="12"/>
-    </row>
-    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN63" s="12"/>
+      <c r="BQ63" s="12"/>
+    </row>
+    <row r="64" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="10"/>
       <c r="E64" s="11"/>
-      <c r="BO64" s="12"/>
-      <c r="BR64" s="12"/>
-    </row>
-    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN64" s="12"/>
+      <c r="BQ64" s="12"/>
+    </row>
+    <row r="65" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="10"/>
       <c r="E65" s="11"/>
-      <c r="BO65" s="12"/>
-      <c r="BR65" s="12"/>
-    </row>
-    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN65" s="12"/>
+      <c r="BQ65" s="12"/>
+    </row>
+    <row r="66" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="10"/>
       <c r="E66" s="11"/>
-      <c r="BO66" s="12"/>
-      <c r="BR66" s="12"/>
-    </row>
-    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN66" s="12"/>
+      <c r="BQ66" s="12"/>
+    </row>
+    <row r="67" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="10"/>
       <c r="E67" s="11"/>
-      <c r="BO67" s="12"/>
-      <c r="BR67" s="12"/>
-    </row>
-    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN67" s="12"/>
+      <c r="BQ67" s="12"/>
+    </row>
+    <row r="68" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="10"/>
       <c r="E68" s="11"/>
-      <c r="BO68" s="12"/>
-      <c r="BR68" s="12"/>
-    </row>
-    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN68" s="12"/>
+      <c r="BQ68" s="12"/>
+    </row>
+    <row r="69" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="10"/>
       <c r="E69" s="11"/>
-      <c r="BO69" s="12"/>
-      <c r="BR69" s="12"/>
-    </row>
-    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN69" s="12"/>
+      <c r="BQ69" s="12"/>
+    </row>
+    <row r="70" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="10"/>
       <c r="E70" s="11"/>
-      <c r="BO70" s="12"/>
-      <c r="BR70" s="12"/>
-    </row>
-    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN70" s="12"/>
+      <c r="BQ70" s="12"/>
+    </row>
+    <row r="71" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="10"/>
       <c r="E71" s="11"/>
-      <c r="BO71" s="12"/>
-      <c r="BR71" s="12"/>
-    </row>
-    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN71" s="12"/>
+      <c r="BQ71" s="12"/>
+    </row>
+    <row r="72" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="10"/>
       <c r="E72" s="11"/>
-      <c r="BO72" s="12"/>
-      <c r="BR72" s="12"/>
-    </row>
-    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN72" s="12"/>
+      <c r="BQ72" s="12"/>
+    </row>
+    <row r="73" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="10"/>
       <c r="E73" s="11"/>
-      <c r="BO73" s="12"/>
-      <c r="BR73" s="12"/>
-    </row>
-    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN73" s="12"/>
+      <c r="BQ73" s="12"/>
+    </row>
+    <row r="74" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="10"/>
       <c r="E74" s="11"/>
-      <c r="BO74" s="12"/>
-      <c r="BR74" s="12"/>
-    </row>
-    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN74" s="12"/>
+      <c r="BQ74" s="12"/>
+    </row>
+    <row r="75" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="10"/>
       <c r="E75" s="11"/>
-      <c r="BO75" s="12"/>
-      <c r="BR75" s="12"/>
-    </row>
-    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN75" s="12"/>
+      <c r="BQ75" s="12"/>
+    </row>
+    <row r="76" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="10"/>
       <c r="E76" s="11"/>
-      <c r="BO76" s="12"/>
-      <c r="BR76" s="12"/>
-    </row>
-    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN76" s="12"/>
+      <c r="BQ76" s="12"/>
+    </row>
+    <row r="77" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="10"/>
       <c r="E77" s="11"/>
-      <c r="BO77" s="12"/>
-      <c r="BR77" s="12"/>
-    </row>
-    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN77" s="12"/>
+      <c r="BQ77" s="12"/>
+    </row>
+    <row r="78" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="10"/>
       <c r="E78" s="11"/>
-      <c r="BO78" s="12"/>
-      <c r="BR78" s="12"/>
-    </row>
-    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN78" s="12"/>
+      <c r="BQ78" s="12"/>
+    </row>
+    <row r="79" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="10"/>
       <c r="E79" s="11"/>
-      <c r="BO79" s="12"/>
-      <c r="BR79" s="12"/>
-    </row>
-    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN79" s="12"/>
+      <c r="BQ79" s="12"/>
+    </row>
+    <row r="80" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="10"/>
       <c r="E80" s="11"/>
-      <c r="BO80" s="12"/>
-      <c r="BR80" s="12"/>
-    </row>
-    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN80" s="12"/>
+      <c r="BQ80" s="12"/>
+    </row>
+    <row r="81" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="10"/>
       <c r="E81" s="11"/>
-      <c r="BO81" s="12"/>
-      <c r="BR81" s="12"/>
-    </row>
-    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN81" s="12"/>
+      <c r="BQ81" s="12"/>
+    </row>
+    <row r="82" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="10"/>
       <c r="E82" s="11"/>
-      <c r="BO82" s="12"/>
-      <c r="BR82" s="12"/>
-    </row>
-    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN82" s="12"/>
+      <c r="BQ82" s="12"/>
+    </row>
+    <row r="83" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="10"/>
       <c r="E83" s="11"/>
-      <c r="BO83" s="12"/>
-      <c r="BR83" s="12"/>
-    </row>
-    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN83" s="12"/>
+      <c r="BQ83" s="12"/>
+    </row>
+    <row r="84" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="10"/>
       <c r="E84" s="11"/>
-      <c r="BO84" s="12"/>
-      <c r="BR84" s="12"/>
-    </row>
-    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN84" s="12"/>
+      <c r="BQ84" s="12"/>
+    </row>
+    <row r="85" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="10"/>
       <c r="E85" s="11"/>
-      <c r="BO85" s="12"/>
-      <c r="BR85" s="12"/>
-    </row>
-    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN85" s="12"/>
+      <c r="BQ85" s="12"/>
+    </row>
+    <row r="86" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="10"/>
       <c r="E86" s="11"/>
-      <c r="BO86" s="12"/>
-      <c r="BR86" s="12"/>
-    </row>
-    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN86" s="12"/>
+      <c r="BQ86" s="12"/>
+    </row>
+    <row r="87" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="10"/>
       <c r="E87" s="11"/>
-      <c r="BO87" s="12"/>
-      <c r="BR87" s="12"/>
-    </row>
-    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN87" s="12"/>
+      <c r="BQ87" s="12"/>
+    </row>
+    <row r="88" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="10"/>
       <c r="E88" s="11"/>
-      <c r="BO88" s="12"/>
-      <c r="BR88" s="12"/>
-    </row>
-    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN88" s="12"/>
+      <c r="BQ88" s="12"/>
+    </row>
+    <row r="89" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="10"/>
       <c r="E89" s="11"/>
-      <c r="BO89" s="12"/>
-      <c r="BR89" s="12"/>
-    </row>
-    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN89" s="12"/>
+      <c r="BQ89" s="12"/>
+    </row>
+    <row r="90" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="10"/>
       <c r="E90" s="11"/>
-      <c r="BO90" s="12"/>
-      <c r="BR90" s="12"/>
-    </row>
-    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN90" s="12"/>
+      <c r="BQ90" s="12"/>
+    </row>
+    <row r="91" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="10"/>
       <c r="E91" s="11"/>
-      <c r="BO91" s="12"/>
-      <c r="BR91" s="12"/>
-    </row>
-    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN91" s="12"/>
+      <c r="BQ91" s="12"/>
+    </row>
+    <row r="92" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="10"/>
       <c r="E92" s="11"/>
-      <c r="BO92" s="12"/>
-      <c r="BR92" s="12"/>
-    </row>
-    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN92" s="12"/>
+      <c r="BQ92" s="12"/>
+    </row>
+    <row r="93" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="10"/>
       <c r="E93" s="11"/>
-      <c r="BO93" s="12"/>
-      <c r="BR93" s="12"/>
-    </row>
-    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN93" s="12"/>
+      <c r="BQ93" s="12"/>
+    </row>
+    <row r="94" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="10"/>
       <c r="E94" s="11"/>
-      <c r="BO94" s="12"/>
-      <c r="BR94" s="12"/>
-    </row>
-    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN94" s="12"/>
+      <c r="BQ94" s="12"/>
+    </row>
+    <row r="95" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="10"/>
       <c r="E95" s="11"/>
-      <c r="BO95" s="12"/>
-      <c r="BR95" s="12"/>
-    </row>
-    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN95" s="12"/>
+      <c r="BQ95" s="12"/>
+    </row>
+    <row r="96" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="10"/>
       <c r="E96" s="11"/>
-      <c r="BO96" s="12"/>
-      <c r="BR96" s="12"/>
-    </row>
-    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN96" s="12"/>
+      <c r="BQ96" s="12"/>
+    </row>
+    <row r="97" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="10"/>
       <c r="E97" s="11"/>
-      <c r="BO97" s="12"/>
-      <c r="BR97" s="12"/>
-    </row>
-    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN97" s="12"/>
+      <c r="BQ97" s="12"/>
+    </row>
+    <row r="98" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="10"/>
       <c r="E98" s="11"/>
-      <c r="BO98" s="12"/>
-      <c r="BR98" s="12"/>
-    </row>
-    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN98" s="12"/>
+      <c r="BQ98" s="12"/>
+    </row>
+    <row r="99" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="10"/>
       <c r="E99" s="11"/>
-      <c r="BO99" s="12"/>
-      <c r="BR99" s="12"/>
-    </row>
-    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN99" s="12"/>
+      <c r="BQ99" s="12"/>
+    </row>
+    <row r="100" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="10"/>
       <c r="E100" s="11"/>
-      <c r="BO100" s="12"/>
-      <c r="BR100" s="12"/>
-    </row>
-    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN100" s="12"/>
+      <c r="BQ100" s="12"/>
+    </row>
+    <row r="101" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="10"/>
       <c r="E101" s="11"/>
-      <c r="BO101" s="12"/>
-      <c r="BR101" s="12"/>
-    </row>
-    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN101" s="12"/>
+      <c r="BQ101" s="12"/>
+    </row>
+    <row r="102" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="10"/>
       <c r="E102" s="11"/>
-      <c r="BO102" s="12"/>
-      <c r="BR102" s="12"/>
-    </row>
-    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN102" s="12"/>
+      <c r="BQ102" s="12"/>
+    </row>
+    <row r="103" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="10"/>
       <c r="E103" s="11"/>
-      <c r="BO103" s="12"/>
-      <c r="BR103" s="12"/>
-    </row>
-    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN103" s="12"/>
+      <c r="BQ103" s="12"/>
+    </row>
+    <row r="104" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="10"/>
       <c r="E104" s="11"/>
-      <c r="BO104" s="12"/>
-      <c r="BR104" s="12"/>
-    </row>
-    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN104" s="12"/>
+      <c r="BQ104" s="12"/>
+    </row>
+    <row r="105" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="10"/>
       <c r="E105" s="11"/>
-      <c r="BO105" s="12"/>
-      <c r="BR105" s="12"/>
-    </row>
-    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN105" s="12"/>
+      <c r="BQ105" s="12"/>
+    </row>
+    <row r="106" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="10"/>
       <c r="E106" s="11"/>
-      <c r="BO106" s="12"/>
-      <c r="BR106" s="12"/>
-    </row>
-    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN106" s="12"/>
+      <c r="BQ106" s="12"/>
+    </row>
+    <row r="107" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="10"/>
       <c r="E107" s="11"/>
-      <c r="BO107" s="12"/>
-      <c r="BR107" s="12"/>
-    </row>
-    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN107" s="12"/>
+      <c r="BQ107" s="12"/>
+    </row>
+    <row r="108" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="10"/>
       <c r="E108" s="11"/>
-      <c r="BO108" s="12"/>
-      <c r="BR108" s="12"/>
-    </row>
-    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN108" s="12"/>
+      <c r="BQ108" s="12"/>
+    </row>
+    <row r="109" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="10"/>
       <c r="E109" s="11"/>
-      <c r="BO109" s="12"/>
-      <c r="BR109" s="12"/>
-    </row>
-    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN109" s="12"/>
+      <c r="BQ109" s="12"/>
+    </row>
+    <row r="110" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
       <c r="E110" s="11"/>
-      <c r="BO110" s="12"/>
-      <c r="BR110" s="12"/>
-    </row>
-    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN110" s="12"/>
+      <c r="BQ110" s="12"/>
+    </row>
+    <row r="111" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="10"/>
       <c r="E111" s="11"/>
-      <c r="BO111" s="12"/>
-      <c r="BR111" s="12"/>
-    </row>
-    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN111" s="12"/>
+      <c r="BQ111" s="12"/>
+    </row>
+    <row r="112" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="10"/>
       <c r="E112" s="11"/>
-      <c r="BO112" s="12"/>
-      <c r="BR112" s="12"/>
-    </row>
-    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN112" s="12"/>
+      <c r="BQ112" s="12"/>
+    </row>
+    <row r="113" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="10"/>
       <c r="E113" s="11"/>
-      <c r="BO113" s="12"/>
-      <c r="BR113" s="12"/>
-    </row>
-    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN113" s="12"/>
+      <c r="BQ113" s="12"/>
+    </row>
+    <row r="114" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="10"/>
       <c r="E114" s="11"/>
-      <c r="BO114" s="12"/>
-      <c r="BR114" s="12"/>
-    </row>
-    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN114" s="12"/>
+      <c r="BQ114" s="12"/>
+    </row>
+    <row r="115" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="10"/>
       <c r="E115" s="11"/>
-      <c r="BO115" s="12"/>
-      <c r="BR115" s="12"/>
-    </row>
-    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN115" s="12"/>
+      <c r="BQ115" s="12"/>
+    </row>
+    <row r="116" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="10"/>
       <c r="E116" s="11"/>
-      <c r="BO116" s="12"/>
-      <c r="BR116" s="12"/>
-    </row>
-    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN116" s="12"/>
+      <c r="BQ116" s="12"/>
+    </row>
+    <row r="117" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="10"/>
       <c r="E117" s="11"/>
-      <c r="BO117" s="12"/>
-      <c r="BR117" s="12"/>
-    </row>
-    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN117" s="12"/>
+      <c r="BQ117" s="12"/>
+    </row>
+    <row r="118" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="10"/>
       <c r="E118" s="11"/>
-      <c r="BO118" s="12"/>
-      <c r="BR118" s="12"/>
-    </row>
-    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN118" s="12"/>
+      <c r="BQ118" s="12"/>
+    </row>
+    <row r="119" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="10"/>
       <c r="E119" s="11"/>
-      <c r="BO119" s="12"/>
-      <c r="BR119" s="12"/>
-    </row>
-    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN119" s="12"/>
+      <c r="BQ119" s="12"/>
+    </row>
+    <row r="120" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="10"/>
       <c r="E120" s="11"/>
-      <c r="BO120" s="12"/>
-      <c r="BR120" s="12"/>
-    </row>
-    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN120" s="12"/>
+      <c r="BQ120" s="12"/>
+    </row>
+    <row r="121" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="10"/>
       <c r="E121" s="11"/>
-      <c r="BO121" s="12"/>
-      <c r="BR121" s="12"/>
-    </row>
-    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN121" s="12"/>
+      <c r="BQ121" s="12"/>
+    </row>
+    <row r="122" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="10"/>
       <c r="E122" s="11"/>
-      <c r="BO122" s="12"/>
-      <c r="BR122" s="12"/>
-    </row>
-    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN122" s="12"/>
+      <c r="BQ122" s="12"/>
+    </row>
+    <row r="123" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="10"/>
       <c r="E123" s="11"/>
-      <c r="BO123" s="12"/>
-      <c r="BR123" s="12"/>
-    </row>
-    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN123" s="12"/>
+      <c r="BQ123" s="12"/>
+    </row>
+    <row r="124" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="10"/>
       <c r="E124" s="11"/>
-      <c r="BO124" s="12"/>
-      <c r="BR124" s="12"/>
-    </row>
-    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN124" s="12"/>
+      <c r="BQ124" s="12"/>
+    </row>
+    <row r="125" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="10"/>
       <c r="E125" s="11"/>
-      <c r="BO125" s="12"/>
-      <c r="BR125" s="12"/>
-    </row>
-    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN125" s="12"/>
+      <c r="BQ125" s="12"/>
+    </row>
+    <row r="126" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="10"/>
       <c r="E126" s="11"/>
-      <c r="BO126" s="12"/>
-      <c r="BR126" s="12"/>
-    </row>
-    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN126" s="12"/>
+      <c r="BQ126" s="12"/>
+    </row>
+    <row r="127" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="10"/>
       <c r="E127" s="11"/>
-      <c r="BO127" s="12"/>
-      <c r="BR127" s="12"/>
-    </row>
-    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN127" s="12"/>
+      <c r="BQ127" s="12"/>
+    </row>
+    <row r="128" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="10"/>
       <c r="E128" s="11"/>
-      <c r="BO128" s="12"/>
-      <c r="BR128" s="12"/>
-    </row>
-    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN128" s="12"/>
+      <c r="BQ128" s="12"/>
+    </row>
+    <row r="129" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="10"/>
       <c r="E129" s="11"/>
-      <c r="BO129" s="12"/>
-      <c r="BR129" s="12"/>
-    </row>
-    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN129" s="12"/>
+      <c r="BQ129" s="12"/>
+    </row>
+    <row r="130" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="10"/>
       <c r="E130" s="11"/>
-      <c r="BO130" s="12"/>
-      <c r="BR130" s="12"/>
-    </row>
-    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN130" s="12"/>
+      <c r="BQ130" s="12"/>
+    </row>
+    <row r="131" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="10"/>
       <c r="E131" s="11"/>
-      <c r="BO131" s="12"/>
-      <c r="BR131" s="12"/>
-    </row>
-    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN131" s="12"/>
+      <c r="BQ131" s="12"/>
+    </row>
+    <row r="132" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="10"/>
       <c r="E132" s="11"/>
-      <c r="BO132" s="12"/>
-      <c r="BR132" s="12"/>
-    </row>
-    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN132" s="12"/>
+      <c r="BQ132" s="12"/>
+    </row>
+    <row r="133" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="10"/>
       <c r="E133" s="11"/>
-      <c r="BO133" s="12"/>
-      <c r="BR133" s="12"/>
-    </row>
-    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN133" s="12"/>
+      <c r="BQ133" s="12"/>
+    </row>
+    <row r="134" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="10"/>
       <c r="E134" s="11"/>
-      <c r="BO134" s="12"/>
-      <c r="BR134" s="12"/>
-    </row>
-    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN134" s="12"/>
+      <c r="BQ134" s="12"/>
+    </row>
+    <row r="135" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="10"/>
       <c r="E135" s="11"/>
-      <c r="BO135" s="12"/>
-      <c r="BR135" s="12"/>
-    </row>
-    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN135" s="12"/>
+      <c r="BQ135" s="12"/>
+    </row>
+    <row r="136" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="10"/>
       <c r="E136" s="11"/>
-      <c r="BO136" s="12"/>
-      <c r="BR136" s="12"/>
-    </row>
-    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN136" s="12"/>
+      <c r="BQ136" s="12"/>
+    </row>
+    <row r="137" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="10"/>
       <c r="E137" s="11"/>
-      <c r="BO137" s="12"/>
-      <c r="BR137" s="12"/>
-    </row>
-    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN137" s="12"/>
+      <c r="BQ137" s="12"/>
+    </row>
+    <row r="138" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="10"/>
       <c r="E138" s="11"/>
-      <c r="BO138" s="12"/>
-      <c r="BR138" s="12"/>
-    </row>
-    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN138" s="12"/>
+      <c r="BQ138" s="12"/>
+    </row>
+    <row r="139" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="10"/>
       <c r="E139" s="11"/>
-      <c r="BO139" s="12"/>
-      <c r="BR139" s="12"/>
-    </row>
-    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN139" s="12"/>
+      <c r="BQ139" s="12"/>
+    </row>
+    <row r="140" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="10"/>
       <c r="E140" s="11"/>
-      <c r="BO140" s="12"/>
-      <c r="BR140" s="12"/>
-    </row>
-    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN140" s="12"/>
+      <c r="BQ140" s="12"/>
+    </row>
+    <row r="141" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="10"/>
       <c r="E141" s="11"/>
-      <c r="BO141" s="12"/>
-      <c r="BR141" s="12"/>
-    </row>
-    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN141" s="12"/>
+      <c r="BQ141" s="12"/>
+    </row>
+    <row r="142" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="10"/>
       <c r="E142" s="11"/>
-      <c r="BO142" s="12"/>
-      <c r="BR142" s="12"/>
-    </row>
-    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN142" s="12"/>
+      <c r="BQ142" s="12"/>
+    </row>
+    <row r="143" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="10"/>
       <c r="E143" s="11"/>
-      <c r="BO143" s="12"/>
-      <c r="BR143" s="12"/>
-    </row>
-    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN143" s="12"/>
+      <c r="BQ143" s="12"/>
+    </row>
+    <row r="144" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="10"/>
       <c r="E144" s="11"/>
-      <c r="BO144" s="12"/>
-      <c r="BR144" s="12"/>
-    </row>
-    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN144" s="12"/>
+      <c r="BQ144" s="12"/>
+    </row>
+    <row r="145" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="10"/>
       <c r="E145" s="11"/>
-      <c r="BO145" s="12"/>
-      <c r="BR145" s="12"/>
-    </row>
-    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN145" s="12"/>
+      <c r="BQ145" s="12"/>
+    </row>
+    <row r="146" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="10"/>
       <c r="E146" s="11"/>
-      <c r="BO146" s="12"/>
-      <c r="BR146" s="12"/>
-    </row>
-    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN146" s="12"/>
+      <c r="BQ146" s="12"/>
+    </row>
+    <row r="147" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="10"/>
       <c r="E147" s="11"/>
-      <c r="BO147" s="12"/>
-      <c r="BR147" s="12"/>
-    </row>
-    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN147" s="12"/>
+      <c r="BQ147" s="12"/>
+    </row>
+    <row r="148" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="10"/>
       <c r="E148" s="11"/>
-      <c r="BO148" s="12"/>
-      <c r="BR148" s="12"/>
-    </row>
-    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN148" s="12"/>
+      <c r="BQ148" s="12"/>
+    </row>
+    <row r="149" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="10"/>
       <c r="E149" s="11"/>
-      <c r="BO149" s="12"/>
-      <c r="BR149" s="12"/>
-    </row>
-    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN149" s="12"/>
+      <c r="BQ149" s="12"/>
+    </row>
+    <row r="150" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="10"/>
       <c r="E150" s="11"/>
-      <c r="BO150" s="12"/>
-      <c r="BR150" s="12"/>
-    </row>
-    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN150" s="12"/>
+      <c r="BQ150" s="12"/>
+    </row>
+    <row r="151" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="10"/>
       <c r="E151" s="11"/>
-      <c r="BO151" s="12"/>
-      <c r="BR151" s="12"/>
-    </row>
-    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN151" s="12"/>
+      <c r="BQ151" s="12"/>
+    </row>
+    <row r="152" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="10"/>
       <c r="E152" s="11"/>
-      <c r="BO152" s="12"/>
-      <c r="BR152" s="12"/>
-    </row>
-    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN152" s="12"/>
+      <c r="BQ152" s="12"/>
+    </row>
+    <row r="153" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="10"/>
       <c r="E153" s="11"/>
-      <c r="BO153" s="12"/>
-      <c r="BR153" s="12"/>
-    </row>
-    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN153" s="12"/>
+      <c r="BQ153" s="12"/>
+    </row>
+    <row r="154" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="10"/>
       <c r="E154" s="11"/>
-      <c r="BO154" s="12"/>
-      <c r="BR154" s="12"/>
-    </row>
-    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN154" s="12"/>
+      <c r="BQ154" s="12"/>
+    </row>
+    <row r="155" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="10"/>
       <c r="E155" s="11"/>
-      <c r="BO155" s="12"/>
-      <c r="BR155" s="12"/>
-    </row>
-    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN155" s="12"/>
+      <c r="BQ155" s="12"/>
+    </row>
+    <row r="156" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="10"/>
       <c r="E156" s="11"/>
-      <c r="BO156" s="12"/>
-      <c r="BR156" s="12"/>
-    </row>
-    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN156" s="12"/>
+      <c r="BQ156" s="12"/>
+    </row>
+    <row r="157" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="10"/>
       <c r="E157" s="11"/>
-      <c r="BO157" s="12"/>
-      <c r="BR157" s="12"/>
-    </row>
-    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN157" s="12"/>
+      <c r="BQ157" s="12"/>
+    </row>
+    <row r="158" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="10"/>
       <c r="E158" s="11"/>
-      <c r="BO158" s="12"/>
-      <c r="BR158" s="12"/>
-    </row>
-    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN158" s="12"/>
+      <c r="BQ158" s="12"/>
+    </row>
+    <row r="159" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="10"/>
       <c r="E159" s="11"/>
-      <c r="BO159" s="12"/>
-      <c r="BR159" s="12"/>
-    </row>
-    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN159" s="12"/>
+      <c r="BQ159" s="12"/>
+    </row>
+    <row r="160" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="10"/>
       <c r="E160" s="11"/>
-      <c r="BO160" s="12"/>
-      <c r="BR160" s="12"/>
-    </row>
-    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN160" s="12"/>
+      <c r="BQ160" s="12"/>
+    </row>
+    <row r="161" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="10"/>
       <c r="E161" s="11"/>
-      <c r="BO161" s="12"/>
-      <c r="BR161" s="12"/>
-    </row>
-    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN161" s="12"/>
+      <c r="BQ161" s="12"/>
+    </row>
+    <row r="162" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="10"/>
       <c r="E162" s="11"/>
-      <c r="BO162" s="12"/>
-      <c r="BR162" s="12"/>
-    </row>
-    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN162" s="12"/>
+      <c r="BQ162" s="12"/>
+    </row>
+    <row r="163" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="10"/>
       <c r="E163" s="11"/>
-      <c r="BO163" s="12"/>
-      <c r="BR163" s="12"/>
-    </row>
-    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN163" s="12"/>
+      <c r="BQ163" s="12"/>
+    </row>
+    <row r="164" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="10"/>
       <c r="E164" s="11"/>
-      <c r="BO164" s="12"/>
-      <c r="BR164" s="12"/>
-    </row>
-    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN164" s="12"/>
+      <c r="BQ164" s="12"/>
+    </row>
+    <row r="165" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="10"/>
       <c r="E165" s="11"/>
-      <c r="BO165" s="12"/>
-      <c r="BR165" s="12"/>
-    </row>
-    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN165" s="12"/>
+      <c r="BQ165" s="12"/>
+    </row>
+    <row r="166" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="10"/>
       <c r="E166" s="11"/>
-      <c r="BO166" s="12"/>
-      <c r="BR166" s="12"/>
-    </row>
-    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN166" s="12"/>
+      <c r="BQ166" s="12"/>
+    </row>
+    <row r="167" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="10"/>
       <c r="E167" s="11"/>
-      <c r="BO167" s="12"/>
-      <c r="BR167" s="12"/>
-    </row>
-    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN167" s="12"/>
+      <c r="BQ167" s="12"/>
+    </row>
+    <row r="168" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="10"/>
       <c r="E168" s="11"/>
-      <c r="BO168" s="12"/>
-      <c r="BR168" s="12"/>
-    </row>
-    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN168" s="12"/>
+      <c r="BQ168" s="12"/>
+    </row>
+    <row r="169" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="10"/>
       <c r="E169" s="11"/>
-      <c r="BO169" s="12"/>
-      <c r="BR169" s="12"/>
-    </row>
-    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN169" s="12"/>
+      <c r="BQ169" s="12"/>
+    </row>
+    <row r="170" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="10"/>
       <c r="E170" s="11"/>
-      <c r="BO170" s="12"/>
-      <c r="BR170" s="12"/>
-    </row>
-    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN170" s="12"/>
+      <c r="BQ170" s="12"/>
+    </row>
+    <row r="171" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="10"/>
       <c r="E171" s="11"/>
-      <c r="BO171" s="12"/>
-      <c r="BR171" s="12"/>
-    </row>
-    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN171" s="12"/>
+      <c r="BQ171" s="12"/>
+    </row>
+    <row r="172" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="10"/>
       <c r="E172" s="11"/>
-      <c r="BO172" s="12"/>
-      <c r="BR172" s="12"/>
-    </row>
-    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN172" s="12"/>
+      <c r="BQ172" s="12"/>
+    </row>
+    <row r="173" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="10"/>
       <c r="E173" s="11"/>
-      <c r="BO173" s="12"/>
-      <c r="BR173" s="12"/>
-    </row>
-    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN173" s="12"/>
+      <c r="BQ173" s="12"/>
+    </row>
+    <row r="174" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="10"/>
       <c r="E174" s="11"/>
-      <c r="BO174" s="12"/>
-      <c r="BR174" s="12"/>
-    </row>
-    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN174" s="12"/>
+      <c r="BQ174" s="12"/>
+    </row>
+    <row r="175" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="10"/>
       <c r="E175" s="11"/>
-      <c r="BO175" s="12"/>
-      <c r="BR175" s="12"/>
-    </row>
-    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN175" s="12"/>
+      <c r="BQ175" s="12"/>
+    </row>
+    <row r="176" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="10"/>
       <c r="E176" s="11"/>
-      <c r="BO176" s="12"/>
-      <c r="BR176" s="12"/>
-    </row>
-    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN176" s="12"/>
+      <c r="BQ176" s="12"/>
+    </row>
+    <row r="177" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="10"/>
       <c r="E177" s="11"/>
-      <c r="BO177" s="12"/>
-      <c r="BR177" s="12"/>
-    </row>
-    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN177" s="12"/>
+      <c r="BQ177" s="12"/>
+    </row>
+    <row r="178" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="10"/>
       <c r="E178" s="11"/>
-      <c r="BO178" s="12"/>
-      <c r="BR178" s="12"/>
-    </row>
-    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN178" s="12"/>
+      <c r="BQ178" s="12"/>
+    </row>
+    <row r="179" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="10"/>
       <c r="E179" s="11"/>
-      <c r="BO179" s="12"/>
-      <c r="BR179" s="12"/>
-    </row>
-    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN179" s="12"/>
+      <c r="BQ179" s="12"/>
+    </row>
+    <row r="180" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="10"/>
       <c r="E180" s="11"/>
-      <c r="BO180" s="12"/>
-      <c r="BR180" s="12"/>
-    </row>
-    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN180" s="12"/>
+      <c r="BQ180" s="12"/>
+    </row>
+    <row r="181" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="10"/>
       <c r="E181" s="11"/>
-      <c r="BO181" s="12"/>
-      <c r="BR181" s="12"/>
-    </row>
-    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN181" s="12"/>
+      <c r="BQ181" s="12"/>
+    </row>
+    <row r="182" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="10"/>
       <c r="E182" s="11"/>
-      <c r="BO182" s="12"/>
-      <c r="BR182" s="12"/>
-    </row>
-    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN182" s="12"/>
+      <c r="BQ182" s="12"/>
+    </row>
+    <row r="183" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="10"/>
       <c r="E183" s="11"/>
-      <c r="BO183" s="12"/>
-      <c r="BR183" s="12"/>
-    </row>
-    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN183" s="12"/>
+      <c r="BQ183" s="12"/>
+    </row>
+    <row r="184" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="10"/>
       <c r="E184" s="11"/>
-      <c r="BO184" s="12"/>
-      <c r="BR184" s="12"/>
-    </row>
-    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN184" s="12"/>
+      <c r="BQ184" s="12"/>
+    </row>
+    <row r="185" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="10"/>
       <c r="E185" s="11"/>
-      <c r="BO185" s="12"/>
-      <c r="BR185" s="12"/>
-    </row>
-    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN185" s="12"/>
+      <c r="BQ185" s="12"/>
+    </row>
+    <row r="186" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="10"/>
       <c r="E186" s="11"/>
-      <c r="BO186" s="12"/>
-      <c r="BR186" s="12"/>
-    </row>
-    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN186" s="12"/>
+      <c r="BQ186" s="12"/>
+    </row>
+    <row r="187" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="10"/>
       <c r="E187" s="11"/>
-      <c r="BO187" s="12"/>
-      <c r="BR187" s="12"/>
-    </row>
-    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN187" s="12"/>
+      <c r="BQ187" s="12"/>
+    </row>
+    <row r="188" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="10"/>
       <c r="E188" s="11"/>
-      <c r="BO188" s="12"/>
-      <c r="BR188" s="12"/>
-    </row>
-    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN188" s="12"/>
+      <c r="BQ188" s="12"/>
+    </row>
+    <row r="189" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="10"/>
       <c r="E189" s="11"/>
-      <c r="BO189" s="12"/>
-      <c r="BR189" s="12"/>
-    </row>
-    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN189" s="12"/>
+      <c r="BQ189" s="12"/>
+    </row>
+    <row r="190" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="10"/>
       <c r="E190" s="11"/>
-      <c r="BO190" s="12"/>
-      <c r="BR190" s="12"/>
-    </row>
-    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN190" s="12"/>
+      <c r="BQ190" s="12"/>
+    </row>
+    <row r="191" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="10"/>
       <c r="E191" s="11"/>
-      <c r="BO191" s="12"/>
-      <c r="BR191" s="12"/>
-    </row>
-    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN191" s="12"/>
+      <c r="BQ191" s="12"/>
+    </row>
+    <row r="192" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="10"/>
       <c r="E192" s="11"/>
-      <c r="BO192" s="12"/>
-      <c r="BR192" s="12"/>
-    </row>
-    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN192" s="12"/>
+      <c r="BQ192" s="12"/>
+    </row>
+    <row r="193" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="10"/>
       <c r="E193" s="11"/>
-      <c r="BO193" s="12"/>
-      <c r="BR193" s="12"/>
-    </row>
-    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN193" s="12"/>
+      <c r="BQ193" s="12"/>
+    </row>
+    <row r="194" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="10"/>
       <c r="E194" s="11"/>
-      <c r="BO194" s="12"/>
-      <c r="BR194" s="12"/>
-    </row>
-    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN194" s="12"/>
+      <c r="BQ194" s="12"/>
+    </row>
+    <row r="195" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="10"/>
       <c r="E195" s="11"/>
-      <c r="BO195" s="12"/>
-      <c r="BR195" s="12"/>
-    </row>
-    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN195" s="12"/>
+      <c r="BQ195" s="12"/>
+    </row>
+    <row r="196" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="10"/>
       <c r="E196" s="11"/>
-      <c r="BO196" s="12"/>
-      <c r="BR196" s="12"/>
-    </row>
-    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN196" s="12"/>
+      <c r="BQ196" s="12"/>
+    </row>
+    <row r="197" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="10"/>
       <c r="E197" s="11"/>
-      <c r="BO197" s="12"/>
-      <c r="BR197" s="12"/>
-    </row>
-    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN197" s="12"/>
+      <c r="BQ197" s="12"/>
+    </row>
+    <row r="198" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="10"/>
       <c r="E198" s="11"/>
-      <c r="BO198" s="12"/>
-      <c r="BR198" s="12"/>
-    </row>
-    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN198" s="12"/>
+      <c r="BQ198" s="12"/>
+    </row>
+    <row r="199" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="10"/>
       <c r="E199" s="11"/>
-      <c r="BO199" s="12"/>
-      <c r="BR199" s="12"/>
-    </row>
-    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN199" s="12"/>
+      <c r="BQ199" s="12"/>
+    </row>
+    <row r="200" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="10"/>
       <c r="E200" s="11"/>
-      <c r="BO200" s="12"/>
-      <c r="BR200" s="12"/>
-    </row>
-    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN200" s="12"/>
+      <c r="BQ200" s="12"/>
+    </row>
+    <row r="201" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="10"/>
       <c r="E201" s="11"/>
-      <c r="BO201" s="12"/>
-      <c r="BR201" s="12"/>
-    </row>
-    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN201" s="12"/>
+      <c r="BQ201" s="12"/>
+    </row>
+    <row r="202" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="10"/>
       <c r="E202" s="11"/>
-      <c r="BO202" s="12"/>
-      <c r="BR202" s="12"/>
-    </row>
-    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN202" s="12"/>
+      <c r="BQ202" s="12"/>
+    </row>
+    <row r="203" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="10"/>
       <c r="E203" s="11"/>
-      <c r="BO203" s="12"/>
-      <c r="BR203" s="12"/>
-    </row>
-    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN203" s="12"/>
+      <c r="BQ203" s="12"/>
+    </row>
+    <row r="204" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="10"/>
       <c r="E204" s="11"/>
-      <c r="BO204" s="12"/>
-      <c r="BR204" s="12"/>
-    </row>
-    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN204" s="12"/>
+      <c r="BQ204" s="12"/>
+    </row>
+    <row r="205" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="10"/>
       <c r="E205" s="11"/>
-      <c r="BO205" s="12"/>
-      <c r="BR205" s="12"/>
-    </row>
-    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN205" s="12"/>
+      <c r="BQ205" s="12"/>
+    </row>
+    <row r="206" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="10"/>
       <c r="E206" s="11"/>
-      <c r="BO206" s="12"/>
-      <c r="BR206" s="12"/>
-    </row>
-    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN206" s="12"/>
+      <c r="BQ206" s="12"/>
+    </row>
+    <row r="207" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="10"/>
       <c r="E207" s="11"/>
-      <c r="BO207" s="12"/>
-      <c r="BR207" s="12"/>
-    </row>
-    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN207" s="12"/>
+      <c r="BQ207" s="12"/>
+    </row>
+    <row r="208" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="10"/>
       <c r="E208" s="11"/>
-      <c r="BO208" s="12"/>
-      <c r="BR208" s="12"/>
-    </row>
-    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN208" s="12"/>
+      <c r="BQ208" s="12"/>
+    </row>
+    <row r="209" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="10"/>
       <c r="E209" s="11"/>
-      <c r="BO209" s="12"/>
-      <c r="BR209" s="12"/>
-    </row>
-    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN209" s="12"/>
+      <c r="BQ209" s="12"/>
+    </row>
+    <row r="210" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="10"/>
       <c r="E210" s="11"/>
-      <c r="BO210" s="12"/>
-      <c r="BR210" s="12"/>
-    </row>
-    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN210" s="12"/>
+      <c r="BQ210" s="12"/>
+    </row>
+    <row r="211" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="10"/>
       <c r="E211" s="11"/>
-      <c r="BO211" s="12"/>
-      <c r="BR211" s="12"/>
-    </row>
-    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN211" s="12"/>
+      <c r="BQ211" s="12"/>
+    </row>
+    <row r="212" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="10"/>
       <c r="E212" s="11"/>
-      <c r="BO212" s="12"/>
-      <c r="BR212" s="12"/>
-    </row>
-    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN212" s="12"/>
+      <c r="BQ212" s="12"/>
+    </row>
+    <row r="213" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="10"/>
       <c r="E213" s="11"/>
-      <c r="BO213" s="12"/>
-      <c r="BR213" s="12"/>
-    </row>
-    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN213" s="12"/>
+      <c r="BQ213" s="12"/>
+    </row>
+    <row r="214" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="10"/>
       <c r="E214" s="11"/>
-      <c r="BO214" s="12"/>
-      <c r="BR214" s="12"/>
-    </row>
-    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN214" s="12"/>
+      <c r="BQ214" s="12"/>
+    </row>
+    <row r="215" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="10"/>
       <c r="E215" s="11"/>
-      <c r="BO215" s="12"/>
-      <c r="BR215" s="12"/>
-    </row>
-    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN215" s="12"/>
+      <c r="BQ215" s="12"/>
+    </row>
+    <row r="216" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="10"/>
       <c r="E216" s="11"/>
-      <c r="BO216" s="12"/>
-      <c r="BR216" s="12"/>
-    </row>
-    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN216" s="12"/>
+      <c r="BQ216" s="12"/>
+    </row>
+    <row r="217" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="10"/>
       <c r="E217" s="11"/>
-      <c r="BR217" s="12"/>
-    </row>
-    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ217" s="12"/>
+    </row>
+    <row r="218" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="10"/>
       <c r="E218" s="11"/>
-      <c r="BO218" s="12"/>
-      <c r="BR218" s="12"/>
-    </row>
-    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN218" s="12"/>
+      <c r="BQ218" s="12"/>
+    </row>
+    <row r="219" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="10"/>
       <c r="E219" s="11"/>
-      <c r="BO219" s="12"/>
-      <c r="BR219" s="12"/>
-    </row>
-    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN219" s="12"/>
+      <c r="BQ219" s="12"/>
+    </row>
+    <row r="220" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="10"/>
       <c r="E220" s="11"/>
-      <c r="BO220" s="12"/>
-      <c r="BR220" s="12"/>
-    </row>
-    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN220" s="12"/>
+      <c r="BQ220" s="12"/>
+    </row>
+    <row r="221" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="10"/>
       <c r="E221" s="11"/>
-      <c r="BO221" s="12"/>
-      <c r="BR221" s="12"/>
-    </row>
-    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN221" s="12"/>
+      <c r="BQ221" s="12"/>
+    </row>
+    <row r="222" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="10"/>
       <c r="E222" s="11"/>
-      <c r="BO222" s="12"/>
-      <c r="BR222" s="12"/>
-    </row>
-    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN222" s="12"/>
+      <c r="BQ222" s="12"/>
+    </row>
+    <row r="223" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="10"/>
       <c r="E223" s="11"/>
-      <c r="BO223" s="12"/>
-      <c r="BR223" s="12"/>
-    </row>
-    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN223" s="12"/>
+      <c r="BQ223" s="12"/>
+    </row>
+    <row r="224" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="10"/>
       <c r="E224" s="11"/>
-      <c r="BO224" s="12"/>
-      <c r="BR224" s="12"/>
-    </row>
-    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN224" s="12"/>
+      <c r="BQ224" s="12"/>
+    </row>
+    <row r="225" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="10"/>
       <c r="E225" s="11"/>
-      <c r="BO225" s="12"/>
-      <c r="BR225" s="12"/>
-    </row>
-    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN225" s="12"/>
+      <c r="BQ225" s="12"/>
+    </row>
+    <row r="226" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="10"/>
       <c r="E226" s="11"/>
-      <c r="BO226" s="12"/>
-      <c r="BR226" s="12"/>
-    </row>
-    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN226" s="12"/>
+      <c r="BQ226" s="12"/>
+    </row>
+    <row r="227" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="10"/>
       <c r="E227" s="11"/>
-      <c r="BO227" s="12"/>
-      <c r="BR227" s="12"/>
-    </row>
-    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN227" s="12"/>
+      <c r="BQ227" s="12"/>
+    </row>
+    <row r="228" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="10"/>
       <c r="E228" s="11"/>
-      <c r="BO228" s="12"/>
-      <c r="BR228" s="12"/>
-    </row>
-    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN228" s="12"/>
+      <c r="BQ228" s="12"/>
+    </row>
+    <row r="229" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="10"/>
       <c r="E229" s="11"/>
-      <c r="BO229" s="12"/>
-      <c r="BR229" s="12"/>
-    </row>
-    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN229" s="12"/>
+      <c r="BQ229" s="12"/>
+    </row>
+    <row r="230" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="10"/>
       <c r="E230" s="11"/>
-      <c r="BO230" s="12"/>
-      <c r="BR230" s="12"/>
-    </row>
-    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN230" s="12"/>
+      <c r="BQ230" s="12"/>
+    </row>
+    <row r="231" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="10"/>
       <c r="E231" s="11"/>
-      <c r="BO231" s="12"/>
-      <c r="BR231" s="12"/>
-    </row>
-    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN231" s="12"/>
+      <c r="BQ231" s="12"/>
+    </row>
+    <row r="232" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="10"/>
       <c r="E232" s="11"/>
-      <c r="BO232" s="12"/>
-      <c r="BR232" s="12"/>
-    </row>
-    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN232" s="12"/>
+      <c r="BQ232" s="12"/>
+    </row>
+    <row r="233" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="10"/>
       <c r="E233" s="11"/>
-      <c r="BO233" s="12"/>
-      <c r="BR233" s="12"/>
-    </row>
-    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN233" s="12"/>
+      <c r="BQ233" s="12"/>
+    </row>
+    <row r="234" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="10"/>
       <c r="E234" s="11"/>
-      <c r="BO234" s="12"/>
-      <c r="BR234" s="12"/>
-    </row>
-    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN234" s="12"/>
+      <c r="BQ234" s="12"/>
+    </row>
+    <row r="235" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="10"/>
       <c r="E235" s="11"/>
-      <c r="BO235" s="12"/>
-      <c r="BR235" s="12"/>
-    </row>
-    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN235" s="12"/>
+      <c r="BQ235" s="12"/>
+    </row>
+    <row r="236" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="10"/>
       <c r="E236" s="11"/>
-      <c r="BO236" s="12"/>
-      <c r="BR236" s="12"/>
-    </row>
-    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN236" s="12"/>
+      <c r="BQ236" s="12"/>
+    </row>
+    <row r="237" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="10"/>
       <c r="E237" s="11"/>
-      <c r="BO237" s="12"/>
-      <c r="BR237" s="12"/>
-    </row>
-    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN237" s="12"/>
+      <c r="BQ237" s="12"/>
+    </row>
+    <row r="238" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="10"/>
       <c r="E238" s="11"/>
-      <c r="BO238" s="12"/>
-      <c r="BR238" s="12"/>
-    </row>
-    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN238" s="12"/>
+      <c r="BQ238" s="12"/>
+    </row>
+    <row r="239" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="10"/>
       <c r="E239" s="11"/>
-      <c r="BO239" s="12"/>
-      <c r="BR239" s="12"/>
-    </row>
-    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN239" s="12"/>
+      <c r="BQ239" s="12"/>
+    </row>
+    <row r="240" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="10"/>
       <c r="E240" s="11"/>
-      <c r="BO240" s="12"/>
-      <c r="BR240" s="12"/>
-    </row>
-    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN240" s="12"/>
+      <c r="BQ240" s="12"/>
+    </row>
+    <row r="241" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="10"/>
       <c r="E241" s="11"/>
-      <c r="BO241" s="12"/>
-      <c r="BR241" s="12"/>
-    </row>
-    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN241" s="12"/>
+      <c r="BQ241" s="12"/>
+    </row>
+    <row r="242" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="10"/>
       <c r="E242" s="11"/>
-      <c r="BO242" s="12"/>
-      <c r="BR242" s="12"/>
-    </row>
-    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN242" s="12"/>
+      <c r="BQ242" s="12"/>
+    </row>
+    <row r="243" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="10"/>
       <c r="E243" s="11"/>
-      <c r="BO243" s="12"/>
-      <c r="BR243" s="12"/>
-    </row>
-    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN243" s="12"/>
+      <c r="BQ243" s="12"/>
+    </row>
+    <row r="244" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="10"/>
       <c r="E244" s="11"/>
-      <c r="BO244" s="12"/>
-      <c r="BR244" s="12"/>
-    </row>
-    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN244" s="12"/>
+      <c r="BQ244" s="12"/>
+    </row>
+    <row r="245" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="10"/>
       <c r="E245" s="11"/>
-      <c r="BO245" s="12"/>
-      <c r="BR245" s="12"/>
-    </row>
-    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN245" s="12"/>
+      <c r="BQ245" s="12"/>
+    </row>
+    <row r="246" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="10"/>
       <c r="E246" s="11"/>
-      <c r="BO246" s="12"/>
-      <c r="BR246" s="12"/>
-    </row>
-    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN246" s="12"/>
+      <c r="BQ246" s="12"/>
+    </row>
+    <row r="247" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="10"/>
       <c r="E247" s="11"/>
-      <c r="BO247" s="12"/>
-      <c r="BR247" s="12"/>
-    </row>
-    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN247" s="12"/>
+      <c r="BQ247" s="12"/>
+    </row>
+    <row r="248" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="10"/>
       <c r="E248" s="11"/>
-      <c r="BO248" s="12"/>
-      <c r="BR248" s="12"/>
-    </row>
-    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN248" s="12"/>
+      <c r="BQ248" s="12"/>
+    </row>
+    <row r="249" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="10"/>
       <c r="E249" s="11"/>
-      <c r="BO249" s="12"/>
-      <c r="BR249" s="12"/>
-    </row>
-    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN249" s="12"/>
+      <c r="BQ249" s="12"/>
+    </row>
+    <row r="250" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="10"/>
       <c r="E250" s="11"/>
-      <c r="BO250" s="12"/>
-      <c r="BR250" s="12"/>
-    </row>
-    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN250" s="12"/>
+      <c r="BQ250" s="12"/>
+    </row>
+    <row r="251" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="10"/>
       <c r="E251" s="11"/>
-      <c r="BO251" s="12"/>
-      <c r="BR251" s="12"/>
-    </row>
-    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN251" s="12"/>
+      <c r="BQ251" s="12"/>
+    </row>
+    <row r="252" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="10"/>
       <c r="E252" s="11"/>
-      <c r="BO252" s="12"/>
-      <c r="BR252" s="12"/>
-    </row>
-    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN252" s="12"/>
+      <c r="BQ252" s="12"/>
+    </row>
+    <row r="253" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="10"/>
       <c r="E253" s="11"/>
-      <c r="BO253" s="12"/>
-      <c r="BR253" s="12"/>
-    </row>
-    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN253" s="12"/>
+      <c r="BQ253" s="12"/>
+    </row>
+    <row r="254" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="10"/>
       <c r="E254" s="11"/>
-      <c r="BO254" s="12"/>
-      <c r="BR254" s="12"/>
-    </row>
-    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN254" s="12"/>
+      <c r="BQ254" s="12"/>
+    </row>
+    <row r="255" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="10"/>
       <c r="E255" s="11"/>
-      <c r="BO255" s="12"/>
-      <c r="BR255" s="12"/>
-    </row>
-    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN255" s="12"/>
+      <c r="BQ255" s="12"/>
+    </row>
+    <row r="256" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="10"/>
       <c r="E256" s="11"/>
-      <c r="BO256" s="12"/>
-      <c r="BR256" s="12"/>
-    </row>
-    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN256" s="12"/>
+      <c r="BQ256" s="12"/>
+    </row>
+    <row r="257" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="10"/>
       <c r="E257" s="11"/>
-      <c r="BO257" s="12"/>
-      <c r="BR257" s="12"/>
-    </row>
-    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN257" s="12"/>
+      <c r="BQ257" s="12"/>
+    </row>
+    <row r="258" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="10"/>
       <c r="E258" s="11"/>
-      <c r="BO258" s="12"/>
-      <c r="BR258" s="12"/>
-    </row>
-    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN258" s="12"/>
+      <c r="BQ258" s="12"/>
+    </row>
+    <row r="259" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="10"/>
       <c r="E259" s="11"/>
-      <c r="BO259" s="12"/>
-      <c r="BR259" s="12"/>
-    </row>
-    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN259" s="12"/>
+      <c r="BQ259" s="12"/>
+    </row>
+    <row r="260" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="10"/>
       <c r="E260" s="11"/>
-      <c r="BR260" s="12"/>
-    </row>
-    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ260" s="12"/>
+    </row>
+    <row r="261" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="10"/>
       <c r="E261" s="11"/>
-      <c r="BO261" s="12"/>
-      <c r="BR261" s="12"/>
-    </row>
-    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN261" s="12"/>
+      <c r="BQ261" s="12"/>
+    </row>
+    <row r="262" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="10"/>
       <c r="E262" s="11"/>
-      <c r="BO262" s="12"/>
-      <c r="BR262" s="12"/>
-    </row>
-    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN262" s="12"/>
+      <c r="BQ262" s="12"/>
+    </row>
+    <row r="263" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="10"/>
       <c r="E263" s="11"/>
-      <c r="BO263" s="12"/>
-      <c r="BR263" s="12"/>
-    </row>
-    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN263" s="12"/>
+      <c r="BQ263" s="12"/>
+    </row>
+    <row r="264" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="10"/>
       <c r="E264" s="11"/>
-      <c r="BO264" s="12"/>
-      <c r="BR264" s="12"/>
-    </row>
-    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN264" s="12"/>
+      <c r="BQ264" s="12"/>
+    </row>
+    <row r="265" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="10"/>
       <c r="E265" s="11"/>
-      <c r="BO265" s="12"/>
-      <c r="BR265" s="12"/>
-    </row>
-    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN265" s="12"/>
+      <c r="BQ265" s="12"/>
+    </row>
+    <row r="266" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="10"/>
       <c r="E266" s="11"/>
-      <c r="BO266" s="12"/>
-      <c r="BR266" s="12"/>
-    </row>
-    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN266" s="12"/>
+      <c r="BQ266" s="12"/>
+    </row>
+    <row r="267" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="10"/>
       <c r="E267" s="11"/>
-      <c r="BO267" s="12"/>
-      <c r="BR267" s="12"/>
-    </row>
-    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN267" s="12"/>
+      <c r="BQ267" s="12"/>
+    </row>
+    <row r="268" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="10"/>
       <c r="E268" s="11"/>
-      <c r="BO268" s="12"/>
-      <c r="BR268" s="12"/>
-    </row>
-    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN268" s="12"/>
+      <c r="BQ268" s="12"/>
+    </row>
+    <row r="269" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="10"/>
       <c r="E269" s="11"/>
-      <c r="BO269" s="12"/>
-      <c r="BR269" s="12"/>
-    </row>
-    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN269" s="12"/>
+      <c r="BQ269" s="12"/>
+    </row>
+    <row r="270" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="10"/>
       <c r="E270" s="11"/>
-      <c r="BO270" s="12"/>
-      <c r="BR270" s="12"/>
-    </row>
-    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN270" s="12"/>
+      <c r="BQ270" s="12"/>
+    </row>
+    <row r="271" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="10"/>
       <c r="E271" s="11"/>
-      <c r="BO271" s="12"/>
-      <c r="BR271" s="12"/>
-    </row>
-    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN271" s="12"/>
+      <c r="BQ271" s="12"/>
+    </row>
+    <row r="272" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="10"/>
       <c r="E272" s="11"/>
-      <c r="BO272" s="12"/>
-      <c r="BR272" s="12"/>
-    </row>
-    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN272" s="12"/>
+      <c r="BQ272" s="12"/>
+    </row>
+    <row r="273" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="10"/>
       <c r="E273" s="11"/>
-      <c r="BO273" s="12"/>
-      <c r="BR273" s="12"/>
-    </row>
-    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN273" s="12"/>
+      <c r="BQ273" s="12"/>
+    </row>
+    <row r="274" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="10"/>
       <c r="E274" s="11"/>
-      <c r="BO274" s="12"/>
-      <c r="BR274" s="12"/>
-    </row>
-    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN274" s="12"/>
+      <c r="BQ274" s="12"/>
+    </row>
+    <row r="275" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="10"/>
       <c r="E275" s="11"/>
-      <c r="BO275" s="12"/>
-      <c r="BR275" s="12"/>
-    </row>
-    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN275" s="12"/>
+      <c r="BQ275" s="12"/>
+    </row>
+    <row r="276" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="10"/>
       <c r="E276" s="11"/>
-      <c r="BO276" s="12"/>
-      <c r="BR276" s="12"/>
-    </row>
-    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN276" s="12"/>
+      <c r="BQ276" s="12"/>
+    </row>
+    <row r="277" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="10"/>
       <c r="E277" s="11"/>
-      <c r="BO277" s="12"/>
-      <c r="BR277" s="12"/>
-    </row>
-    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN277" s="12"/>
+      <c r="BQ277" s="12"/>
+    </row>
+    <row r="278" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="10"/>
       <c r="E278" s="11"/>
-      <c r="BO278" s="12"/>
-      <c r="BR278" s="12"/>
-    </row>
-    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN278" s="12"/>
+      <c r="BQ278" s="12"/>
+    </row>
+    <row r="279" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="10"/>
       <c r="E279" s="11"/>
-      <c r="BO279" s="12"/>
-      <c r="BR279" s="12"/>
-    </row>
-    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN279" s="12"/>
+      <c r="BQ279" s="12"/>
+    </row>
+    <row r="280" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="10"/>
       <c r="E280" s="11"/>
-      <c r="BO280" s="12"/>
-      <c r="BR280" s="12"/>
-    </row>
-    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN280" s="12"/>
+      <c r="BQ280" s="12"/>
+    </row>
+    <row r="281" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="10"/>
       <c r="E281" s="11"/>
-      <c r="BO281" s="12"/>
-      <c r="BR281" s="12"/>
-    </row>
-    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN281" s="12"/>
+      <c r="BQ281" s="12"/>
+    </row>
+    <row r="282" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="10"/>
       <c r="E282" s="11"/>
-      <c r="BO282" s="12"/>
-      <c r="BR282" s="12"/>
-    </row>
-    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN282" s="12"/>
+      <c r="BQ282" s="12"/>
+    </row>
+    <row r="283" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="10"/>
       <c r="E283" s="11"/>
-      <c r="BO283" s="12"/>
-      <c r="BR283" s="12"/>
-    </row>
-    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN283" s="12"/>
+      <c r="BQ283" s="12"/>
+    </row>
+    <row r="284" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="10"/>
       <c r="E284" s="11"/>
-      <c r="BO284" s="12"/>
-      <c r="BR284" s="12"/>
-    </row>
-    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN284" s="12"/>
+      <c r="BQ284" s="12"/>
+    </row>
+    <row r="285" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="10"/>
       <c r="E285" s="11"/>
-      <c r="BO285" s="12"/>
-      <c r="BR285" s="12"/>
-    </row>
-    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN285" s="12"/>
+      <c r="BQ285" s="12"/>
+    </row>
+    <row r="286" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="10"/>
       <c r="E286" s="11"/>
-      <c r="BO286" s="12"/>
-      <c r="BR286" s="12"/>
-    </row>
-    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN286" s="12"/>
+      <c r="BQ286" s="12"/>
+    </row>
+    <row r="287" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="10"/>
       <c r="E287" s="11"/>
-      <c r="BO287" s="12"/>
-      <c r="BR287" s="12"/>
-    </row>
-    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN287" s="12"/>
+      <c r="BQ287" s="12"/>
+    </row>
+    <row r="288" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="10"/>
       <c r="E288" s="11"/>
-      <c r="BO288" s="12"/>
-      <c r="BR288" s="12"/>
-    </row>
-    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN288" s="12"/>
+      <c r="BQ288" s="12"/>
+    </row>
+    <row r="289" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="10"/>
       <c r="E289" s="11"/>
-      <c r="BO289" s="12"/>
-      <c r="BR289" s="12"/>
-    </row>
-    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN289" s="12"/>
+      <c r="BQ289" s="12"/>
+    </row>
+    <row r="290" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="10"/>
       <c r="E290" s="11"/>
-      <c r="BO290" s="12"/>
-      <c r="BR290" s="12"/>
-    </row>
-    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN290" s="12"/>
+      <c r="BQ290" s="12"/>
+    </row>
+    <row r="291" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="10"/>
       <c r="E291" s="11"/>
-      <c r="BO291" s="12"/>
-      <c r="BR291" s="12"/>
-    </row>
-    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN291" s="12"/>
+      <c r="BQ291" s="12"/>
+    </row>
+    <row r="292" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="10"/>
       <c r="E292" s="11"/>
-      <c r="BO292" s="12"/>
-      <c r="BR292" s="12"/>
-    </row>
-    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN292" s="12"/>
+      <c r="BQ292" s="12"/>
+    </row>
+    <row r="293" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="10"/>
       <c r="E293" s="11"/>
-      <c r="BO293" s="12"/>
-      <c r="BR293" s="12"/>
-    </row>
-    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN293" s="12"/>
+      <c r="BQ293" s="12"/>
+    </row>
+    <row r="294" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="10"/>
       <c r="E294" s="11"/>
-      <c r="BO294" s="12"/>
-      <c r="BR294" s="12"/>
-    </row>
-    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN294" s="12"/>
+      <c r="BQ294" s="12"/>
+    </row>
+    <row r="295" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="10"/>
       <c r="E295" s="11"/>
-      <c r="BO295" s="12"/>
-      <c r="BR295" s="12"/>
-    </row>
-    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN295" s="12"/>
+      <c r="BQ295" s="12"/>
+    </row>
+    <row r="296" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="10"/>
       <c r="E296" s="11"/>
-      <c r="BO296" s="12"/>
-      <c r="BR296" s="12"/>
-    </row>
-    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN296" s="12"/>
+      <c r="BQ296" s="12"/>
+    </row>
+    <row r="297" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="10"/>
       <c r="E297" s="11"/>
-      <c r="BO297" s="12"/>
-      <c r="BR297" s="12"/>
-    </row>
-    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN297" s="12"/>
+      <c r="BQ297" s="12"/>
+    </row>
+    <row r="298" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="10"/>
       <c r="E298" s="11"/>
-      <c r="BO298" s="12"/>
-      <c r="BR298" s="12"/>
-    </row>
-    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN298" s="12"/>
+      <c r="BQ298" s="12"/>
+    </row>
+    <row r="299" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="10"/>
       <c r="E299" s="11"/>
-      <c r="BO299" s="12"/>
-      <c r="BR299" s="12"/>
-    </row>
-    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN299" s="12"/>
+      <c r="BQ299" s="12"/>
+    </row>
+    <row r="300" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="10"/>
       <c r="E300" s="11"/>
-      <c r="BO300" s="12"/>
-      <c r="BR300" s="12"/>
-    </row>
-    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN300" s="12"/>
+      <c r="BQ300" s="12"/>
+    </row>
+    <row r="301" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="10"/>
       <c r="E301" s="11"/>
-      <c r="BO301" s="12"/>
-      <c r="BR301" s="12"/>
-    </row>
-    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN301" s="12"/>
+      <c r="BQ301" s="12"/>
+    </row>
+    <row r="302" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="10"/>
       <c r="E302" s="11"/>
-      <c r="BO302" s="12"/>
-      <c r="BR302" s="12"/>
-    </row>
-    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN302" s="12"/>
+      <c r="BQ302" s="12"/>
+    </row>
+    <row r="303" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="10"/>
       <c r="E303" s="11"/>
-      <c r="BO303" s="12"/>
-      <c r="BR303" s="12"/>
-    </row>
-    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN303" s="12"/>
+      <c r="BQ303" s="12"/>
+    </row>
+    <row r="304" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="10"/>
       <c r="E304" s="11"/>
-      <c r="BO304" s="12"/>
-      <c r="BR304" s="12"/>
-    </row>
-    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN304" s="12"/>
+      <c r="BQ304" s="12"/>
+    </row>
+    <row r="305" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="10"/>
       <c r="E305" s="11"/>
-      <c r="BO305" s="12"/>
-      <c r="BR305" s="12"/>
-    </row>
-    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN305" s="12"/>
+      <c r="BQ305" s="12"/>
+    </row>
+    <row r="306" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="10"/>
       <c r="E306" s="11"/>
-      <c r="BO306" s="12"/>
-      <c r="BR306" s="12"/>
-    </row>
-    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN306" s="12"/>
+      <c r="BQ306" s="12"/>
+    </row>
+    <row r="307" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="10"/>
       <c r="E307" s="11"/>
-      <c r="BO307" s="12"/>
-      <c r="BR307" s="12"/>
-    </row>
-    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN307" s="12"/>
+      <c r="BQ307" s="12"/>
+    </row>
+    <row r="308" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="10"/>
       <c r="E308" s="11"/>
-      <c r="BO308" s="12"/>
-      <c r="BR308" s="12"/>
-    </row>
-    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN308" s="12"/>
+      <c r="BQ308" s="12"/>
+    </row>
+    <row r="309" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="10"/>
       <c r="E309" s="11"/>
-      <c r="BO309" s="12"/>
-      <c r="BR309" s="12"/>
-    </row>
-    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN309" s="12"/>
+      <c r="BQ309" s="12"/>
+    </row>
+    <row r="310" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="10"/>
       <c r="E310" s="11"/>
-      <c r="BO310" s="12"/>
-      <c r="BR310" s="12"/>
-    </row>
-    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN310" s="12"/>
+      <c r="BQ310" s="12"/>
+    </row>
+    <row r="311" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="10"/>
       <c r="E311" s="11"/>
-      <c r="BO311" s="12"/>
-      <c r="BR311" s="12"/>
-    </row>
-    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN311" s="12"/>
+      <c r="BQ311" s="12"/>
+    </row>
+    <row r="312" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="10"/>
       <c r="E312" s="11"/>
-      <c r="BO312" s="12"/>
-      <c r="BR312" s="12"/>
-    </row>
-    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN312" s="12"/>
+      <c r="BQ312" s="12"/>
+    </row>
+    <row r="313" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="10"/>
       <c r="E313" s="11"/>
-      <c r="BO313" s="12"/>
-      <c r="BR313" s="12"/>
-    </row>
-    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN313" s="12"/>
+      <c r="BQ313" s="12"/>
+    </row>
+    <row r="314" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="10"/>
       <c r="E314" s="11"/>
-      <c r="BO314" s="12"/>
-      <c r="BR314" s="12"/>
-    </row>
-    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN314" s="12"/>
+      <c r="BQ314" s="12"/>
+    </row>
+    <row r="315" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="10"/>
       <c r="E315" s="11"/>
-      <c r="BO315" s="12"/>
-      <c r="BR315" s="12"/>
-    </row>
-    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN315" s="12"/>
+      <c r="BQ315" s="12"/>
+    </row>
+    <row r="316" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="10"/>
       <c r="E316" s="11"/>
-      <c r="BR316" s="12"/>
-    </row>
-    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ316" s="12"/>
+    </row>
+    <row r="317" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="10"/>
       <c r="E317" s="11"/>
-      <c r="BR317" s="12"/>
-    </row>
-    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ317" s="12"/>
+    </row>
+    <row r="318" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="10"/>
       <c r="E318" s="11"/>
-      <c r="BR318" s="12"/>
-    </row>
-    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ318" s="12"/>
+    </row>
+    <row r="319" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="10"/>
       <c r="E319" s="11"/>
-      <c r="BO319" s="12"/>
-      <c r="BR319" s="12"/>
-    </row>
-    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN319" s="12"/>
+      <c r="BQ319" s="12"/>
+    </row>
+    <row r="320" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="10"/>
       <c r="E320" s="11"/>
-      <c r="BO320" s="12"/>
-      <c r="BR320" s="12"/>
-    </row>
-    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN320" s="12"/>
+      <c r="BQ320" s="12"/>
+    </row>
+    <row r="321" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="10"/>
       <c r="E321" s="11"/>
-      <c r="BO321" s="12"/>
-      <c r="BR321" s="12"/>
-    </row>
-    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN321" s="12"/>
+      <c r="BQ321" s="12"/>
+    </row>
+    <row r="322" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="10"/>
       <c r="E322" s="11"/>
-      <c r="BO322" s="12"/>
-      <c r="BR322" s="12"/>
-    </row>
-    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN322" s="12"/>
+      <c r="BQ322" s="12"/>
+    </row>
+    <row r="323" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="10"/>
       <c r="E323" s="11"/>
-      <c r="BO323" s="12"/>
-      <c r="BR323" s="12"/>
-    </row>
-    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN323" s="12"/>
+      <c r="BQ323" s="12"/>
+    </row>
+    <row r="324" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="10"/>
       <c r="E324" s="11"/>
-      <c r="BO324" s="12"/>
-      <c r="BR324" s="12"/>
-    </row>
-    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN324" s="12"/>
+      <c r="BQ324" s="12"/>
+    </row>
+    <row r="325" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="10"/>
       <c r="E325" s="11"/>
-      <c r="BO325" s="12"/>
-      <c r="BR325" s="12"/>
-    </row>
-    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN325" s="12"/>
+      <c r="BQ325" s="12"/>
+    </row>
+    <row r="326" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="10"/>
       <c r="E326" s="11"/>
-      <c r="BO326" s="12"/>
-      <c r="BR326" s="12"/>
-    </row>
-    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN326" s="12"/>
+      <c r="BQ326" s="12"/>
+    </row>
+    <row r="327" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="10"/>
       <c r="E327" s="11"/>
-      <c r="BO327" s="12"/>
-      <c r="BR327" s="12"/>
-    </row>
-    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN327" s="12"/>
+      <c r="BQ327" s="12"/>
+    </row>
+    <row r="328" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="10"/>
       <c r="E328" s="11"/>
-      <c r="BO328" s="12"/>
-      <c r="BR328" s="12"/>
-    </row>
-    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN328" s="12"/>
+      <c r="BQ328" s="12"/>
+    </row>
+    <row r="329" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="10"/>
       <c r="E329" s="11"/>
-      <c r="BO329" s="12"/>
-      <c r="BR329" s="12"/>
-    </row>
-    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN329" s="12"/>
+      <c r="BQ329" s="12"/>
+    </row>
+    <row r="330" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="10"/>
       <c r="E330" s="11"/>
-      <c r="BO330" s="12"/>
-      <c r="BR330" s="12"/>
-    </row>
-    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN330" s="12"/>
+      <c r="BQ330" s="12"/>
+    </row>
+    <row r="331" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="10"/>
       <c r="E331" s="11"/>
-      <c r="BO331" s="12"/>
-      <c r="BR331" s="12"/>
-    </row>
-    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN331" s="12"/>
+      <c r="BQ331" s="12"/>
+    </row>
+    <row r="332" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="10"/>
       <c r="E332" s="11"/>
-      <c r="BO332" s="12"/>
-      <c r="BR332" s="12"/>
-    </row>
-    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN332" s="12"/>
+      <c r="BQ332" s="12"/>
+    </row>
+    <row r="333" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="10"/>
       <c r="E333" s="11"/>
-      <c r="BO333" s="12"/>
-      <c r="BR333" s="12"/>
-    </row>
-    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN333" s="12"/>
+      <c r="BQ333" s="12"/>
+    </row>
+    <row r="334" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="10"/>
       <c r="E334" s="11"/>
-      <c r="BO334" s="12"/>
-      <c r="BR334" s="12"/>
-    </row>
-    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN334" s="12"/>
+      <c r="BQ334" s="12"/>
+    </row>
+    <row r="335" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="10"/>
       <c r="E335" s="11"/>
-      <c r="BO335" s="12"/>
-      <c r="BR335" s="12"/>
-    </row>
-    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN335" s="12"/>
+      <c r="BQ335" s="12"/>
+    </row>
+    <row r="336" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="10"/>
       <c r="E336" s="11"/>
-      <c r="BO336" s="12"/>
-      <c r="BR336" s="12"/>
-    </row>
-    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN336" s="12"/>
+      <c r="BQ336" s="12"/>
+    </row>
+    <row r="337" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="10"/>
       <c r="E337" s="11"/>
-      <c r="BO337" s="12"/>
-      <c r="BR337" s="12"/>
-    </row>
-    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN337" s="12"/>
+      <c r="BQ337" s="12"/>
+    </row>
+    <row r="338" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="10"/>
       <c r="E338" s="11"/>
-      <c r="BO338" s="12"/>
-      <c r="BR338" s="12"/>
-    </row>
-    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN338" s="12"/>
+      <c r="BQ338" s="12"/>
+    </row>
+    <row r="339" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="10"/>
       <c r="E339" s="11"/>
-      <c r="BO339" s="12"/>
-      <c r="BR339" s="12"/>
-    </row>
-    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN339" s="12"/>
+      <c r="BQ339" s="12"/>
+    </row>
+    <row r="340" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="10"/>
       <c r="E340" s="11"/>
-      <c r="BO340" s="12"/>
-      <c r="BR340" s="12"/>
-    </row>
-    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN340" s="12"/>
+      <c r="BQ340" s="12"/>
+    </row>
+    <row r="341" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="10"/>
       <c r="E341" s="11"/>
-      <c r="BO341" s="12"/>
-      <c r="BR341" s="12"/>
-    </row>
-    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN341" s="12"/>
+      <c r="BQ341" s="12"/>
+    </row>
+    <row r="342" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="10"/>
       <c r="E342" s="11"/>
-      <c r="BO342" s="12"/>
-      <c r="BR342" s="12"/>
-    </row>
-    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN342" s="12"/>
+      <c r="BQ342" s="12"/>
+    </row>
+    <row r="343" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="10"/>
       <c r="E343" s="11"/>
-      <c r="BO343" s="12"/>
-      <c r="BR343" s="12"/>
-    </row>
-    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN343" s="12"/>
+      <c r="BQ343" s="12"/>
+    </row>
+    <row r="344" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="10"/>
       <c r="E344" s="11"/>
-      <c r="BO344" s="12"/>
-      <c r="BR344" s="12"/>
-    </row>
-    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN344" s="12"/>
+      <c r="BQ344" s="12"/>
+    </row>
+    <row r="345" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="10"/>
       <c r="E345" s="11"/>
-      <c r="BO345" s="12"/>
-      <c r="BR345" s="12"/>
-    </row>
-    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN345" s="12"/>
+      <c r="BQ345" s="12"/>
+    </row>
+    <row r="346" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="10"/>
       <c r="E346" s="11"/>
-      <c r="BO346" s="12"/>
-      <c r="BR346" s="12"/>
-    </row>
-    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN346" s="12"/>
+      <c r="BQ346" s="12"/>
+    </row>
+    <row r="347" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="10"/>
       <c r="E347" s="11"/>
-      <c r="BO347" s="12"/>
-      <c r="BR347" s="12"/>
-    </row>
-    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN347" s="12"/>
+      <c r="BQ347" s="12"/>
+    </row>
+    <row r="348" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="10"/>
       <c r="E348" s="11"/>
-      <c r="BO348" s="12"/>
-      <c r="BR348" s="12"/>
-    </row>
-    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN348" s="12"/>
+      <c r="BQ348" s="12"/>
+    </row>
+    <row r="349" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="10"/>
       <c r="E349" s="11"/>
-      <c r="BO349" s="12"/>
-      <c r="BR349" s="12"/>
-    </row>
-    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN349" s="12"/>
+      <c r="BQ349" s="12"/>
+    </row>
+    <row r="350" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="10"/>
       <c r="E350" s="11"/>
-      <c r="BO350" s="12"/>
-      <c r="BR350" s="12"/>
-    </row>
-    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN350" s="12"/>
+      <c r="BQ350" s="12"/>
+    </row>
+    <row r="351" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="10"/>
       <c r="E351" s="11"/>
-      <c r="BO351" s="12"/>
-      <c r="BR351" s="12"/>
-    </row>
-    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN351" s="12"/>
+      <c r="BQ351" s="12"/>
+    </row>
+    <row r="352" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="10"/>
       <c r="E352" s="11"/>
-      <c r="BO352" s="12"/>
-      <c r="BR352" s="12"/>
-    </row>
-    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN352" s="12"/>
+      <c r="BQ352" s="12"/>
+    </row>
+    <row r="353" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="10"/>
       <c r="E353" s="11"/>
-      <c r="BR353" s="12"/>
-    </row>
-    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ353" s="12"/>
+    </row>
+    <row r="354" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="10"/>
       <c r="E354" s="11"/>
-      <c r="BR354" s="12"/>
-    </row>
-    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ354" s="12"/>
+    </row>
+    <row r="355" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="10"/>
       <c r="E355" s="11"/>
-      <c r="BO355" s="12"/>
-      <c r="BR355" s="12"/>
-    </row>
-    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN355" s="12"/>
+      <c r="BQ355" s="12"/>
+    </row>
+    <row r="356" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="10"/>
       <c r="E356" s="11"/>
-      <c r="BO356" s="12"/>
-      <c r="BR356" s="12"/>
-    </row>
-    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN356" s="12"/>
+      <c r="BQ356" s="12"/>
+    </row>
+    <row r="357" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="10"/>
       <c r="E357" s="11"/>
-      <c r="BO357" s="12"/>
-      <c r="BR357" s="12"/>
-    </row>
-    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN357" s="12"/>
+      <c r="BQ357" s="12"/>
+    </row>
+    <row r="358" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="10"/>
       <c r="E358" s="11"/>
-      <c r="BO358" s="12"/>
-      <c r="BR358" s="12"/>
-    </row>
-    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN358" s="12"/>
+      <c r="BQ358" s="12"/>
+    </row>
+    <row r="359" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="10"/>
       <c r="E359" s="11"/>
-      <c r="BO359" s="12"/>
-      <c r="BR359" s="12"/>
-    </row>
-    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN359" s="12"/>
+      <c r="BQ359" s="12"/>
+    </row>
+    <row r="360" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="10"/>
       <c r="E360" s="11"/>
-      <c r="BO360" s="12"/>
-      <c r="BR360" s="12"/>
-    </row>
-    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN360" s="12"/>
+      <c r="BQ360" s="12"/>
+    </row>
+    <row r="361" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="10"/>
       <c r="E361" s="11"/>
-      <c r="BO361" s="12"/>
-      <c r="BR361" s="12"/>
-    </row>
-    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN361" s="12"/>
+      <c r="BQ361" s="12"/>
+    </row>
+    <row r="362" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="10"/>
       <c r="E362" s="11"/>
-      <c r="BO362" s="12"/>
-      <c r="BR362" s="12"/>
-    </row>
-    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN362" s="12"/>
+      <c r="BQ362" s="12"/>
+    </row>
+    <row r="363" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="10"/>
       <c r="E363" s="11"/>
-      <c r="BO363" s="12"/>
-      <c r="BR363" s="12"/>
-    </row>
-    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN363" s="12"/>
+      <c r="BQ363" s="12"/>
+    </row>
+    <row r="364" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="10"/>
       <c r="E364" s="11"/>
-      <c r="BO364" s="12"/>
-      <c r="BR364" s="12"/>
-    </row>
-    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN364" s="12"/>
+      <c r="BQ364" s="12"/>
+    </row>
+    <row r="365" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="10"/>
       <c r="E365" s="11"/>
-      <c r="BO365" s="12"/>
-      <c r="BR365" s="12"/>
-    </row>
-    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN365" s="12"/>
+      <c r="BQ365" s="12"/>
+    </row>
+    <row r="366" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="10"/>
       <c r="E366" s="11"/>
-      <c r="BO366" s="12"/>
-      <c r="BR366" s="12"/>
-    </row>
-    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN366" s="12"/>
+      <c r="BQ366" s="12"/>
+    </row>
+    <row r="367" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="10"/>
       <c r="E367" s="11"/>
-      <c r="BO367" s="12"/>
-      <c r="BR367" s="12"/>
-    </row>
-    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN367" s="12"/>
+      <c r="BQ367" s="12"/>
+    </row>
+    <row r="368" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="10"/>
       <c r="E368" s="11"/>
-      <c r="BO368" s="12"/>
-      <c r="BR368" s="12"/>
-    </row>
-    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN368" s="12"/>
+      <c r="BQ368" s="12"/>
+    </row>
+    <row r="369" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="10"/>
       <c r="E369" s="11"/>
-      <c r="BO369" s="12"/>
-      <c r="BR369" s="12"/>
-    </row>
-    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN369" s="12"/>
+      <c r="BQ369" s="12"/>
+    </row>
+    <row r="370" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="10"/>
       <c r="E370" s="11"/>
-      <c r="BO370" s="12"/>
-      <c r="BR370" s="12"/>
-    </row>
-    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN370" s="12"/>
+      <c r="BQ370" s="12"/>
+    </row>
+    <row r="371" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="10"/>
       <c r="E371" s="11"/>
-      <c r="BO371" s="12"/>
-      <c r="BR371" s="12"/>
-    </row>
-    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN371" s="12"/>
+      <c r="BQ371" s="12"/>
+    </row>
+    <row r="372" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="10"/>
       <c r="E372" s="11"/>
-      <c r="BO372" s="12"/>
-      <c r="BR372" s="12"/>
-    </row>
-    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN372" s="12"/>
+      <c r="BQ372" s="12"/>
+    </row>
+    <row r="373" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="10"/>
       <c r="E373" s="11"/>
-      <c r="BO373" s="12"/>
-      <c r="BR373" s="12"/>
-    </row>
-    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN373" s="12"/>
+      <c r="BQ373" s="12"/>
+    </row>
+    <row r="374" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="10"/>
       <c r="E374" s="11"/>
-      <c r="BO374" s="12"/>
-      <c r="BR374" s="12"/>
-    </row>
-    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN374" s="12"/>
+      <c r="BQ374" s="12"/>
+    </row>
+    <row r="375" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="10"/>
       <c r="E375" s="11"/>
-      <c r="BO375" s="12"/>
-      <c r="BR375" s="12"/>
-    </row>
-    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN375" s="12"/>
+      <c r="BQ375" s="12"/>
+    </row>
+    <row r="376" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="10"/>
       <c r="E376" s="11"/>
-      <c r="BO376" s="12"/>
-      <c r="BR376" s="12"/>
-    </row>
-    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN376" s="12"/>
+      <c r="BQ376" s="12"/>
+    </row>
+    <row r="377" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="10"/>
       <c r="E377" s="11"/>
-      <c r="BO377" s="12"/>
-      <c r="BR377" s="12"/>
-    </row>
-    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN377" s="12"/>
+      <c r="BQ377" s="12"/>
+    </row>
+    <row r="378" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="10"/>
       <c r="E378" s="11"/>
-      <c r="BR378" s="12"/>
-    </row>
-    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ378" s="12"/>
+    </row>
+    <row r="379" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="10"/>
       <c r="E379" s="11"/>
-      <c r="BR379" s="12"/>
-    </row>
-    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ379" s="12"/>
+    </row>
+    <row r="380" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="10"/>
       <c r="E380" s="11"/>
-      <c r="BO380" s="12"/>
-      <c r="BR380" s="12"/>
-    </row>
-    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN380" s="12"/>
+      <c r="BQ380" s="12"/>
+    </row>
+    <row r="381" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="10"/>
       <c r="E381" s="11"/>
-      <c r="BO381" s="12"/>
-      <c r="BR381" s="12"/>
-    </row>
-    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN381" s="12"/>
+      <c r="BQ381" s="12"/>
+    </row>
+    <row r="382" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="10"/>
       <c r="E382" s="11"/>
-      <c r="BR382" s="12"/>
-    </row>
-    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ382" s="12"/>
+    </row>
+    <row r="383" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="10"/>
       <c r="E383" s="11"/>
-      <c r="BR383" s="12"/>
-    </row>
-    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ383" s="12"/>
+    </row>
+    <row r="384" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="10"/>
       <c r="E384" s="11"/>
-      <c r="BO384" s="12"/>
-      <c r="BR384" s="12"/>
-    </row>
-    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN384" s="12"/>
+      <c r="BQ384" s="12"/>
+    </row>
+    <row r="385" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="10"/>
       <c r="E385" s="11"/>
-      <c r="BO385" s="12"/>
-      <c r="BR385" s="12"/>
-    </row>
-    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN385" s="12"/>
+      <c r="BQ385" s="12"/>
+    </row>
+    <row r="386" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="10"/>
       <c r="E386" s="11"/>
-      <c r="BO386" s="12"/>
-      <c r="BR386" s="12"/>
-    </row>
-    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN386" s="12"/>
+      <c r="BQ386" s="12"/>
+    </row>
+    <row r="387" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="10"/>
       <c r="E387" s="11"/>
-      <c r="BO387" s="12"/>
-      <c r="BR387" s="12"/>
-    </row>
-    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN387" s="12"/>
+      <c r="BQ387" s="12"/>
+    </row>
+    <row r="388" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="10"/>
       <c r="E388" s="11"/>
-      <c r="BO388" s="12"/>
-      <c r="BR388" s="12"/>
-    </row>
-    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN388" s="12"/>
+      <c r="BQ388" s="12"/>
+    </row>
+    <row r="389" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="10"/>
       <c r="E389" s="11"/>
-      <c r="BO389" s="12"/>
-      <c r="BR389" s="12"/>
-    </row>
-    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN389" s="12"/>
+      <c r="BQ389" s="12"/>
+    </row>
+    <row r="390" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="10"/>
       <c r="E390" s="11"/>
-      <c r="BO390" s="12"/>
-      <c r="BR390" s="12"/>
-    </row>
-    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN390" s="12"/>
+      <c r="BQ390" s="12"/>
+    </row>
+    <row r="391" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="10"/>
       <c r="E391" s="11"/>
-      <c r="BO391" s="12"/>
-      <c r="BR391" s="12"/>
-    </row>
-    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN391" s="12"/>
+      <c r="BQ391" s="12"/>
+    </row>
+    <row r="392" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="10"/>
       <c r="E392" s="11"/>
-      <c r="BO392" s="12"/>
-      <c r="BR392" s="12"/>
-    </row>
-    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN392" s="12"/>
+      <c r="BQ392" s="12"/>
+    </row>
+    <row r="393" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="10"/>
       <c r="E393" s="11"/>
-      <c r="BO393" s="12"/>
-      <c r="BR393" s="12"/>
-    </row>
-    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN393" s="12"/>
+      <c r="BQ393" s="12"/>
+    </row>
+    <row r="394" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="10"/>
       <c r="E394" s="11"/>
-      <c r="BO394" s="12"/>
-      <c r="BR394" s="12"/>
-    </row>
-    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN394" s="12"/>
+      <c r="BQ394" s="12"/>
+    </row>
+    <row r="395" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="10"/>
       <c r="E395" s="11"/>
-      <c r="BO395" s="12"/>
-      <c r="BR395" s="12"/>
-    </row>
-    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN395" s="12"/>
+      <c r="BQ395" s="12"/>
+    </row>
+    <row r="396" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="10"/>
       <c r="E396" s="11"/>
-      <c r="BO396" s="12"/>
-      <c r="BR396" s="12"/>
-    </row>
-    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN396" s="12"/>
+      <c r="BQ396" s="12"/>
+    </row>
+    <row r="397" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="10"/>
       <c r="E397" s="11"/>
-      <c r="BO397" s="12"/>
-      <c r="BR397" s="12"/>
-    </row>
-    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN397" s="12"/>
+      <c r="BQ397" s="12"/>
+    </row>
+    <row r="398" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="10"/>
       <c r="E398" s="11"/>
-      <c r="BO398" s="12"/>
-      <c r="BR398" s="12"/>
-    </row>
-    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN398" s="12"/>
+      <c r="BQ398" s="12"/>
+    </row>
+    <row r="399" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="10"/>
       <c r="E399" s="11"/>
-      <c r="BO399" s="12"/>
-      <c r="BR399" s="12"/>
-    </row>
-    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN399" s="12"/>
+      <c r="BQ399" s="12"/>
+    </row>
+    <row r="400" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="10"/>
       <c r="E400" s="11"/>
-      <c r="BO400" s="12"/>
+      <c r="BN400" s="12"/>
     </row>
     <row r="401" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D401" s="10"/>
@@ -6117,334 +6115,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" t="s">
         <v>143</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>144</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>145</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>146</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="U1" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="Y1" t="s">
         <v>160</v>
       </c>
-      <c r="U1" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="V1" s="3" t="s">
+      <c r="Z1" t="s">
         <v>161</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="AB1" t="s">
         <v>163</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>164</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AD1" t="s">
         <v>165</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AE1" t="s">
         <v>166</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AF1" t="s">
         <v>167</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AG1" t="s">
         <v>168</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AH1" t="s">
         <v>169</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AI1" t="s">
         <v>170</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AJ1" t="s">
         <v>171</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AK1" t="s">
         <v>172</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AL1" t="s">
         <v>173</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AM1" t="s">
         <v>174</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AN1" t="s">
         <v>175</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AO1" t="s">
         <v>176</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AP1" t="s">
         <v>177</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AQ1" t="s">
         <v>178</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AR1" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="AS1" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="AT1" t="s">
         <v>179</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AU1" t="s">
         <v>180</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AV1" t="s">
         <v>181</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AW1" t="s">
         <v>182</v>
       </c>
-      <c r="AR1" s="13" t="s">
-        <v>557</v>
-      </c>
-      <c r="AS1" s="13" t="s">
-        <v>558</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AX1" t="s">
         <v>183</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AY1" t="s">
         <v>184</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AZ1" t="s">
         <v>185</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BA1" t="s">
         <v>186</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BB1" t="s">
         <v>187</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BC1" t="s">
         <v>188</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BD1" t="s">
         <v>189</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BE1" t="s">
         <v>190</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BF1" t="s">
         <v>191</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BG1" t="s">
         <v>192</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BH1" t="s">
         <v>193</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BJ1" t="s">
+        <v>193</v>
+      </c>
+      <c r="BK1" t="s">
         <v>194</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BL1" t="s">
         <v>195</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BM1" t="s">
         <v>196</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BN1" t="s">
         <v>197</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>197</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BO1" t="s">
         <v>198</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BP1" t="s">
         <v>199</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BQ1" t="s">
         <v>200</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BR1" t="s">
         <v>201</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BS1" t="s">
         <v>202</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BT1" t="s">
         <v>203</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BU1" t="s">
         <v>204</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BV1" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BW1" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BX1" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BY1" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="BV1" s="4" t="s">
+      <c r="BZ1" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="BW1" s="4" t="s">
+      <c r="CA1" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="BX1" s="4" t="s">
+      <c r="CB1" t="s">
         <v>211</v>
       </c>
-      <c r="BY1" s="4" t="s">
+      <c r="CC1" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="BZ1" s="4" t="s">
+      <c r="CD1" t="s">
         <v>213</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CE1" t="s">
         <v>214</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CF1" t="s">
         <v>215</v>
       </c>
-      <c r="CC1" s="4" t="s">
+      <c r="CG1" t="s">
         <v>216</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CH1" t="s">
         <v>217</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CI1" t="s">
         <v>218</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CJ1" t="s">
         <v>219</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CK1" t="s">
         <v>220</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CL1" t="s">
         <v>221</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CM1" t="s">
         <v>222</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CN1" t="s">
         <v>223</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CO1" t="s">
         <v>224</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CP1" t="s">
         <v>225</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CQ1" t="s">
         <v>226</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CR1" t="s">
+        <v>203</v>
+      </c>
+      <c r="CS1" t="s">
         <v>227</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CT1" t="s">
         <v>228</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CU1" t="s">
         <v>229</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CV1" t="s">
         <v>230</v>
       </c>
-      <c r="CR1" t="s">
-        <v>207</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CW1" t="s">
         <v>231</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CX1" t="s">
         <v>232</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CY1" t="s">
         <v>233</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CZ1" t="s">
+        <v>232</v>
+      </c>
+      <c r="DA1" t="s">
         <v>234</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DB1" t="s">
         <v>235</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DC1" t="s">
         <v>236</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DD1" t="s">
         <v>237</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>236</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DE1" t="s">
         <v>238</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DF1" t="s">
         <v>239</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DG1" t="s">
         <v>240</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DH1" t="s">
         <v>241</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DI1" t="s">
         <v>242</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>243</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>244</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>245</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6452,337 +6450,337 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I2" t="s">
+        <v>246</v>
+      </c>
+      <c r="J2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>267</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>268</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>269</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>270</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>272</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AR2" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="AS2" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>285</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>286</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>287</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>288</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>289</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>292</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>293</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>294</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>295</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>296</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>297</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>300</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>301</v>
+      </c>
+      <c r="BO2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>249</v>
-      </c>
-      <c r="I2" t="s">
-        <v>250</v>
-      </c>
-      <c r="J2" t="s">
-        <v>251</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>266</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>267</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>269</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>270</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>271</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>272</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>273</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>274</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>276</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>284</v>
-      </c>
-      <c r="AR2" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="AS2" s="13" t="s">
-        <v>560</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>288</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>290</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>292</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>293</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>294</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>295</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>296</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>297</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>300</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>301</v>
-      </c>
-      <c r="BK2" t="s">
+      <c r="BP2" t="s">
         <v>302</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BQ2" t="s">
         <v>303</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BR2" t="s">
         <v>304</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BS2" t="s">
         <v>305</v>
       </c>
-      <c r="BO2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BT2" t="s">
         <v>306</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BU2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV2" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BW2" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BX2" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BY2" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="BU2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BV2" s="4" t="s">
+      <c r="BZ2" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="BW2" s="4" t="s">
+      <c r="CA2" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="BX2" s="4" t="s">
+      <c r="CB2" t="s">
         <v>313</v>
       </c>
-      <c r="BY2" s="4" t="s">
+      <c r="CC2" t="s">
         <v>314</v>
       </c>
-      <c r="BZ2" s="4" t="s">
+      <c r="CD2" t="s">
         <v>315</v>
       </c>
-      <c r="CA2" s="4" t="s">
+      <c r="CE2" t="s">
         <v>316</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CF2" t="s">
         <v>317</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CG2" t="s">
         <v>318</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CH2" t="s">
         <v>319</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CI2" t="s">
         <v>320</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CJ2" t="s">
         <v>321</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CK2" t="s">
         <v>322</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CL2" t="s">
         <v>323</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CM2" t="s">
         <v>324</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CN2" t="s">
         <v>325</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CO2" t="s">
         <v>326</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CP2" t="s">
         <v>327</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CQ2" t="s">
         <v>328</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CR2" t="s">
         <v>329</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CS2" t="s">
         <v>330</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CT2" t="s">
         <v>331</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CU2" t="s">
         <v>332</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CV2" t="s">
         <v>333</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CW2" t="s">
         <v>334</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CX2" t="s">
         <v>335</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CY2" t="s">
         <v>336</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CZ2" t="s">
         <v>337</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="DA2" t="s">
         <v>338</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="DB2" t="s">
         <v>339</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DC2" t="s">
         <v>340</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DD2" t="s">
         <v>341</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DE2" t="s">
         <v>342</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DF2" t="s">
         <v>343</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DG2" t="s">
         <v>344</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DH2" t="s">
         <v>345</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DI2" t="s">
         <v>346</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>347</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>348</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>349</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -6802,338 +6800,338 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>347</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="M3" s="3" t="s">
+      <c r="P3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>350</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI3" t="s">
         <v>118</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>354</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>122</v>
       </c>
       <c r="AJ3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AM3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AN3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AO3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AP3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="13" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AS3" s="13" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AT3" t="s">
+        <v>353</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>354</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>353</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>355</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>356</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BV3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="BW3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="BX3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BY3" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="AU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
+      <c r="BZ3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA3" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CC3" t="s">
         <v>358</v>
       </c>
-      <c r="AY3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>357</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" t="s">
+      <c r="CD3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG3" t="s">
         <v>359</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="CH3" t="s">
         <v>360</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="BX3" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY3" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="BZ3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA3" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>362</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>363</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>364</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="CK3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="CL3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="CM3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CN3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CO3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CP3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CQ3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CR3" t="s">
+        <v>358</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CV3" t="s">
         <v>362</v>
       </c>
-      <c r="CS3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>366</v>
-      </c>
       <c r="CW3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="CX3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="CY3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="CZ3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="DA3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="DB3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="DC3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="DD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DE3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DF3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DG3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DH3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DI3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:113" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C5" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J5" s="3"/>
       <c r="M5"/>
@@ -7152,13 +7150,13 @@
         <v>1</v>
       </c>
       <c r="AO5" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AT5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AX5" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AZ5">
         <v>1</v>
@@ -7167,26 +7165,26 @@
         <v>1</v>
       </c>
       <c r="BP5" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="BV5"/>
       <c r="CB5" t="s">
+        <v>371</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>372</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>373</v>
+      </c>
+      <c r="CI5" t="s">
+        <v>374</v>
+      </c>
+      <c r="CL5" t="s">
         <v>375</v>
       </c>
-      <c r="CG5" t="s">
+      <c r="CN5" t="s">
         <v>376</v>
-      </c>
-      <c r="CH5" t="s">
-        <v>377</v>
-      </c>
-      <c r="CI5" t="s">
-        <v>378</v>
-      </c>
-      <c r="CL5" t="s">
-        <v>379</v>
-      </c>
-      <c r="CN5" t="s">
-        <v>380</v>
       </c>
       <c r="CO5">
         <v>-10</v>
@@ -7198,21 +7196,21 @@
         <v>5</v>
       </c>
       <c r="CY5" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C6" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="M6"/>
       <c r="N6"/>
@@ -7227,7 +7225,7 @@
         <v>1</v>
       </c>
       <c r="AO6" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AW6">
         <v>1</v>
@@ -7237,7 +7235,7 @@
       </c>
       <c r="BV6"/>
       <c r="CN6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="CR6">
         <v>9999</v>
@@ -7248,10 +7246,10 @@
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -7261,7 +7259,7 @@
       <c r="N7"/>
       <c r="P7"/>
       <c r="Q7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
@@ -7274,13 +7272,13 @@
         <v>1</v>
       </c>
       <c r="AO7" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AW7">
         <v>1</v>
       </c>
       <c r="AX7" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AZ7">
         <v>0.65</v>
@@ -7289,29 +7287,29 @@
         <v>99</v>
       </c>
       <c r="BO7" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="BP7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="BS7">
         <v>0.1</v>
       </c>
       <c r="BV7"/>
       <c r="CH7" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="CI7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="CL7" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="CM7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="CN7" s="6" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="CO7" s="3">
         <v>-0.8</v>
@@ -7322,15 +7320,15 @@
         <v>0.8</v>
       </c>
       <c r="CY7" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C8" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -7340,7 +7338,7 @@
       <c r="N8"/>
       <c r="P8"/>
       <c r="Q8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
@@ -7353,7 +7351,7 @@
         <v>1</v>
       </c>
       <c r="AO8" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AW8">
         <v>1</v>
@@ -7363,7 +7361,7 @@
       </c>
       <c r="BV8"/>
       <c r="CN8" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="CO8">
         <v>-10</v>
@@ -7377,23 +7375,23 @@
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C9" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="M9"/>
       <c r="N9"/>
       <c r="P9"/>
       <c r="Q9" s="5" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
@@ -7406,13 +7404,13 @@
         <v>1</v>
       </c>
       <c r="AO9" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AW9">
         <v>1</v>
       </c>
       <c r="AX9" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="AZ9">
         <v>0.6</v>
@@ -7427,33 +7425,33 @@
       <c r="CQ9" s="3"/>
       <c r="CR9" s="3"/>
       <c r="CY9" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C11" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D11" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E11" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F11" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G11">
         <v>3</v>
       </c>
       <c r="J11" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="M11"/>
       <c r="N11"/>
@@ -7465,19 +7463,19 @@
         <v>1</v>
       </c>
       <c r="AG11" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AT11" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BD11">
         <v>1</v>
       </c>
       <c r="BO11" s="13" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="BP11" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="BT11">
         <v>99999</v>
@@ -7492,7 +7490,7 @@
         <v>1</v>
       </c>
       <c r="BY11" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BZ11"/>
       <c r="CA11"/>
@@ -7504,7 +7502,7 @@
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
       <c r="CN11" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="CO11">
         <v>1</v>
@@ -7513,33 +7511,33 @@
         <v>99999</v>
       </c>
       <c r="CU11" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C12" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D12" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E12" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F12" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="J12" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="M12"/>
       <c r="N12"/>
@@ -7551,19 +7549,19 @@
         <v>1</v>
       </c>
       <c r="AG12" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AT12" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BD12">
         <v>1</v>
       </c>
       <c r="BO12" s="13" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="BP12" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="BT12">
         <v>99999</v>
@@ -7578,7 +7576,7 @@
         <v>1</v>
       </c>
       <c r="BY12" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BZ12"/>
       <c r="CA12"/>
@@ -7590,7 +7588,7 @@
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
       <c r="CN12" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="CO12">
         <v>1</v>
@@ -7599,21 +7597,21 @@
         <v>99999</v>
       </c>
       <c r="CU12" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C13" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J13" s="3"/>
       <c r="M13"/>
       <c r="N13"/>
       <c r="O13" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
@@ -7626,13 +7624,13 @@
         <v>1</v>
       </c>
       <c r="AO13" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AT13" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="AX13" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AZ13">
         <v>1</v>
@@ -7641,26 +7639,26 @@
         <v>1</v>
       </c>
       <c r="BP13" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="BV13"/>
       <c r="CB13" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="CG13" t="s">
+        <v>372</v>
+      </c>
+      <c r="CH13" t="s">
+        <v>373</v>
+      </c>
+      <c r="CI13" t="s">
+        <v>374</v>
+      </c>
+      <c r="CL13" t="s">
+        <v>375</v>
+      </c>
+      <c r="CN13" t="s">
         <v>376</v>
-      </c>
-      <c r="CH13" t="s">
-        <v>377</v>
-      </c>
-      <c r="CI13" t="s">
-        <v>378</v>
-      </c>
-      <c r="CL13" t="s">
-        <v>379</v>
-      </c>
-      <c r="CN13" t="s">
-        <v>380</v>
       </c>
       <c r="CO13">
         <v>-10</v>
@@ -7672,23 +7670,23 @@
         <v>5</v>
       </c>
       <c r="CY13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C14" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="H14" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="M14"/>
       <c r="N14"/>
       <c r="O14" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
@@ -7701,13 +7699,13 @@
         <v>1</v>
       </c>
       <c r="AO14" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AW14">
         <v>1</v>
       </c>
       <c r="AX14" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AZ14">
         <v>1</v>
@@ -7716,7 +7714,7 @@
         <v>1</v>
       </c>
       <c r="BP14" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="CB14" s="3"/>
       <c r="CC14" s="3"/>
@@ -7726,10 +7724,10 @@
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="CN14" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="CR14">
         <v>1</v>
@@ -7737,16 +7735,16 @@
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C15" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="M15"/>
       <c r="N15"/>
@@ -7758,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="AG15" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BD15">
         <v>1</v>
@@ -7767,14 +7765,14 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="CB15" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="CC15" s="3"/>
       <c r="CD15" s="3"/>
       <c r="CE15" s="3"/>
       <c r="CF15" s="3"/>
       <c r="CG15" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CH15" s="3"/>
       <c r="CI15" s="3"/>
@@ -7809,28 +7807,28 @@
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C17" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D17" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F17" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="J17" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M17"/>
       <c r="N17"/>
@@ -7842,17 +7840,17 @@
         <v>1</v>
       </c>
       <c r="AG17" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AZ17" s="3"/>
       <c r="BD17">
         <v>1</v>
       </c>
       <c r="BO17" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="BP17" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="BT17">
         <v>20</v>
@@ -7867,7 +7865,7 @@
         <v>1</v>
       </c>
       <c r="BY17" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BZ17"/>
       <c r="CA17"/>
@@ -7879,7 +7877,7 @@
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
       <c r="CN17" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="CO17">
         <v>70</v>
@@ -7888,20 +7886,20 @@
         <v>20</v>
       </c>
       <c r="DC17" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C18" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="M18"/>
       <c r="N18"/>
       <c r="O18" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
@@ -7914,13 +7912,13 @@
         <v>1</v>
       </c>
       <c r="AO18" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AT18" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AX18" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AZ18">
         <v>0.75</v>
@@ -7929,28 +7927,28 @@
         <v>1</v>
       </c>
       <c r="BP18" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="BS18">
         <v>0.5</v>
       </c>
       <c r="CB18" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="CE18" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="CH18" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="CI18" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="CL18" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="CN18" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="CO18">
         <v>-0.04</v>
@@ -7959,21 +7957,21 @@
         <v>0.6</v>
       </c>
       <c r="CY18" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C19" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="M19"/>
       <c r="N19"/>
@@ -7985,14 +7983,14 @@
         <v>1</v>
       </c>
       <c r="AG19" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BD19">
         <v>1</v>
       </c>
       <c r="BV19"/>
       <c r="CN19" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="CO19">
         <v>0.2</v>
@@ -8003,21 +8001,21 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C20" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="M20"/>
       <c r="N20"/>
       <c r="Q20" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
@@ -8030,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="AO20" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AW20">
         <v>1</v>
@@ -8040,7 +8038,7 @@
       </c>
       <c r="BV20"/>
       <c r="CN20" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="CR20">
         <v>9999</v>
@@ -8051,16 +8049,16 @@
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C21" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="M21"/>
       <c r="N21"/>
@@ -8072,7 +8070,7 @@
         <v>1</v>
       </c>
       <c r="AG21" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AZ21" s="3"/>
       <c r="BD21">
@@ -8082,14 +8080,14 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="CB21" s="3" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="CC21" s="3"/>
       <c r="CD21" s="3"/>
       <c r="CE21" s="3"/>
       <c r="CF21" s="3"/>
       <c r="CG21" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CH21" s="3"/>
       <c r="CI21" s="3"/>
@@ -8097,7 +8095,7 @@
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
       <c r="CN21" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="CR21">
         <v>19.7</v>
@@ -8117,10 +8115,10 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -8128,10 +8126,10 @@
       <c r="M22"/>
       <c r="N22"/>
       <c r="O22" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="P22" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
@@ -8141,7 +8139,7 @@
         <v>1</v>
       </c>
       <c r="AG22" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AZ22" s="3"/>
       <c r="BD22">
@@ -8151,14 +8149,14 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="CB22" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="CC22" s="3"/>
       <c r="CD22" s="3"/>
       <c r="CE22" s="3"/>
       <c r="CF22" s="3"/>
       <c r="CG22" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CH22" s="3"/>
       <c r="CI22" s="3"/>
@@ -8191,28 +8189,28 @@
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C24" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D24" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E24" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="F24" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
       <c r="J24" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M24"/>
       <c r="N24"/>
@@ -8224,19 +8222,19 @@
         <v>1</v>
       </c>
       <c r="AG24" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AT24" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="BD24">
         <v>1</v>
       </c>
       <c r="BO24" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="BP24" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="BT24">
         <v>30</v>
@@ -8251,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="BY24" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BZ24"/>
       <c r="CA24"/>
@@ -8263,7 +8261,7 @@
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
       <c r="CN24" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="CO24">
         <v>3</v>
@@ -8272,26 +8270,26 @@
         <v>30</v>
       </c>
       <c r="CU24" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="DB24" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="DC24" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C25" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="M25"/>
       <c r="N25"/>
       <c r="O25" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
@@ -8304,13 +8302,13 @@
         <v>1</v>
       </c>
       <c r="AO25" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AT25" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="AX25" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AZ25">
         <v>1</v>
@@ -8319,25 +8317,25 @@
         <v>4</v>
       </c>
       <c r="BP25" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="CB25" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="CG25" t="s">
+        <v>372</v>
+      </c>
+      <c r="CH25" t="s">
+        <v>373</v>
+      </c>
+      <c r="CI25" t="s">
+        <v>374</v>
+      </c>
+      <c r="CL25" t="s">
+        <v>375</v>
+      </c>
+      <c r="CN25" t="s">
         <v>376</v>
-      </c>
-      <c r="CH25" t="s">
-        <v>377</v>
-      </c>
-      <c r="CI25" t="s">
-        <v>378</v>
-      </c>
-      <c r="CL25" t="s">
-        <v>379</v>
-      </c>
-      <c r="CN25" t="s">
-        <v>380</v>
       </c>
       <c r="CO25">
         <v>-10</v>
@@ -8349,21 +8347,21 @@
         <v>5</v>
       </c>
       <c r="CY25" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C26" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I26">
         <v>1</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="M26"/>
       <c r="N26"/>
@@ -8378,7 +8376,7 @@
         <v>1</v>
       </c>
       <c r="AO26" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AW26">
         <v>1</v>
@@ -8388,7 +8386,7 @@
       </c>
       <c r="BV26"/>
       <c r="CN26" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="CR26">
         <v>9999</v>
@@ -8399,16 +8397,16 @@
     </row>
     <row r="27" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C27" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I27">
         <v>1</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="M27"/>
       <c r="N27"/>
@@ -8420,7 +8418,7 @@
         <v>1</v>
       </c>
       <c r="AG27" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BD27">
         <v>1</v>
@@ -8429,14 +8427,14 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="CB27" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="CC27" s="3"/>
       <c r="CD27" s="3"/>
       <c r="CE27" s="3"/>
       <c r="CF27" s="3"/>
       <c r="CG27" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CH27" s="3"/>
       <c r="CI27" s="3"/>
@@ -8458,19 +8456,19 @@
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C28" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I28">
         <v>1</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="M28"/>
       <c r="N28"/>
@@ -8484,7 +8482,7 @@
         <v>1</v>
       </c>
       <c r="AG28" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BD28">
         <v>1</v>
@@ -8493,14 +8491,14 @@
         <v>0.5</v>
       </c>
       <c r="CB28" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="CC28" s="3"/>
       <c r="CD28" s="3"/>
       <c r="CE28" s="3"/>
       <c r="CF28" s="3"/>
       <c r="CG28" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CH28" s="3"/>
       <c r="CI28" s="3"/>
@@ -9639,37 +9637,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>446</v>
+      </c>
+      <c r="F1" t="s">
+        <v>447</v>
+      </c>
+      <c r="G1" t="s">
+        <v>448</v>
+      </c>
+      <c r="H1" t="s">
+        <v>449</v>
+      </c>
+      <c r="I1" t="s">
         <v>450</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>451</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>452</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>453</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>454</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>455</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>456</v>
-      </c>
-      <c r="M1" t="s">
-        <v>457</v>
-      </c>
-      <c r="N1" t="s">
-        <v>458</v>
-      </c>
-      <c r="O1" t="s">
-        <v>459</v>
-      </c>
-      <c r="P1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -9677,49 +9675,49 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F2" t="s">
+        <v>458</v>
+      </c>
+      <c r="G2" t="s">
+        <v>459</v>
+      </c>
+      <c r="H2" t="s">
+        <v>460</v>
+      </c>
+      <c r="I2" t="s">
         <v>461</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>462</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>463</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
         <v>464</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>465</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>466</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" t="s">
         <v>467</v>
       </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" t="s">
-        <v>468</v>
-      </c>
-      <c r="N2" t="s">
-        <v>469</v>
-      </c>
-      <c r="O2" t="s">
-        <v>470</v>
-      </c>
-      <c r="P2" t="s">
-        <v>471</v>
-      </c>
       <c r="Q2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -9733,51 +9731,51 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="P3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C4" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -9785,89 +9783,89 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C5" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="J5" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="Q5" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C8" t="s">
+        <v>470</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q8" t="s">
         <v>474</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C10" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="Q10" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="Q11" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C12" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -9875,38 +9873,38 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C13" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="K13">
         <v>0.3</v>
       </c>
       <c r="Q13" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C14" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C15" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -9914,38 +9912,38 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C16" t="s">
+        <v>470</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q16" t="s">
         <v>474</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="J16" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C17" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="Q19" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="276" spans="16:16" x14ac:dyDescent="0.25">
@@ -9980,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9988,13 +9986,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10005,24 +10003,24 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B4" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C4" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D4" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -10045,7 +10043,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -10053,31 +10051,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
       <c r="D2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="H2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="I2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10094,33 +10092,33 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C4" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="E4">
         <v>50</v>
@@ -10153,34 +10151,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F1" t="s">
         <v>503</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>504</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>505</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>506</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>507</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>508</v>
-      </c>
-      <c r="I1" t="s">
-        <v>509</v>
-      </c>
-      <c r="J1" t="s">
-        <v>510</v>
-      </c>
-      <c r="K1" t="s">
-        <v>511</v>
-      </c>
-      <c r="L1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10188,37 +10186,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F2" t="s">
         <v>513</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>514</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>515</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>516</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>517</v>
       </c>
-      <c r="G2" t="s">
-        <v>518</v>
-      </c>
-      <c r="H2" t="s">
-        <v>519</v>
-      </c>
-      <c r="I2" t="s">
-        <v>520</v>
-      </c>
-      <c r="J2" t="s">
-        <v>521</v>
-      </c>
       <c r="K2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -10229,45 +10227,45 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B4" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="D4" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -10303,31 +10301,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E2" t="s">
+        <v>522</v>
+      </c>
+      <c r="F2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E2" t="s">
-        <v>526</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
       <c r="G2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="H2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10344,22 +10342,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -10388,28 +10386,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10417,28 +10415,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10446,10 +10444,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -10472,33 +10470,33 @@
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -10507,13 +10505,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/logos.xlsx
+++ b/Excel/一方通行/logos.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="564">
   <si>
     <t>Id</t>
   </si>
@@ -670,6 +670,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -2057,11 +2063,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -2375,30 +2384,30 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2411,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV4"/>
+  <dimension ref="A1:BX4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -2481,13 +2490,15 @@
     <col min="65" max="65" width="9" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2659,6 +2670,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -2879,6 +2892,12 @@
       <c r="BV2" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -2888,7 +2907,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2896,91 +2915,91 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="W3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AD3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>2</v>
@@ -2989,10 +3008,10 @@
         <v>2</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AN3" s="2" t="s">
         <v>2</v>
@@ -3001,50 +3020,50 @@
         <v>2</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AS3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AS3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="BA3" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BC3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BD3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BE3" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BF3" s="2" t="s">
         <v>2</v>
@@ -3059,43 +3078,49 @@
         <v>2</v>
       </c>
       <c r="BJ3" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BK3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BL3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BM3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BN3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BP3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BQ3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BR3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BS3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BT3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BU3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BV3" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -3103,17 +3128,17 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -3180,23 +3205,23 @@
         <v>4</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AP4" s="2"/>
       <c r="AQ4" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AR4" s="2">
         <v>1</v>
@@ -3218,51 +3243,53 @@
       <c r="BC4" s="2"/>
       <c r="BD4" s="2"/>
       <c r="BE4" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BG4" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BH4" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BI4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BJ4" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK4" s="2">
         <v>6</v>
       </c>
       <c r="BL4" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BM4" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BN4" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BO4" s="2"/>
-      <c r="BP4" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="BP4" s="2"/>
       <c r="BQ4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2" t="s">
         <v>152</v>
       </c>
+      <c r="BR4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BS4" s="2"/>
       <c r="BT4" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BU4" s="2"/>
-      <c r="BV4" s="2">
+        <v>154</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3280,2280 +3307,2280 @@
   <dimension ref="A1:DI516"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
-    <col min="93" max="93" width="9.5" customWidth="1" style="2"/>
-    <col min="94" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="104" width="9.5" customWidth="1" style="2"/>
-    <col min="105" max="106" width="9" customWidth="1" style="2"/>
-    <col min="107" max="108" width="9.5" customWidth="1" style="2"/>
-    <col min="109" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="111" width="9" customWidth="1" style="2"/>
-    <col min="112" max="113" width="9.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="3"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1" style="3"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1" style="3"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="3"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="3"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="3"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="3"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="3"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="3"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="3"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="3"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="3"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="3"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="3"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="3"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="3"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="3"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="3"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="3"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="3"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="3"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="3"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="3"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="3"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="3"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="3"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="3"/>
+    <col min="40" max="40" width="15" customWidth="1" style="3"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="3"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="3"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="3"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="3"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9" customWidth="1" style="3"/>
+    <col min="52" max="52" width="7" customWidth="1" style="3"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="3"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="3"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="3"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="3"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="3"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="3"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="3"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="3"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="3"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="3"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="3"/>
+    <col min="72" max="73" width="8" customWidth="1" style="3"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="3"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="3"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="3"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="3"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="3"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="3"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="3"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="3"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="3"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="3"/>
+    <col min="86" max="86" width="9" customWidth="1" style="3"/>
+    <col min="87" max="87" width="16" customWidth="1" style="3"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="3"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="3"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="3"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="3"/>
+    <col min="93" max="93" width="9.5" customWidth="1" style="3"/>
+    <col min="94" max="98" width="9" customWidth="1" style="3"/>
+    <col min="99" max="99" width="14" customWidth="1" style="3"/>
+    <col min="100" max="100" width="8" customWidth="1" style="3"/>
+    <col min="101" max="101" width="9" customWidth="1" style="3"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="3"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="3"/>
+    <col min="104" max="104" width="9.5" customWidth="1" style="3"/>
+    <col min="105" max="106" width="9" customWidth="1" style="3"/>
+    <col min="107" max="108" width="9.5" customWidth="1" style="3"/>
+    <col min="109" max="109" width="9" customWidth="1" style="3"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="3"/>
+    <col min="111" max="111" width="9" customWidth="1" style="3"/>
+    <col min="112" max="113" width="9.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="U1" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AV1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AW1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BD1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="BK1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BL1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BM1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BN1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BO1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BP1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BR1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BS1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BT1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BU1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BV1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BW1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BX1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="BY1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CA1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CB1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CC1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CD1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CE1" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CF1" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CG1" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CH1" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CI1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CK1" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CL1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CM1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CN1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CO1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CP1" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CR1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="CS1" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CT1" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CU1" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CV1" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CW1" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="CX1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="CY1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="CZ1" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="DA1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DB1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DC1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DD1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DE1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DF1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DG1" s="3" t="s">
         <v>258</v>
       </c>
+      <c r="DH1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="T2" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AE2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AF2" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AG2" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AI2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AK2" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AL2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AM2" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AN2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AO2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AP2" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AS2" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AT2" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AU2" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AV2" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AW2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AX2" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="AY2" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BA2" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BB2" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BC2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BE2" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BF2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BG2" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BH2" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BI2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BK2" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BL2" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BM2" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="BO2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="BP2" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BP2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BQ2" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BR2" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BS2" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="BU2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="BV2" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BV2" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BW2" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="BX2" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="BY2" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="BZ2" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CA2" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CB2" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CC2" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CD2" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CE2" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CF2" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CG2" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CH2" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CI2" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CJ2" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CK2" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CL2" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CM2" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CN2" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CO2" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CP2" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CQ2" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CR2" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CS2" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CT2" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CU2" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CV2" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CW2" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="CX2" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="CY2" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="CZ2" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DA2" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DB2" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DC2" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DD2" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DE2" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DF2" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="DI2" s="2" t="s">
+      <c r="DG2" s="3" t="s">
         <v>364</v>
       </c>
+      <c r="DH2" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="DI2" s="3" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="U3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="AR3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AW3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="BA3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="BP3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="BQ3" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="BS3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI3" s="2" t="s">
+      <c r="BT3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BV3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BW3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BX3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BY3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="BZ3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CA3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="CB3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CC3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="CD3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CE3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CG3" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="CH3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="CI3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="CK3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="CL3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="CN3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CP3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="CS3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CT3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CU3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CV3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="CW3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="CX3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="CY3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="CZ3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="DA3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="DB3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="DC3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="DD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DI3" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="S5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="AX5" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BP5" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="CB5" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="CG5" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="CH5" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="CI5" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CL5" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="CN5" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="CO5" s="3">
+        <v>-10</v>
+      </c>
+      <c r="CP5" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CR5" s="3">
+        <v>5</v>
+      </c>
+      <c r="CY5" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="AW6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN6" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="CR6" s="3">
+        <v>9999</v>
+      </c>
+      <c r="CS6" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AW7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ7" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>99</v>
+      </c>
+      <c r="BO7" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="BP7" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="BS7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CH7" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="CI7" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CL7" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="CM7" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="CN7" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="CO7" s="3">
+        <v>-0.8</v>
+      </c>
+      <c r="CR7" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="CY7" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO8" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AW8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD8" s="3">
+        <v>99</v>
+      </c>
+      <c r="CN8" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="CO8" s="3">
+        <v>-10</v>
+      </c>
+      <c r="CP8" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CR8" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AW9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="AZ9" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="BD9" s="3">
+        <v>99</v>
+      </c>
+      <c r="CY9" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="G11" s="3">
         <v>3</v>
       </c>
-      <c r="AK3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="J11" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AT11" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="BD11" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO11" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="BP11" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BT11" s="3">
+        <v>99999</v>
+      </c>
+      <c r="BV11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW11" s="3">
+        <v>60</v>
+      </c>
+      <c r="BX11" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY11" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="CN11" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="CO11" s="3">
+        <v>1</v>
+      </c>
+      <c r="CR11" s="3">
+        <v>99999</v>
+      </c>
+      <c r="CU11" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AT12" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="BD12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO12" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="BP12" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="BT12" s="3">
+        <v>99999</v>
+      </c>
+      <c r="BV12" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW12" s="3">
+        <v>60</v>
+      </c>
+      <c r="BX12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY12" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="CN12" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="CO12" s="3">
+        <v>1</v>
+      </c>
+      <c r="CR12" s="3">
+        <v>99999</v>
+      </c>
+      <c r="CU12" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="AC13" s="3">
         <v>2</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AD13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AT13" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="AX13" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ13" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="3">
+        <v>1</v>
+      </c>
+      <c r="BP13" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="CB13" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="CG13" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="CH13" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="CI13" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CL13" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="CN13" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="CO13" s="3">
+        <v>-10</v>
+      </c>
+      <c r="CP13" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CR13" s="3">
+        <v>5</v>
+      </c>
+      <c r="CY13" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2</v>
       </c>
-      <c r="AS3" s="2" t="s">
+      <c r="AD14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="AW14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AX14" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ14" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD14" s="3">
+        <v>1</v>
+      </c>
+      <c r="BP14" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="CL14" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="CN14" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="CR14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="BD15" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS15" s="3">
+        <v>0.333</v>
+      </c>
+      <c r="CB15" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="CG15" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="DD15" s="3">
+        <v>1</v>
+      </c>
+      <c r="DF15" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG15" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="BD17" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO17" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="BP17" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="BT17" s="3">
+        <v>20</v>
+      </c>
+      <c r="BV17" s="3">
+        <v>20</v>
+      </c>
+      <c r="BW17" s="3">
+        <v>30</v>
+      </c>
+      <c r="BX17" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY17" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="CN17" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="CO17" s="3">
+        <v>70</v>
+      </c>
+      <c r="CR17" s="3">
+        <v>20</v>
+      </c>
+      <c r="DC17" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="AC18" s="3">
         <v>2</v>
       </c>
-      <c r="AT3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="CI3" s="2" t="s">
+      <c r="AD18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AT18" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="AX18" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ18" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="BD18" s="3">
+        <v>1</v>
+      </c>
+      <c r="BP18" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="BS18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="CB18" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="CE18" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="CH18" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="CI18" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CL18" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="CN18" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="CO18" s="3">
+        <v>-0.04</v>
+      </c>
+      <c r="CR18" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="CY18" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="BD19" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN19" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="CO19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="CR19" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="AC20" s="3">
         <v>2</v>
       </c>
-      <c r="CJ3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="S5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="2">
+      <c r="AD20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO20" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AW20" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD20" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN20" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="CR20" s="3">
+        <v>9999</v>
+      </c>
+      <c r="CS20" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="BD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS21" s="3">
+        <v>0.167</v>
+      </c>
+      <c r="CB21" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="CG21" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="CN21" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="CR21" s="3">
+        <v>19.7</v>
+      </c>
+      <c r="DD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="DF21" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG21" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="BD22" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS22" s="3">
+        <v>0.267</v>
+      </c>
+      <c r="CB22" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="CG22" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="DD22" s="3">
+        <v>1</v>
+      </c>
+      <c r="DF22" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG22" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AT24" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="BD24" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO24" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="BP24" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="BT24" s="3">
+        <v>30</v>
+      </c>
+      <c r="BV24" s="3">
+        <v>30</v>
+      </c>
+      <c r="BW24" s="3">
+        <v>45</v>
+      </c>
+      <c r="BX24" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY24" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="CN24" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="CO24" s="3">
+        <v>3</v>
+      </c>
+      <c r="CR24" s="3">
+        <v>30</v>
+      </c>
+      <c r="CU24" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="DB24" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="DC24" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="AC25" s="3">
         <v>2</v>
       </c>
-      <c r="AD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO5" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AT5" s="2" t="s">
+      <c r="AD25" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO25" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AT25" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="AX25" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ25" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD25" s="3">
+        <v>4</v>
+      </c>
+      <c r="BP25" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="CB25" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="CG25" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="CH25" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="CI25" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CL25" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="CN25" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="CO25" s="3">
+        <v>-10</v>
+      </c>
+      <c r="CP25" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CR25" s="3">
+        <v>5</v>
+      </c>
+      <c r="CY25" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="AX5" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AZ5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP5" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="CB5" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="CG5" s="2" t="s">
+      <c r="I26" s="3">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO26" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="AW26" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD26" s="3">
+        <v>4</v>
+      </c>
+      <c r="CN26" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="CH5" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="CI5" s="2" t="s">
+      <c r="CR26" s="3">
+        <v>9999</v>
+      </c>
+      <c r="CS26" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="BD27" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS27" s="3">
+        <v>0.167</v>
+      </c>
+      <c r="CB27" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="CG27" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="CL5" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="CN5" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="CO5" s="2">
-        <v>-10</v>
-      </c>
-      <c r="CP5" s="2">
+      <c r="DD27" s="3">
+        <v>1</v>
+      </c>
+      <c r="DF27" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG27" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="BD28" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS28" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="CB28" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="CG28" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="DD28" s="3">
+        <v>1</v>
+      </c>
+      <c r="DF28" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG28" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH28" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="CL496" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="CL498" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="CL499" s="3">
         <v>0.1</v>
       </c>
-      <c r="CR5" s="2">
-        <v>5</v>
-      </c>
-      <c r="CY5" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC6" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="AW6" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN6" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="CR6" s="2">
-        <v>9999</v>
-      </c>
-      <c r="CS6" s="2">
+    </row>
+    <row r="501">
+      <c r="CL501" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="CL508" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="CL510" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="CL511" s="3">
         <v>0.6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AW7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AX7" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AZ7" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="BD7" s="2">
-        <v>99</v>
-      </c>
-      <c r="BO7" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="BP7" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="BS7" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CH7" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="CI7" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CL7" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="CM7" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="CN7" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="CO7" s="2">
-        <v>-0.8</v>
-      </c>
-      <c r="CR7" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="CY7" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AW8" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD8" s="2">
-        <v>99</v>
-      </c>
-      <c r="CN8" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="CO8" s="2">
-        <v>-10</v>
-      </c>
-      <c r="CP8" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CR8" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AC9" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD9" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO9" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AW9" s="2">
-        <v>1</v>
-      </c>
-      <c r="AX9" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="AZ9" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="BD9" s="2">
-        <v>99</v>
-      </c>
-      <c r="CY9" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="G11" s="2">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="AT11" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="BD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO11" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="BP11" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BT11" s="2">
-        <v>99999</v>
-      </c>
-      <c r="BV11" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW11" s="2">
-        <v>60</v>
-      </c>
-      <c r="BX11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY11" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="CN11" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="CO11" s="2">
-        <v>1</v>
-      </c>
-      <c r="CR11" s="2">
-        <v>99999</v>
-      </c>
-      <c r="CU11" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="G12" s="2">
-        <v>3</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="AC12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="AT12" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="BD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO12" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="BP12" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BT12" s="2">
-        <v>99999</v>
-      </c>
-      <c r="BV12" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW12" s="2">
-        <v>60</v>
-      </c>
-      <c r="BX12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY12" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="CN12" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="CO12" s="2">
-        <v>1</v>
-      </c>
-      <c r="CR12" s="2">
-        <v>99999</v>
-      </c>
-      <c r="CU12" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="AC13" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO13" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AT13" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="AX13" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AZ13" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP13" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="CB13" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="CG13" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="CH13" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="CI13" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CL13" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="CN13" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="CO13" s="2">
-        <v>-10</v>
-      </c>
-      <c r="CP13" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CR13" s="2">
-        <v>5</v>
-      </c>
-      <c r="CY13" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="AC14" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO14" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="AW14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AX14" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AZ14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP14" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="CL14" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="CN14" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="CR14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC15" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="BD15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS15" s="2">
-        <v>0.333</v>
-      </c>
-      <c r="CB15" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="CG15" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="DD15" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF15" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG15" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="G17" s="2">
-        <v>3</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="AC17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="BD17" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO17" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="BP17" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="BT17" s="2">
-        <v>20</v>
-      </c>
-      <c r="BV17" s="2">
-        <v>20</v>
-      </c>
-      <c r="BW17" s="2">
-        <v>30</v>
-      </c>
-      <c r="BX17" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY17" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="CN17" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="CO17" s="2">
-        <v>70</v>
-      </c>
-      <c r="CR17" s="2">
-        <v>20</v>
-      </c>
-      <c r="DC17" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="AC18" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO18" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AT18" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="AX18" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AZ18" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="BD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP18" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="BS18" s="2">
+    <row r="514">
+      <c r="CL514" s="3">
         <v>0.5</v>
       </c>
-      <c r="CB18" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="CE18" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="CH18" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="CI18" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CL18" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="CN18" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="CO18" s="2">
-        <v>-0.04</v>
-      </c>
-      <c r="CR18" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="CY18" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="BD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN19" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="CO19" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="CR19" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="AC20" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO20" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AW20" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN20" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="CR20" s="2">
-        <v>9999</v>
-      </c>
-      <c r="CS20" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC21" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG21" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS21" s="2">
-        <v>0.167</v>
-      </c>
-      <c r="CB21" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="CG21" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="CN21" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="CR21" s="2">
-        <v>19.7</v>
-      </c>
-      <c r="DD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="AC22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="BD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS22" s="2">
-        <v>0.267</v>
-      </c>
-      <c r="CB22" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="CG22" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="DD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF22" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG22" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH22" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="G24" s="2">
-        <v>3</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="AC24" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="AT24" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="BD24" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO24" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="BP24" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="BT24" s="2">
-        <v>30</v>
-      </c>
-      <c r="BV24" s="2">
-        <v>30</v>
-      </c>
-      <c r="BW24" s="2">
-        <v>45</v>
-      </c>
-      <c r="BX24" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY24" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="CN24" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="CO24" s="2">
-        <v>3</v>
-      </c>
-      <c r="CR24" s="2">
-        <v>30</v>
-      </c>
-      <c r="CU24" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="DB24" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="DC24" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="AC25" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD25" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO25" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AT25" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="AX25" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AZ25" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD25" s="2">
-        <v>4</v>
-      </c>
-      <c r="BP25" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="CB25" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="CG25" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="CH25" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="CI25" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CL25" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="CN25" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="CO25" s="2">
-        <v>-10</v>
-      </c>
-      <c r="CP25" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CR25" s="2">
-        <v>5</v>
-      </c>
-      <c r="CY25" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC26" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO26" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="AW26" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD26" s="2">
-        <v>4</v>
-      </c>
-      <c r="CN26" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="CR26" s="2">
-        <v>9999</v>
-      </c>
-      <c r="CS26" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I27" s="2">
-        <v>1</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC27" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG27" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="BD27" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS27" s="2">
-        <v>0.167</v>
-      </c>
-      <c r="CB27" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="CG27" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="DD27" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF27" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG27" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH27" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I28" s="2">
-        <v>1</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="AC28" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="BD28" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS28" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="CB28" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="CG28" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="DD28" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF28" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG28" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH28" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="CL496" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="CL498" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="CL499" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="CL501" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="CL508" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="CL510" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="CL511" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="514">
-      <c r="CL514" s="2">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="515">
-      <c r="CL515" s="2">
+      <c r="CL515" s="3">
         <v>0.667</v>
       </c>
     </row>
     <row r="516">
-      <c r="CL516" s="2">
+      <c r="CL516" s="3">
         <v>0.2</v>
       </c>
     </row>
@@ -5571,342 +5598,342 @@
   <dimension ref="A1:Q277"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="13" customWidth="1" style="3"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="3"/>
+    <col min="3" max="6" width="9" customWidth="1" style="3"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="3"/>
+    <col min="8" max="8" width="15" customWidth="1" style="3"/>
+    <col min="9" max="13" width="9" customWidth="1" style="3"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="3"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="3"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="3"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>477</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>350</v>
+      <c r="O2" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>132</v>
+      <c r="L3" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="H4" s="2">
+      <c r="A4" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="H4" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="Q5" s="2" t="s">
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="2" t="s">
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q16" s="3" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>508</v>
+      <c r="A17" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="2" t="s">
-        <v>509</v>
+      <c r="Q19" s="3" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="276">
-      <c r="P276" s="2">
+      <c r="P276" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="277">
-      <c r="P277" s="2">
+      <c r="P277" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5923,60 +5950,60 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="9" customWidth="1" style="3"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>510</v>
+      <c r="C1" s="3" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>350</v>
+      <c r="C2" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>132</v>
+      <c r="C3" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>514</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>516</v>
       </c>
     </row>
   </sheetData>
@@ -5992,96 +6019,96 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="9" customWidth="1" style="3"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="3"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="C4" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="E4" s="3">
         <v>50</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>2</v>
       </c>
     </row>
@@ -6098,139 +6125,139 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="28" customWidth="1" style="3"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="3"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="3"/>
+    <col min="12" max="12" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>529</v>
       </c>
+      <c r="K1" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2">
+      <c r="A4" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
         <v>60</v>
       </c>
     </row>
@@ -6248,45 +6275,45 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="3"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="3"/>
+    <col min="7" max="9" width="9" customWidth="1" style="3"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -6304,22 +6331,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -6351,28 +6378,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2">
@@ -6380,28 +6407,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3">
@@ -6409,10 +6436,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
